--- a/forms/届出書_法的リスク見直し提案_v2.xlsx
+++ b/forms/届出書_法的リスク見直し提案_v2.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="届出書 法的リスク見直し提案" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後①誓約書(幹部用)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後②鍵の保管誓約書" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後③物品借用書" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後④メアド申請書" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後⑤勤務休暇届" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +63,37 @@
       <color rgb="00B91C1C"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001E3A6B"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +120,13 @@
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +148,25 @@
         <color rgb="00B0B7C3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -139,6 +192,33 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -856,4 +936,465 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>※ 黄色ハイライト＝今回の変更箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>誓　約　書　（幹部用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>株式会社ウェルピア羽島／大日産業株式会社　　代表取締役　林　幹根　殿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氏名　　　　　　　　　　　　　　　　　㊞　　　　所属　　　　　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>今後、私は店鍵・設定業務を行うにあたり、下記の事項を誠実に厳守することを誓約します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>記</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>1. いかなる理由によるものであろうと、設定の漏えいは一切致しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>2. その他不正行為に関しても一切致しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>3. 前項1〜2に反した場合は、就業規則に基づく処分に従います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="29" customHeight="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>4. 上記誓約に違反し、故意又は重大な過失により会社に損害を与えた場合は、法令の範囲内で、会社に生じた現実の損害について、下記の極度額を上限として応分の賠償責任を負います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>【身元保証】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>・保証期間：5年（身元保証法の上限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>・極度額：金　　　　　　　　円</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（区分の目安：幹部＝月の総支給額×24ヶ月／役職＝×12ヶ月／一般社員＝×6ヶ月。賞与は含まない。上記から算出した具体的金額を必ず記入すること＝民法465条の2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保証人　　住所：　　　　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　氏名：　　　　　　　　　　㊞　　生年月日：　　　　　　</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>※ 黄色ハイライト＝今回の変更箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>鍵の保管・利用に関する誓約書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>大日産業株式会社　　代表取締役　林　幹根　殿　　　　氏名　　　　　　　㊞</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>わたしは会社より＜　　　　業務＞に関して、　　年　　月　　日に下記の鍵を預託されました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>これらの鍵の保管には細心の注意を払うとともに、店舗の運営管理のために適切に使用し、目的外には使用いたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="29" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>施錠忘れ又は鍵の紛失により会社に被害が生じた場合は、故意又は重大な過失があるときに限り、会社に生じた現実の損害の範囲で、信義則上相当な限度において賠償します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>業務から外れたとき、あるいは会社の請求があったときは速やかに返還いたします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>記</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">セキュリティカード　　　個　　No.　　　　　／　店舗鍵　　　個　　No.　　　　　</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>※ 黄色ハイライト＝今回の変更箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>物品借用書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">令和　　　年　　　月　　　日　　　氏名　　　　　　㊞　　所属　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>私は、下記の物品を下記のとおりお借り入れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>1. 使用目的　／　2. 借用期間　／　3. 借用物品　／　5. 備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>【留意点】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>・使用目的に沿って使用してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>・本人限り使用可。他に貸与・貸出する行為は禁止です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>・使用の必要がなくなった場合は速やかに本社総務まで返納してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>・故意又は重大な過失により紛失・破損した場合は、会社に生じた現実の損害の範囲で、相当な限度において負担していただくことがあります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>※ 黄色ハイライト＝今回の変更箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>メールアドレス申請書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">令和　　　年　　　月　　　日　　　氏名　　　　　　㊞　　所属　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>2. 希望アドレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　第一希望　[　　　　　　　　　]@eurostar-2000.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　第二希望　[　　　　　　　　　]@eurostar-2000.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>注意：アドレスにはアルファベット・英数字以外は使用しないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>3. アカウント情報　アカウント名：[　　　　　　　　　]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>※ パスワードは紙には記載しません。初回ログイン時にご本人が設定してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>（旧様式の「パスワード：[　]」記入欄は削除しました）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>※ 黄色ハイライト＝今回の変更箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>勤務・休暇届出書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>届出事項（該当にㇾ印）：　□遅刻　□早退　□時間外勤務　□年次有給休暇　□慶弔休暇　□特別休暇　□欠勤　□振替休日出勤　□代休休日出勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>《理由》欄について</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>※ 年次有給休暇は取得理由の記入は不要です（労基法39条・時季指定権）。《理由》欄の対象外とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>※ 《理由》欄は、慶弔休暇・特別休暇・欠勤など理由確認が必要な区分のみ記入してください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/forms/届出書_法的リスク見直し提案_v2.xlsx
+++ b/forms/届出書_法的リスク見直し提案_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,49 @@
       <color rgb="001E3A6B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="HG明朝B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="HG明朝B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="HG明朝B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="HGP明朝B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="HGP明朝B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -126,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -162,11 +205,205 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="dotted"/>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <left style="dotted"/>
+      <right style="thin"/>
+      <top style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom style="dotted"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted"/>
+      <bottom style="dotted"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom style="dotted"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="dotted"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <bottom style="dotted"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="dotted"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="dotted"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="dotted"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -218,6 +455,169 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -944,133 +1344,919 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B23"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="1" max="1"/>
+    <col width="2.77734375" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="3" max="3"/>
+    <col width="2.77734375" customWidth="1" min="4" max="4"/>
+    <col width="2.77734375" customWidth="1" min="5" max="5"/>
+    <col width="2.77734375" customWidth="1" min="6" max="6"/>
+    <col width="2.77734375" customWidth="1" min="7" max="7"/>
+    <col width="2.77734375" customWidth="1" min="8" max="8"/>
+    <col width="2.77734375" customWidth="1" min="9" max="9"/>
+    <col width="2.77734375" customWidth="1" min="10" max="10"/>
+    <col width="2.77734375" customWidth="1" min="11" max="11"/>
+    <col width="2.77734375" customWidth="1" min="12" max="12"/>
+    <col width="2.77734375" customWidth="1" min="13" max="13"/>
+    <col width="2.77734375" customWidth="1" min="14" max="14"/>
+    <col width="2.77734375" customWidth="1" min="15" max="15"/>
+    <col width="2.77734375" customWidth="1" min="16" max="16"/>
+    <col width="2.77734375" customWidth="1" min="17" max="17"/>
+    <col width="2.77734375" customWidth="1" min="18" max="18"/>
+    <col width="2.77734375" customWidth="1" min="19" max="19"/>
+    <col width="2.77734375" customWidth="1" min="20" max="20"/>
+    <col width="2.77734375" customWidth="1" min="21" max="21"/>
+    <col width="2.77734375" customWidth="1" min="22" max="22"/>
+    <col width="2.77734375" customWidth="1" min="23" max="23"/>
+    <col width="2.77734375" customWidth="1" min="24" max="24"/>
+    <col width="2.77734375" customWidth="1" min="25" max="25"/>
+    <col width="2.77734375" customWidth="1" min="26" max="26"/>
+    <col width="2.77734375" customWidth="1" min="27" max="27"/>
+    <col width="2.77734375" customWidth="1" min="28" max="28"/>
+    <col width="2.77734375" customWidth="1" min="29" max="29"/>
+    <col width="2.77734375" customWidth="1" min="30" max="30"/>
+    <col width="2.77734375" customWidth="1" min="31" max="31"/>
+    <col width="2.77734375" customWidth="1" min="32" max="32"/>
+    <col width="2.77734375" customWidth="1" min="33" max="33"/>
+    <col width="2.77734375" customWidth="1" min="34" max="34"/>
+    <col width="2.77734375" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>※ 黄色ハイライト＝今回の変更箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>誓　約　書　（幹部用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="13" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>届出書⑮-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>令和　　　年　　　月　　　日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>株式会社ウェルピア羽島／大日産業株式会社　　代表取締役　林　幹根　殿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氏名　　　　　　　　　　　　　　　　　㊞　　　　所属　　　　　　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>今後、私は店鍵・設定業務を行うにあたり、下記の事項を誠実に厳守することを誓約します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="15" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="21" t="n"/>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="21" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="21" t="n"/>
+      <c r="L3" s="21" t="n"/>
+      <c r="M3" s="21" t="n"/>
+      <c r="N3" s="21" t="n"/>
+      <c r="O3" s="21" t="n"/>
+      <c r="P3" s="21" t="n"/>
+      <c r="Q3" s="21" t="n"/>
+      <c r="R3" s="21" t="n"/>
+      <c r="S3" s="21" t="n"/>
+      <c r="T3" s="21" t="n"/>
+      <c r="U3" s="21" t="n"/>
+      <c r="V3" s="21" t="n"/>
+      <c r="W3" s="21" t="n"/>
+      <c r="X3" s="21" t="n"/>
+      <c r="Y3" s="21" t="n"/>
+      <c r="Z3" s="21" t="n"/>
+      <c r="AA3" s="21" t="n"/>
+      <c r="AB3" s="21" t="n"/>
+      <c r="AC3" s="21" t="n"/>
+      <c r="AD3" s="21" t="n"/>
+      <c r="AE3" s="21" t="n"/>
+      <c r="AF3" s="21" t="n"/>
+      <c r="AG3" s="21" t="n"/>
+      <c r="AH3" s="21" t="n"/>
+      <c r="AI3" s="21" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>誓　約　書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>（　幹部用　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>大日産業　株式会社</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="21" t="n"/>
+      <c r="M6" s="21" t="n"/>
+      <c r="N6" s="21" t="n"/>
+      <c r="O6" s="21" t="n"/>
+      <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="21" t="n"/>
+      <c r="R6" s="21" t="n"/>
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="21" t="n"/>
+      <c r="U6" s="21" t="n"/>
+      <c r="V6" s="21" t="n"/>
+      <c r="W6" s="21" t="n"/>
+      <c r="X6" s="21" t="n"/>
+      <c r="Y6" s="21" t="n"/>
+      <c r="Z6" s="21" t="n"/>
+      <c r="AA6" s="21" t="n"/>
+      <c r="AB6" s="21" t="n"/>
+      <c r="AC6" s="21" t="n"/>
+      <c r="AD6" s="21" t="n"/>
+      <c r="AE6" s="21" t="n"/>
+      <c r="AF6" s="21" t="n"/>
+      <c r="AG6" s="21" t="n"/>
+      <c r="AH6" s="21" t="n"/>
+      <c r="AI6" s="21" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>代表取締役　林　幹根　殿</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="21" t="n"/>
+      <c r="Y7" s="21" t="n"/>
+      <c r="Z7" s="21" t="n"/>
+      <c r="AA7" s="21" t="n"/>
+      <c r="AB7" s="21" t="n"/>
+      <c r="AC7" s="21" t="n"/>
+      <c r="AD7" s="21" t="n"/>
+      <c r="AE7" s="21" t="n"/>
+      <c r="AF7" s="21" t="n"/>
+      <c r="AG7" s="21" t="n"/>
+      <c r="AH7" s="21" t="n"/>
+      <c r="AI7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="21" t="n"/>
+      <c r="X8" s="21" t="n"/>
+      <c r="Y8" s="21" t="n"/>
+      <c r="Z8" s="21" t="n"/>
+      <c r="AA8" s="21" t="n"/>
+      <c r="AB8" s="21" t="n"/>
+      <c r="AC8" s="21" t="n"/>
+      <c r="AD8" s="21" t="n"/>
+      <c r="AE8" s="21" t="n"/>
+      <c r="AF8" s="21" t="n"/>
+      <c r="AG8" s="21" t="n"/>
+      <c r="AH8" s="21" t="n"/>
+      <c r="AI8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="21" t="n"/>
+      <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="Z9" s="25" t="n"/>
+      <c r="AA9" s="25" t="n"/>
+      <c r="AB9" s="25" t="n"/>
+      <c r="AC9" s="25" t="n"/>
+      <c r="AD9" s="25" t="n"/>
+      <c r="AE9" s="25" t="n"/>
+      <c r="AF9" s="25" t="n"/>
+      <c r="AG9" s="25" t="n"/>
+      <c r="AH9" s="25" t="n"/>
+      <c r="AI9" s="25" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
+      <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+      <c r="U10" s="21" t="n"/>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>所属</t>
+        </is>
+      </c>
+      <c r="Z10" s="25" t="n"/>
+      <c r="AA10" s="25" t="n"/>
+      <c r="AB10" s="25" t="n"/>
+      <c r="AC10" s="25" t="n"/>
+      <c r="AD10" s="25" t="n"/>
+      <c r="AE10" s="25" t="n"/>
+      <c r="AF10" s="25" t="n"/>
+      <c r="AG10" s="25" t="n"/>
+      <c r="AH10" s="25" t="n"/>
+      <c r="AI10" s="25" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="21" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="21" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="21" t="n"/>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="21" t="n"/>
+      <c r="AF11" s="21" t="n"/>
+      <c r="AG11" s="21" t="n"/>
+      <c r="AH11" s="21" t="n"/>
+      <c r="AI11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　今後、私は店鍵、設定業務を行うにあたり、下記の事項を誠実に厳守することを誓約します。</t>
+        </is>
+      </c>
+      <c r="AI12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="21" t="n"/>
+      <c r="P13" s="21" t="n"/>
+      <c r="Q13" s="21" t="n"/>
+      <c r="R13" s="21" t="n"/>
+      <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
+      <c r="U13" s="21" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="21" t="n"/>
+      <c r="X13" s="21" t="n"/>
+      <c r="Y13" s="21" t="n"/>
+      <c r="Z13" s="21" t="n"/>
+      <c r="AA13" s="21" t="n"/>
+      <c r="AB13" s="21" t="n"/>
+      <c r="AC13" s="21" t="n"/>
+      <c r="AD13" s="21" t="n"/>
+      <c r="AE13" s="21" t="n"/>
+      <c r="AF13" s="21" t="n"/>
+      <c r="AG13" s="21" t="n"/>
+      <c r="AH13" s="21" t="n"/>
+      <c r="AI13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>記</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="23" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="23" t="n"/>
+      <c r="AC15" s="23" t="n"/>
+      <c r="AD15" s="23" t="n"/>
+      <c r="AE15" s="23" t="n"/>
+      <c r="AF15" s="23" t="n"/>
+      <c r="AG15" s="23" t="n"/>
+      <c r="AH15" s="23" t="n"/>
+      <c r="AI15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>1. いかなる理由によるものであろうと、設定の漏えいは一切致しません。</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="AI16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="24" t="n"/>
+      <c r="P17" s="24" t="n"/>
+      <c r="Q17" s="24" t="n"/>
+      <c r="R17" s="24" t="n"/>
+      <c r="S17" s="24" t="n"/>
+      <c r="T17" s="24" t="n"/>
+      <c r="U17" s="24" t="n"/>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="24" t="n"/>
+      <c r="X17" s="24" t="n"/>
+      <c r="Y17" s="24" t="n"/>
+      <c r="Z17" s="24" t="n"/>
+      <c r="AA17" s="24" t="n"/>
+      <c r="AB17" s="24" t="n"/>
+      <c r="AC17" s="24" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="24" t="n"/>
+      <c r="AF17" s="24" t="n"/>
+      <c r="AG17" s="24" t="n"/>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>2. その他不正行為に関しても一切致しません。</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>3. 前項1〜2に反した場合は、就業規則に基づく処分に従います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="29" customHeight="1">
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>4. 上記誓約に違反し、故意又は重大な過失により会社に損害を与えた場合は、法令の範囲内で、会社に生じた現実の損害について、下記の極度額を上限として応分の賠償責任を負います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>【身元保証】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>・保証期間：5年（身元保証法の上限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>・極度額：金　　　　　　　　円</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="29" customHeight="1">
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（区分の目安：幹部＝月の総支給額×24ヶ月／役職＝×12ヶ月／一般社員＝×6ヶ月。賞与は含まない。上記から算出した具体的金額を必ず記入すること＝民法465条の2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">保証人　　住所：　　　　　　　　　　　　　　　　　　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　氏名：　　　　　　　　　　㊞　　生年月日：　　　　　　</t>
-        </is>
-      </c>
+      <c r="AI18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="24" t="n"/>
+      <c r="T19" s="24" t="n"/>
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="24" t="n"/>
+      <c r="X19" s="24" t="n"/>
+      <c r="Y19" s="24" t="n"/>
+      <c r="Z19" s="24" t="n"/>
+      <c r="AA19" s="24" t="n"/>
+      <c r="AB19" s="24" t="n"/>
+      <c r="AC19" s="24" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="24" t="n"/>
+      <c r="AF19" s="24" t="n"/>
+      <c r="AG19" s="24" t="n"/>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>3. 前項１～２に反した場合は、就業規則に基づく処分に従います。</t>
+        </is>
+      </c>
+      <c r="AI20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="21" t="n"/>
+      <c r="N21" s="21" t="n"/>
+      <c r="O21" s="21" t="n"/>
+      <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+      <c r="U21" s="21" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="21" t="n"/>
+      <c r="X21" s="21" t="n"/>
+      <c r="Y21" s="21" t="n"/>
+      <c r="Z21" s="21" t="n"/>
+      <c r="AA21" s="21" t="n"/>
+      <c r="AB21" s="21" t="n"/>
+      <c r="AC21" s="21" t="n"/>
+      <c r="AD21" s="21" t="n"/>
+      <c r="AE21" s="21" t="n"/>
+      <c r="AF21" s="21" t="n"/>
+      <c r="AG21" s="21" t="n"/>
+      <c r="AH21" s="21" t="n"/>
+      <c r="AI21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　上記誓約に違反し、故意又は重大な過失により会社に損害を与えた場合は、法令の範囲内で、会社に生じた現実の損害について、下記の極度額を上限として応分の賠償責任を負います。</t>
+        </is>
+      </c>
+      <c r="AI22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="21" t="n"/>
+      <c r="P23" s="21" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="21" t="n"/>
+      <c r="X23" s="21" t="n"/>
+      <c r="Y23" s="21" t="n"/>
+      <c r="Z23" s="21" t="n"/>
+      <c r="AA23" s="21" t="n"/>
+      <c r="AB23" s="21" t="n"/>
+      <c r="AC23" s="21" t="n"/>
+      <c r="AD23" s="21" t="n"/>
+      <c r="AE23" s="21" t="n"/>
+      <c r="AF23" s="21" t="n"/>
+      <c r="AG23" s="21" t="n"/>
+      <c r="AH23" s="21" t="n"/>
+      <c r="AI23" s="21" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>【身元保証】　保証期間：5年（身元保証法の上限）</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
+      <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="21" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="21" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="21" t="n"/>
+      <c r="X24" s="21" t="n"/>
+      <c r="Y24" s="21" t="n"/>
+      <c r="Z24" s="21" t="n"/>
+      <c r="AA24" s="21" t="n"/>
+      <c r="AB24" s="21" t="n"/>
+      <c r="AC24" s="21" t="n"/>
+      <c r="AD24" s="21" t="n"/>
+      <c r="AE24" s="21" t="n"/>
+      <c r="AF24" s="21" t="n"/>
+      <c r="AG24" s="21" t="n"/>
+      <c r="AH24" s="21" t="n"/>
+      <c r="AI24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　極度額：金　　　　　　　　円</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="21" t="n"/>
+      <c r="O25" s="21" t="n"/>
+      <c r="P25" s="21" t="n"/>
+      <c r="Q25" s="21" t="n"/>
+      <c r="R25" s="21" t="n"/>
+      <c r="S25" s="21" t="n"/>
+      <c r="T25" s="21" t="n"/>
+      <c r="U25" s="21" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="21" t="n"/>
+      <c r="X25" s="21" t="n"/>
+      <c r="Y25" s="21" t="n"/>
+      <c r="Z25" s="21" t="n"/>
+      <c r="AA25" s="21" t="n"/>
+      <c r="AB25" s="21" t="n"/>
+      <c r="AC25" s="21" t="n"/>
+      <c r="AD25" s="21" t="n"/>
+      <c r="AE25" s="21" t="n"/>
+      <c r="AF25" s="21" t="n"/>
+      <c r="AG25" s="21" t="n"/>
+      <c r="AH25" s="21" t="n"/>
+      <c r="AI25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（目安：幹部＝月総支給×24／役職×12／一般×6ヶ月。具体的金額を記入＝民法465条の2）</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="21" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="21" t="n"/>
+      <c r="X26" s="21" t="n"/>
+      <c r="Y26" s="21" t="n"/>
+      <c r="Z26" s="21" t="n"/>
+      <c r="AA26" s="21" t="n"/>
+      <c r="AB26" s="21" t="n"/>
+      <c r="AC26" s="21" t="n"/>
+      <c r="AD26" s="21" t="n"/>
+      <c r="AE26" s="21" t="n"/>
+      <c r="AF26" s="21" t="n"/>
+      <c r="AG26" s="21" t="n"/>
+      <c r="AH26" s="21" t="n"/>
+      <c r="AI26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="21" t="n"/>
+      <c r="M27" s="21" t="n"/>
+      <c r="N27" s="21" t="n"/>
+      <c r="O27" s="21" t="n"/>
+      <c r="P27" s="21" t="n"/>
+      <c r="Q27" s="21" t="n"/>
+      <c r="R27" s="21" t="n"/>
+      <c r="S27" s="21" t="n"/>
+      <c r="T27" s="21" t="n"/>
+      <c r="U27" s="21" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="21" t="n"/>
+      <c r="X27" s="21" t="n"/>
+      <c r="Y27" s="21" t="inlineStr">
+        <is>
+          <t>【保証人】</t>
+        </is>
+      </c>
+      <c r="Z27" s="21" t="n"/>
+      <c r="AA27" s="21" t="n"/>
+      <c r="AB27" s="21" t="n"/>
+      <c r="AC27" s="21" t="n"/>
+      <c r="AD27" s="21" t="n"/>
+      <c r="AE27" s="21" t="n"/>
+      <c r="AF27" s="21" t="n"/>
+      <c r="AG27" s="21" t="n"/>
+      <c r="AH27" s="21" t="n"/>
+      <c r="AI27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="21" t="n"/>
+      <c r="M28" s="21" t="n"/>
+      <c r="N28" s="21" t="n"/>
+      <c r="O28" s="21" t="n"/>
+      <c r="P28" s="21" t="n"/>
+      <c r="Q28" s="21" t="n"/>
+      <c r="R28" s="21" t="n"/>
+      <c r="S28" s="21" t="n"/>
+      <c r="T28" s="21" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="U28" s="21" t="n"/>
+      <c r="V28" s="21" t="n"/>
+      <c r="W28" s="21" t="n"/>
+      <c r="X28" s="21" t="n"/>
+      <c r="Y28" s="24" t="n"/>
+      <c r="AI28" s="21" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="21" t="n"/>
+      <c r="M29" s="21" t="n"/>
+      <c r="N29" s="21" t="n"/>
+      <c r="O29" s="21" t="n"/>
+      <c r="P29" s="21" t="n"/>
+      <c r="Q29" s="21" t="n"/>
+      <c r="R29" s="21" t="n"/>
+      <c r="S29" s="21" t="n"/>
+      <c r="T29" s="21" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="U29" s="21" t="n"/>
+      <c r="V29" s="21" t="n"/>
+      <c r="W29" s="21" t="n"/>
+      <c r="X29" s="21" t="n"/>
+      <c r="Y29" s="21" t="n"/>
+      <c r="Z29" s="21" t="n"/>
+      <c r="AA29" s="21" t="n"/>
+      <c r="AB29" s="21" t="n"/>
+      <c r="AC29" s="21" t="n"/>
+      <c r="AD29" s="21" t="n"/>
+      <c r="AE29" s="21" t="n"/>
+      <c r="AF29" s="21" t="n"/>
+      <c r="AG29" s="21" t="n"/>
+      <c r="AH29" s="21" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+      <c r="AI29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="21" t="n"/>
+      <c r="L30" s="21" t="n"/>
+      <c r="M30" s="21" t="n"/>
+      <c r="N30" s="21" t="n"/>
+      <c r="O30" s="21" t="n"/>
+      <c r="P30" s="21" t="n"/>
+      <c r="Q30" s="21" t="n"/>
+      <c r="R30" s="21" t="n"/>
+      <c r="S30" s="21" t="n"/>
+      <c r="T30" s="21" t="inlineStr">
+        <is>
+          <t>生年月日</t>
+        </is>
+      </c>
+      <c r="U30" s="21" t="n"/>
+      <c r="V30" s="21" t="n"/>
+      <c r="W30" s="21" t="n"/>
+      <c r="X30" s="21" t="n"/>
+      <c r="Y30" s="21" t="n"/>
+      <c r="Z30" s="21" t="n"/>
+      <c r="AA30" s="21" t="n"/>
+      <c r="AB30" s="21" t="n"/>
+      <c r="AC30" s="21" t="n"/>
+      <c r="AD30" s="21" t="n"/>
+      <c r="AE30" s="21" t="n"/>
+      <c r="AF30" s="21" t="n"/>
+      <c r="AG30" s="21" t="n"/>
+      <c r="AH30" s="21" t="n"/>
+      <c r="AI30" s="21" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="Y28:AH28"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="A5:AI5"/>
+    <mergeCell ref="A14:AI14"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="B16:AH16"/>
+    <mergeCell ref="V10:Y10"/>
+    <mergeCell ref="A4:AI4"/>
+    <mergeCell ref="B20:AH20"/>
+    <mergeCell ref="B22:AH22"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1081,84 +2267,3646 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B14"/>
+  <dimension ref="A1:BW58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="2.44140625" customWidth="1" min="1" max="1"/>
+    <col width="2.44140625" customWidth="1" min="2" max="2"/>
+    <col width="2.44140625" customWidth="1" min="3" max="3"/>
+    <col width="2.44140625" customWidth="1" min="4" max="4"/>
+    <col width="2.44140625" customWidth="1" min="5" max="5"/>
+    <col width="2.44140625" customWidth="1" min="6" max="6"/>
+    <col width="2.44140625" customWidth="1" min="7" max="7"/>
+    <col width="2.44140625" customWidth="1" min="8" max="8"/>
+    <col width="2.44140625" customWidth="1" min="9" max="9"/>
+    <col width="2.44140625" customWidth="1" min="10" max="10"/>
+    <col width="2.44140625" customWidth="1" min="11" max="11"/>
+    <col width="2.44140625" customWidth="1" min="12" max="12"/>
+    <col width="2.44140625" customWidth="1" min="13" max="13"/>
+    <col width="2.44140625" customWidth="1" min="14" max="14"/>
+    <col width="2.44140625" customWidth="1" min="15" max="15"/>
+    <col width="2.44140625" customWidth="1" min="16" max="16"/>
+    <col width="2.44140625" customWidth="1" min="17" max="17"/>
+    <col width="2.44140625" customWidth="1" min="18" max="18"/>
+    <col width="2.44140625" customWidth="1" min="19" max="19"/>
+    <col width="2.44140625" customWidth="1" min="20" max="20"/>
+    <col width="2.44140625" customWidth="1" min="21" max="21"/>
+    <col width="2.44140625" customWidth="1" min="22" max="22"/>
+    <col width="2.44140625" customWidth="1" min="23" max="23"/>
+    <col width="2.44140625" customWidth="1" min="24" max="24"/>
+    <col width="2.44140625" customWidth="1" min="25" max="25"/>
+    <col width="2.44140625" customWidth="1" min="26" max="26"/>
+    <col width="2.44140625" customWidth="1" min="27" max="27"/>
+    <col width="2.44140625" customWidth="1" min="28" max="28"/>
+    <col width="2.44140625" customWidth="1" min="29" max="29"/>
+    <col width="2.44140625" customWidth="1" min="30" max="30"/>
+    <col width="2.44140625" customWidth="1" min="31" max="31"/>
+    <col width="2.44140625" customWidth="1" min="32" max="32"/>
+    <col width="2.44140625" customWidth="1" min="33" max="33"/>
+    <col width="2.44140625" customWidth="1" min="34" max="34"/>
+    <col width="2.44140625" customWidth="1" min="35" max="35"/>
+    <col width="2.44140625" customWidth="1" min="36" max="36"/>
+    <col width="2.44140625" customWidth="1" min="37" max="37"/>
+    <col width="2.44140625" customWidth="1" min="38" max="38"/>
+    <col width="2.44140625" customWidth="1" min="39" max="39"/>
+    <col width="2.44140625" customWidth="1" min="40" max="40"/>
+    <col width="2.44140625" customWidth="1" min="41" max="41"/>
+    <col width="2.44140625" customWidth="1" min="42" max="42"/>
+    <col width="2.44140625" customWidth="1" min="43" max="43"/>
+    <col width="2.44140625" customWidth="1" min="44" max="44"/>
+    <col width="2.44140625" customWidth="1" min="45" max="45"/>
+    <col width="2.44140625" customWidth="1" min="46" max="46"/>
+    <col width="2.44140625" customWidth="1" min="47" max="47"/>
+    <col width="2.44140625" customWidth="1" min="48" max="48"/>
+    <col width="2.44140625" customWidth="1" min="49" max="49"/>
+    <col width="2.44140625" customWidth="1" min="50" max="50"/>
+    <col width="2.44140625" customWidth="1" min="51" max="51"/>
+    <col width="2.44140625" customWidth="1" min="52" max="52"/>
+    <col width="2.44140625" customWidth="1" min="53" max="53"/>
+    <col width="2.44140625" customWidth="1" min="54" max="54"/>
+    <col width="2.44140625" customWidth="1" min="55" max="55"/>
+    <col width="2.44140625" customWidth="1" min="56" max="56"/>
+    <col width="2.44140625" customWidth="1" min="57" max="57"/>
+    <col width="2.44140625" customWidth="1" min="58" max="58"/>
+    <col width="2.44140625" customWidth="1" min="59" max="59"/>
+    <col width="2.44140625" customWidth="1" min="60" max="60"/>
+    <col width="2.44140625" customWidth="1" min="61" max="61"/>
+    <col width="2.44140625" customWidth="1" min="62" max="62"/>
+    <col width="2.44140625" customWidth="1" min="63" max="63"/>
+    <col width="2.44140625" customWidth="1" min="64" max="64"/>
+    <col width="2.44140625" customWidth="1" min="65" max="65"/>
+    <col width="2.44140625" customWidth="1" min="66" max="66"/>
+    <col width="2.44140625" customWidth="1" min="67" max="67"/>
+    <col width="2.44140625" customWidth="1" min="68" max="68"/>
+    <col width="2.44140625" customWidth="1" min="69" max="69"/>
+    <col width="2.44140625" customWidth="1" min="70" max="70"/>
+    <col width="2.44140625" customWidth="1" min="71" max="71"/>
+    <col width="2.44140625" customWidth="1" min="72" max="72"/>
+    <col width="2.44140625" customWidth="1" min="73" max="73"/>
+    <col width="2.44140625" customWidth="1" min="74" max="74"/>
+    <col width="2.44140625" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>※ 黄色ハイライト＝今回の変更箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="31" t="n"/>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>届出書⑰-1</t>
+        </is>
+      </c>
+      <c r="AK1" s="31" t="n"/>
+      <c r="AL1" s="31" t="n"/>
+      <c r="AM1" s="31" t="n"/>
+      <c r="AN1" s="31" t="n"/>
+      <c r="AO1" s="31" t="n"/>
+      <c r="AP1" s="31" t="n"/>
+      <c r="AQ1" s="31" t="n"/>
+      <c r="AR1" s="31" t="n"/>
+      <c r="AS1" s="31" t="n"/>
+      <c r="AT1" s="31" t="n"/>
+      <c r="AU1" s="31" t="n"/>
+      <c r="AV1" s="31" t="n"/>
+      <c r="AW1" s="31" t="n"/>
+      <c r="AX1" s="31" t="n"/>
+      <c r="AY1" s="31" t="n"/>
+      <c r="AZ1" s="31" t="n"/>
+      <c r="BA1" s="31" t="n"/>
+      <c r="BB1" s="31" t="n"/>
+      <c r="BC1" s="31" t="n"/>
+      <c r="BD1" s="31" t="n"/>
+      <c r="BE1" s="31" t="n"/>
+      <c r="BF1" s="31" t="n"/>
+      <c r="BG1" s="31" t="n"/>
+      <c r="BH1" s="31" t="n"/>
+      <c r="BI1" s="31" t="n"/>
+      <c r="BJ1" s="31" t="n"/>
+      <c r="BK1" s="31" t="n"/>
+      <c r="BL1" s="31" t="n"/>
+      <c r="BM1" s="31" t="n"/>
+      <c r="BN1" s="31" t="n"/>
+      <c r="BO1" s="31" t="n"/>
+      <c r="BP1" s="31" t="n"/>
+      <c r="BQ1" s="31" t="n"/>
+      <c r="BR1" s="31" t="n"/>
+      <c r="BS1" s="31" t="n"/>
+      <c r="BT1" s="31" t="n"/>
+      <c r="BU1" s="31" t="n"/>
+      <c r="BV1" s="31" t="n"/>
+      <c r="BW1" s="31" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="31" t="n"/>
+      <c r="AK2" s="31" t="n"/>
+      <c r="AL2" s="31" t="n"/>
+      <c r="AM2" s="31" t="n"/>
+      <c r="AN2" s="31" t="n"/>
+      <c r="AO2" s="31" t="n"/>
+      <c r="AP2" s="31" t="n"/>
+      <c r="AQ2" s="31" t="n"/>
+      <c r="AR2" s="31" t="n"/>
+      <c r="AS2" s="31" t="n"/>
+      <c r="AT2" s="31" t="n"/>
+      <c r="AU2" s="31" t="n"/>
+      <c r="AV2" s="31" t="n"/>
+      <c r="AW2" s="31" t="n"/>
+      <c r="AX2" s="31" t="n"/>
+      <c r="AY2" s="31" t="n"/>
+      <c r="AZ2" s="31" t="n"/>
+      <c r="BA2" s="31" t="n"/>
+      <c r="BB2" s="31" t="n"/>
+      <c r="BC2" s="31" t="n"/>
+      <c r="BD2" s="31" t="n"/>
+      <c r="BE2" s="31" t="n"/>
+      <c r="BF2" s="31" t="n"/>
+      <c r="BG2" s="31" t="n"/>
+      <c r="BH2" s="31" t="n"/>
+      <c r="BI2" s="31" t="n"/>
+      <c r="BJ2" s="31" t="n"/>
+      <c r="BK2" s="31" t="n"/>
+      <c r="BL2" s="31" t="n"/>
+      <c r="BM2" s="31" t="n"/>
+      <c r="BN2" s="31" t="n"/>
+      <c r="BO2" s="31" t="n"/>
+      <c r="BP2" s="31" t="n"/>
+      <c r="BQ2" s="31" t="n"/>
+      <c r="BR2" s="31" t="n"/>
+      <c r="BS2" s="31" t="n"/>
+      <c r="BT2" s="31" t="n"/>
+      <c r="BU2" s="31" t="n"/>
+      <c r="BV2" s="31" t="n"/>
+      <c r="BW2" s="31" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="31" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="20" t="n"/>
+      <c r="K3" s="20" t="n"/>
+      <c r="L3" s="20" t="n"/>
+      <c r="M3" s="20" t="n"/>
+      <c r="N3" s="20" t="n"/>
+      <c r="O3" s="20" t="n"/>
+      <c r="P3" s="20" t="n"/>
+      <c r="Q3" s="20" t="n"/>
+      <c r="R3" s="20" t="n"/>
+      <c r="S3" s="20" t="n"/>
+      <c r="T3" s="20" t="n"/>
+      <c r="U3" s="20" t="n"/>
+      <c r="V3" s="20" t="n"/>
+      <c r="W3" s="20" t="n"/>
+      <c r="X3" s="20" t="n"/>
+      <c r="Y3" s="20" t="n"/>
+      <c r="Z3" s="20" t="n"/>
+      <c r="AA3" s="20" t="n"/>
+      <c r="AB3" s="20" t="n"/>
+      <c r="AC3" s="20" t="n"/>
+      <c r="AD3" s="20" t="n"/>
+      <c r="AE3" s="20" t="n"/>
+      <c r="AF3" s="20" t="n"/>
+      <c r="AG3" s="20" t="n"/>
+      <c r="AH3" s="20" t="n"/>
+      <c r="AI3" s="20" t="n"/>
+      <c r="AJ3" s="20" t="n"/>
+      <c r="AK3" s="31" t="n"/>
+      <c r="AL3" s="31" t="n"/>
+      <c r="AM3" s="31" t="n"/>
+      <c r="AN3" s="31" t="n"/>
+      <c r="AO3" s="31" t="n"/>
+      <c r="AP3" s="31" t="n"/>
+      <c r="AQ3" s="31" t="n"/>
+      <c r="AR3" s="31" t="n"/>
+      <c r="AS3" s="31" t="n"/>
+      <c r="AT3" s="31" t="n"/>
+      <c r="AU3" s="31" t="n"/>
+      <c r="AV3" s="31" t="n"/>
+      <c r="AW3" s="31" t="n"/>
+      <c r="AX3" s="31" t="n"/>
+      <c r="AY3" s="31" t="n"/>
+      <c r="AZ3" s="31" t="n"/>
+      <c r="BA3" s="31" t="n"/>
+      <c r="BB3" s="31" t="n"/>
+      <c r="BC3" s="31" t="n"/>
+      <c r="BD3" s="31" t="n"/>
+      <c r="BE3" s="31" t="n"/>
+      <c r="BF3" s="31" t="n"/>
+      <c r="BG3" s="31" t="n"/>
+      <c r="BH3" s="31" t="n"/>
+      <c r="BI3" s="31" t="n"/>
+      <c r="BJ3" s="31" t="n"/>
+      <c r="BK3" s="31" t="n"/>
+      <c r="BL3" s="31" t="n"/>
+      <c r="BM3" s="31" t="n"/>
+      <c r="BN3" s="31" t="n"/>
+      <c r="BO3" s="31" t="n"/>
+      <c r="BP3" s="31" t="n"/>
+      <c r="BQ3" s="31" t="n"/>
+      <c r="BR3" s="31" t="n"/>
+      <c r="BS3" s="31" t="n"/>
+      <c r="BT3" s="31" t="n"/>
+      <c r="BU3" s="31" t="n"/>
+      <c r="BV3" s="31" t="n"/>
+      <c r="BW3" s="31" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="31" t="n"/>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+      <c r="AK4" s="31" t="n"/>
+      <c r="AL4" s="31" t="n"/>
+      <c r="AM4" s="31" t="n"/>
+      <c r="AN4" s="31" t="n"/>
+      <c r="AO4" s="31" t="n"/>
+      <c r="AP4" s="31" t="n"/>
+      <c r="AQ4" s="31" t="n"/>
+      <c r="AR4" s="31" t="n"/>
+      <c r="AS4" s="31" t="n"/>
+      <c r="AT4" s="31" t="n"/>
+      <c r="AU4" s="31" t="n"/>
+      <c r="AV4" s="31" t="n"/>
+      <c r="AW4" s="31" t="n"/>
+      <c r="AX4" s="31" t="n"/>
+      <c r="AY4" s="31" t="n"/>
+      <c r="AZ4" s="31" t="n"/>
+      <c r="BA4" s="31" t="n"/>
+      <c r="BB4" s="31" t="n"/>
+      <c r="BC4" s="31" t="n"/>
+      <c r="BD4" s="31" t="n"/>
+      <c r="BE4" s="31" t="n"/>
+      <c r="BF4" s="31" t="n"/>
+      <c r="BG4" s="31" t="n"/>
+      <c r="BH4" s="31" t="n"/>
+      <c r="BI4" s="31" t="n"/>
+      <c r="BJ4" s="31" t="n"/>
+      <c r="BK4" s="31" t="n"/>
+      <c r="BL4" s="31" t="n"/>
+      <c r="BM4" s="31" t="n"/>
+      <c r="BN4" s="31" t="n"/>
+      <c r="BO4" s="31" t="n"/>
+      <c r="BP4" s="31" t="n"/>
+      <c r="BQ4" s="31" t="n"/>
+      <c r="BR4" s="31" t="n"/>
+      <c r="BS4" s="31" t="n"/>
+      <c r="BT4" s="31" t="n"/>
+      <c r="BU4" s="31" t="n"/>
+      <c r="BV4" s="31" t="n"/>
+      <c r="BW4" s="31" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="31" t="n"/>
+      <c r="AK5" s="31" t="n"/>
+      <c r="AL5" s="31" t="n"/>
+      <c r="AM5" s="31" t="n"/>
+      <c r="AN5" s="31" t="n"/>
+      <c r="AO5" s="31" t="n"/>
+      <c r="AP5" s="31" t="n"/>
+      <c r="AQ5" s="31" t="n"/>
+      <c r="AR5" s="31" t="n"/>
+      <c r="AS5" s="31" t="n"/>
+      <c r="AT5" s="31" t="n"/>
+      <c r="AU5" s="31" t="n"/>
+      <c r="AV5" s="31" t="n"/>
+      <c r="AW5" s="31" t="n"/>
+      <c r="AX5" s="31" t="n"/>
+      <c r="AY5" s="31" t="n"/>
+      <c r="AZ5" s="31" t="n"/>
+      <c r="BA5" s="31" t="n"/>
+      <c r="BB5" s="31" t="n"/>
+      <c r="BC5" s="31" t="n"/>
+      <c r="BD5" s="31" t="n"/>
+      <c r="BE5" s="31" t="n"/>
+      <c r="BF5" s="31" t="n"/>
+      <c r="BG5" s="31" t="n"/>
+      <c r="BH5" s="31" t="n"/>
+      <c r="BI5" s="31" t="n"/>
+      <c r="BJ5" s="31" t="n"/>
+      <c r="BK5" s="31" t="n"/>
+      <c r="BL5" s="31" t="n"/>
+      <c r="BM5" s="31" t="n"/>
+      <c r="BN5" s="31" t="n"/>
+      <c r="BO5" s="31" t="n"/>
+      <c r="BP5" s="31" t="n"/>
+      <c r="BQ5" s="31" t="n"/>
+      <c r="BR5" s="31" t="n"/>
+      <c r="BS5" s="31" t="n"/>
+      <c r="BT5" s="31" t="n"/>
+      <c r="BU5" s="31" t="n"/>
+      <c r="BV5" s="31" t="n"/>
+      <c r="BW5" s="31" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="31" t="n"/>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>大日産業株式会社　　　　　　　　　代表取締役　林　幹根　殿</t>
+        </is>
+      </c>
+      <c r="M6" s="31" t="n"/>
+      <c r="N6" s="31" t="n"/>
+      <c r="O6" s="31" t="n"/>
+      <c r="P6" s="31" t="n"/>
+      <c r="Q6" s="31" t="n"/>
+      <c r="R6" s="31" t="n"/>
+      <c r="S6" s="31" t="n"/>
+      <c r="T6" s="31" t="n"/>
+      <c r="U6" s="31" t="n"/>
+      <c r="V6" s="31" t="n"/>
+      <c r="W6" s="31" t="n"/>
+      <c r="X6" s="31" t="n"/>
+      <c r="Y6" s="31" t="n"/>
+      <c r="Z6" s="31" t="n"/>
+      <c r="AA6" s="31" t="n"/>
+      <c r="AB6" s="31" t="n"/>
+      <c r="AC6" s="31" t="n"/>
+      <c r="AD6" s="31" t="n"/>
+      <c r="AE6" s="31" t="n"/>
+      <c r="AF6" s="31" t="n"/>
+      <c r="AG6" s="31" t="n"/>
+      <c r="AH6" s="31" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="31" t="n"/>
+      <c r="AL6" s="31" t="n"/>
+      <c r="AM6" s="31" t="n"/>
+      <c r="AN6" s="31" t="n"/>
+      <c r="AO6" s="31" t="n"/>
+      <c r="AP6" s="31" t="n"/>
+      <c r="AQ6" s="31" t="n"/>
+      <c r="AR6" s="31" t="n"/>
+      <c r="AS6" s="31" t="n"/>
+      <c r="AT6" s="31" t="n"/>
+      <c r="AU6" s="31" t="n"/>
+      <c r="AV6" s="31" t="n"/>
+      <c r="AW6" s="31" t="n"/>
+      <c r="AX6" s="31" t="n"/>
+      <c r="AY6" s="31" t="n"/>
+      <c r="AZ6" s="31" t="n"/>
+      <c r="BA6" s="31" t="n"/>
+      <c r="BB6" s="31" t="n"/>
+      <c r="BC6" s="31" t="n"/>
+      <c r="BD6" s="31" t="n"/>
+      <c r="BE6" s="31" t="n"/>
+      <c r="BF6" s="31" t="n"/>
+      <c r="BG6" s="31" t="n"/>
+      <c r="BH6" s="31" t="n"/>
+      <c r="BI6" s="31" t="n"/>
+      <c r="BJ6" s="31" t="n"/>
+      <c r="BK6" s="31" t="n"/>
+      <c r="BL6" s="31" t="n"/>
+      <c r="BM6" s="31" t="n"/>
+      <c r="BN6" s="31" t="n"/>
+      <c r="BO6" s="31" t="n"/>
+      <c r="BP6" s="31" t="n"/>
+      <c r="BQ6" s="31" t="n"/>
+      <c r="BR6" s="31" t="n"/>
+      <c r="BS6" s="31" t="n"/>
+      <c r="BT6" s="31" t="n"/>
+      <c r="BU6" s="31" t="n"/>
+      <c r="BV6" s="31" t="n"/>
+      <c r="BW6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="31" t="n"/>
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="31" t="n"/>
+      <c r="O7" s="31" t="n"/>
+      <c r="P7" s="31" t="n"/>
+      <c r="Q7" s="31" t="n"/>
+      <c r="R7" s="31" t="n"/>
+      <c r="S7" s="31" t="n"/>
+      <c r="T7" s="31" t="n"/>
+      <c r="U7" s="31" t="n"/>
+      <c r="V7" s="31" t="n"/>
+      <c r="W7" s="31" t="n"/>
+      <c r="X7" s="31" t="n"/>
+      <c r="Y7" s="31" t="n"/>
+      <c r="Z7" s="31" t="n"/>
+      <c r="AA7" s="31" t="n"/>
+      <c r="AB7" s="31" t="n"/>
+      <c r="AC7" s="31" t="n"/>
+      <c r="AD7" s="31" t="n"/>
+      <c r="AE7" s="31" t="n"/>
+      <c r="AF7" s="31" t="n"/>
+      <c r="AG7" s="31" t="n"/>
+      <c r="AH7" s="31" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="31" t="n"/>
+      <c r="AL7" s="31" t="n"/>
+      <c r="AM7" s="31" t="n"/>
+      <c r="AN7" s="31" t="n"/>
+      <c r="AO7" s="31" t="n"/>
+      <c r="AP7" s="31" t="n"/>
+      <c r="AQ7" s="31" t="n"/>
+      <c r="AR7" s="31" t="n"/>
+      <c r="AS7" s="31" t="n"/>
+      <c r="AT7" s="31" t="n"/>
+      <c r="AU7" s="31" t="n"/>
+      <c r="AV7" s="31" t="n"/>
+      <c r="AW7" s="31" t="n"/>
+      <c r="AX7" s="31" t="n"/>
+      <c r="AY7" s="31" t="n"/>
+      <c r="AZ7" s="31" t="n"/>
+      <c r="BA7" s="31" t="n"/>
+      <c r="BB7" s="31" t="n"/>
+      <c r="BC7" s="31" t="n"/>
+      <c r="BD7" s="31" t="n"/>
+      <c r="BE7" s="31" t="n"/>
+      <c r="BF7" s="31" t="n"/>
+      <c r="BG7" s="31" t="n"/>
+      <c r="BH7" s="31" t="n"/>
+      <c r="BI7" s="31" t="n"/>
+      <c r="BJ7" s="31" t="n"/>
+      <c r="BK7" s="31" t="n"/>
+      <c r="BL7" s="31" t="n"/>
+      <c r="BM7" s="31" t="n"/>
+      <c r="BN7" s="31" t="n"/>
+      <c r="BO7" s="31" t="n"/>
+      <c r="BP7" s="31" t="n"/>
+      <c r="BQ7" s="31" t="n"/>
+      <c r="BR7" s="31" t="n"/>
+      <c r="BS7" s="31" t="n"/>
+      <c r="BT7" s="31" t="n"/>
+      <c r="BU7" s="31" t="n"/>
+      <c r="BV7" s="31" t="n"/>
+      <c r="BW7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="31" t="n"/>
+      <c r="O8" s="31" t="n"/>
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="31" t="n"/>
+      <c r="R8" s="31" t="n"/>
+      <c r="S8" s="31" t="n"/>
+      <c r="T8" s="31" t="n"/>
+      <c r="U8" s="31" t="n"/>
+      <c r="V8" s="31" t="n"/>
+      <c r="W8" s="31" t="n"/>
+      <c r="X8" s="31" t="n"/>
+      <c r="Y8" s="31" t="n"/>
+      <c r="Z8" s="31" t="n"/>
+      <c r="AA8" s="31" t="n"/>
+      <c r="AB8" s="31" t="n"/>
+      <c r="AC8" s="31" t="n"/>
+      <c r="AD8" s="31" t="n"/>
+      <c r="AE8" s="31" t="n"/>
+      <c r="AF8" s="31" t="n"/>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="31" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="31" t="n"/>
+      <c r="AL8" s="31" t="n"/>
+      <c r="AM8" s="31" t="n"/>
+      <c r="AN8" s="31" t="n"/>
+      <c r="AO8" s="31" t="n"/>
+      <c r="AP8" s="31" t="n"/>
+      <c r="AQ8" s="31" t="n"/>
+      <c r="AR8" s="31" t="n"/>
+      <c r="AS8" s="31" t="n"/>
+      <c r="AT8" s="31" t="n"/>
+      <c r="AU8" s="31" t="n"/>
+      <c r="AV8" s="31" t="n"/>
+      <c r="AW8" s="31" t="n"/>
+      <c r="AX8" s="31" t="n"/>
+      <c r="AY8" s="31" t="n"/>
+      <c r="AZ8" s="31" t="n"/>
+      <c r="BA8" s="31" t="n"/>
+      <c r="BB8" s="31" t="n"/>
+      <c r="BC8" s="31" t="n"/>
+      <c r="BD8" s="31" t="n"/>
+      <c r="BE8" s="31" t="n"/>
+      <c r="BF8" s="31" t="n"/>
+      <c r="BG8" s="31" t="n"/>
+      <c r="BH8" s="31" t="n"/>
+      <c r="BI8" s="31" t="n"/>
+      <c r="BJ8" s="31" t="n"/>
+      <c r="BK8" s="31" t="n"/>
+      <c r="BL8" s="31" t="n"/>
+      <c r="BM8" s="31" t="n"/>
+      <c r="BN8" s="31" t="n"/>
+      <c r="BO8" s="31" t="n"/>
+      <c r="BP8" s="31" t="n"/>
+      <c r="BQ8" s="31" t="n"/>
+      <c r="BR8" s="31" t="n"/>
+      <c r="BS8" s="31" t="n"/>
+      <c r="BT8" s="31" t="n"/>
+      <c r="BU8" s="31" t="n"/>
+      <c r="BV8" s="31" t="n"/>
+      <c r="BW8" s="31" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n"/>
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+      <c r="J9" s="31" t="n"/>
+      <c r="K9" s="31" t="n"/>
+      <c r="L9" s="31" t="n"/>
+      <c r="M9" s="31" t="n"/>
+      <c r="N9" s="31" t="n"/>
+      <c r="O9" s="31" t="n"/>
+      <c r="P9" s="31" t="n"/>
+      <c r="Q9" s="31" t="n"/>
+      <c r="R9" s="31" t="n"/>
+      <c r="S9" s="31" t="n"/>
+      <c r="T9" s="31" t="n"/>
+      <c r="U9" s="31" t="n"/>
+      <c r="V9" s="31" t="n"/>
+      <c r="W9" s="31" t="n"/>
+      <c r="X9" s="31" t="n"/>
+      <c r="Y9" s="31" t="n"/>
+      <c r="Z9" s="31" t="n"/>
+      <c r="AA9" s="31" t="n"/>
+      <c r="AB9" s="31" t="n"/>
+      <c r="AC9" s="31" t="n"/>
+      <c r="AD9" s="31" t="n"/>
+      <c r="AE9" s="31" t="n"/>
+      <c r="AF9" s="31" t="n"/>
+      <c r="AG9" s="31" t="n"/>
+      <c r="AH9" s="31" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="31" t="n"/>
+      <c r="AL9" s="31" t="n"/>
+      <c r="AM9" s="31" t="n"/>
+      <c r="AN9" s="31" t="n"/>
+      <c r="AO9" s="31" t="n"/>
+      <c r="AP9" s="31" t="n"/>
+      <c r="AQ9" s="31" t="n"/>
+      <c r="AR9" s="31" t="n"/>
+      <c r="AS9" s="31" t="n"/>
+      <c r="AT9" s="31" t="n"/>
+      <c r="AU9" s="31" t="n"/>
+      <c r="AV9" s="31" t="n"/>
+      <c r="AW9" s="31" t="n"/>
+      <c r="AX9" s="31" t="n"/>
+      <c r="AY9" s="31" t="n"/>
+      <c r="AZ9" s="31" t="n"/>
+      <c r="BA9" s="31" t="n"/>
+      <c r="BB9" s="31" t="n"/>
+      <c r="BC9" s="31" t="n"/>
+      <c r="BD9" s="31" t="n"/>
+      <c r="BE9" s="31" t="n"/>
+      <c r="BF9" s="31" t="n"/>
+      <c r="BG9" s="31" t="n"/>
+      <c r="BH9" s="31" t="n"/>
+      <c r="BI9" s="31" t="n"/>
+      <c r="BJ9" s="31" t="n"/>
+      <c r="BK9" s="31" t="n"/>
+      <c r="BL9" s="31" t="n"/>
+      <c r="BM9" s="31" t="n"/>
+      <c r="BN9" s="31" t="n"/>
+      <c r="BO9" s="31" t="n"/>
+      <c r="BP9" s="31" t="n"/>
+      <c r="BQ9" s="31" t="n"/>
+      <c r="BR9" s="31" t="n"/>
+      <c r="BS9" s="31" t="n"/>
+      <c r="BT9" s="31" t="n"/>
+      <c r="BU9" s="31" t="n"/>
+      <c r="BV9" s="31" t="n"/>
+      <c r="BW9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="31" t="n"/>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+      <c r="J10" s="31" t="n"/>
+      <c r="K10" s="31" t="n"/>
+      <c r="L10" s="31" t="n"/>
+      <c r="M10" s="31" t="n"/>
+      <c r="N10" s="31" t="n"/>
+      <c r="O10" s="31" t="n"/>
+      <c r="P10" s="31" t="n"/>
+      <c r="Q10" s="31" t="n"/>
+      <c r="R10" s="31" t="n"/>
+      <c r="S10" s="31" t="n"/>
+      <c r="T10" s="31" t="n"/>
+      <c r="U10" s="31" t="n"/>
+      <c r="V10" s="34" t="inlineStr">
+        <is>
+          <t>氏　　名　　　　　　　　　　　　　　　　　　　㊞</t>
+        </is>
+      </c>
+      <c r="AK10" s="31" t="n"/>
+      <c r="AL10" s="31" t="n"/>
+      <c r="AM10" s="31" t="n"/>
+      <c r="AN10" s="31" t="n"/>
+      <c r="AO10" s="31" t="n"/>
+      <c r="AP10" s="31" t="n"/>
+      <c r="AQ10" s="31" t="n"/>
+      <c r="AR10" s="31" t="n"/>
+      <c r="AS10" s="31" t="n"/>
+      <c r="AT10" s="31" t="n"/>
+      <c r="AU10" s="31" t="n"/>
+      <c r="AV10" s="31" t="n"/>
+      <c r="AW10" s="31" t="n"/>
+      <c r="AX10" s="31" t="n"/>
+      <c r="AY10" s="31" t="n"/>
+      <c r="AZ10" s="31" t="n"/>
+      <c r="BA10" s="31" t="n"/>
+      <c r="BB10" s="31" t="n"/>
+      <c r="BC10" s="31" t="n"/>
+      <c r="BD10" s="31" t="n"/>
+      <c r="BE10" s="31" t="n"/>
+      <c r="BF10" s="31" t="n"/>
+      <c r="BG10" s="31" t="n"/>
+      <c r="BH10" s="31" t="n"/>
+      <c r="BI10" s="31" t="n"/>
+      <c r="BJ10" s="31" t="n"/>
+      <c r="BK10" s="31" t="n"/>
+      <c r="BL10" s="31" t="n"/>
+      <c r="BM10" s="31" t="n"/>
+      <c r="BN10" s="31" t="n"/>
+      <c r="BO10" s="31" t="n"/>
+      <c r="BP10" s="31" t="n"/>
+      <c r="BQ10" s="31" t="n"/>
+      <c r="BR10" s="31" t="n"/>
+      <c r="BS10" s="31" t="n"/>
+      <c r="BT10" s="31" t="n"/>
+      <c r="BU10" s="31" t="n"/>
+      <c r="BV10" s="31" t="n"/>
+      <c r="BW10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="31" t="n"/>
+      <c r="J11" s="31" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="n"/>
+      <c r="P11" s="31" t="n"/>
+      <c r="Q11" s="31" t="n"/>
+      <c r="R11" s="31" t="n"/>
+      <c r="S11" s="31" t="n"/>
+      <c r="T11" s="31" t="n"/>
+      <c r="U11" s="31" t="n"/>
+      <c r="AK11" s="31" t="n"/>
+      <c r="AL11" s="31" t="n"/>
+      <c r="AM11" s="31" t="n"/>
+      <c r="AN11" s="31" t="n"/>
+      <c r="AO11" s="31" t="n"/>
+      <c r="AP11" s="31" t="n"/>
+      <c r="AQ11" s="31" t="n"/>
+      <c r="AR11" s="31" t="n"/>
+      <c r="AS11" s="31" t="n"/>
+      <c r="AT11" s="31" t="n"/>
+      <c r="AU11" s="31" t="n"/>
+      <c r="AV11" s="31" t="n"/>
+      <c r="AW11" s="31" t="n"/>
+      <c r="AX11" s="31" t="n"/>
+      <c r="AY11" s="31" t="n"/>
+      <c r="AZ11" s="31" t="n"/>
+      <c r="BA11" s="31" t="n"/>
+      <c r="BB11" s="31" t="n"/>
+      <c r="BC11" s="31" t="n"/>
+      <c r="BD11" s="31" t="n"/>
+      <c r="BE11" s="31" t="n"/>
+      <c r="BF11" s="31" t="n"/>
+      <c r="BG11" s="31" t="n"/>
+      <c r="BH11" s="31" t="n"/>
+      <c r="BI11" s="31" t="n"/>
+      <c r="BJ11" s="31" t="n"/>
+      <c r="BK11" s="31" t="n"/>
+      <c r="BL11" s="31" t="n"/>
+      <c r="BM11" s="31" t="n"/>
+      <c r="BN11" s="31" t="n"/>
+      <c r="BO11" s="31" t="n"/>
+      <c r="BP11" s="31" t="n"/>
+      <c r="BQ11" s="31" t="n"/>
+      <c r="BR11" s="31" t="n"/>
+      <c r="BS11" s="31" t="n"/>
+      <c r="BT11" s="31" t="n"/>
+      <c r="BU11" s="31" t="n"/>
+      <c r="BV11" s="31" t="n"/>
+      <c r="BW11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n"/>
+      <c r="M12" s="31" t="n"/>
+      <c r="N12" s="31" t="n"/>
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="31" t="n"/>
+      <c r="Q12" s="31" t="n"/>
+      <c r="R12" s="31" t="n"/>
+      <c r="S12" s="31" t="n"/>
+      <c r="T12" s="31" t="n"/>
+      <c r="U12" s="31" t="n"/>
+      <c r="V12" s="34" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="34" t="n"/>
+      <c r="Y12" s="34" t="n"/>
+      <c r="Z12" s="34" t="n"/>
+      <c r="AA12" s="34" t="n"/>
+      <c r="AB12" s="34" t="n"/>
+      <c r="AC12" s="34" t="n"/>
+      <c r="AD12" s="34" t="n"/>
+      <c r="AE12" s="34" t="n"/>
+      <c r="AF12" s="34" t="n"/>
+      <c r="AG12" s="34" t="n"/>
+      <c r="AH12" s="34" t="n"/>
+      <c r="AI12" s="34" t="n"/>
+      <c r="AJ12" s="34" t="n"/>
+      <c r="AK12" s="31" t="n"/>
+      <c r="AL12" s="31" t="n"/>
+      <c r="AM12" s="31" t="n"/>
+      <c r="AN12" s="31" t="n"/>
+      <c r="AO12" s="31" t="n"/>
+      <c r="AP12" s="31" t="n"/>
+      <c r="AQ12" s="31" t="n"/>
+      <c r="AR12" s="31" t="n"/>
+      <c r="AS12" s="31" t="n"/>
+      <c r="AT12" s="31" t="n"/>
+      <c r="AU12" s="31" t="n"/>
+      <c r="AV12" s="31" t="n"/>
+      <c r="AW12" s="31" t="n"/>
+      <c r="AX12" s="31" t="n"/>
+      <c r="AY12" s="31" t="n"/>
+      <c r="AZ12" s="31" t="n"/>
+      <c r="BA12" s="31" t="n"/>
+      <c r="BB12" s="31" t="n"/>
+      <c r="BC12" s="31" t="n"/>
+      <c r="BD12" s="31" t="n"/>
+      <c r="BE12" s="31" t="n"/>
+      <c r="BF12" s="31" t="n"/>
+      <c r="BG12" s="31" t="n"/>
+      <c r="BH12" s="31" t="n"/>
+      <c r="BI12" s="31" t="n"/>
+      <c r="BJ12" s="31" t="n"/>
+      <c r="BK12" s="31" t="n"/>
+      <c r="BL12" s="31" t="n"/>
+      <c r="BM12" s="31" t="n"/>
+      <c r="BN12" s="31" t="n"/>
+      <c r="BO12" s="31" t="n"/>
+      <c r="BP12" s="31" t="n"/>
+      <c r="BQ12" s="31" t="n"/>
+      <c r="BR12" s="31" t="n"/>
+      <c r="BS12" s="31" t="n"/>
+      <c r="BT12" s="31" t="n"/>
+      <c r="BU12" s="31" t="n"/>
+      <c r="BV12" s="31" t="n"/>
+      <c r="BW12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="31" t="n"/>
+      <c r="S13" s="31" t="n"/>
+      <c r="T13" s="31" t="n"/>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="34" t="n"/>
+      <c r="W13" s="34" t="n"/>
+      <c r="X13" s="34" t="n"/>
+      <c r="Y13" s="34" t="n"/>
+      <c r="Z13" s="34" t="n"/>
+      <c r="AA13" s="34" t="n"/>
+      <c r="AB13" s="34" t="n"/>
+      <c r="AC13" s="34" t="n"/>
+      <c r="AD13" s="34" t="n"/>
+      <c r="AE13" s="34" t="n"/>
+      <c r="AF13" s="34" t="n"/>
+      <c r="AG13" s="34" t="n"/>
+      <c r="AH13" s="34" t="n"/>
+      <c r="AI13" s="34" t="n"/>
+      <c r="AJ13" s="34" t="n"/>
+      <c r="AK13" s="31" t="n"/>
+      <c r="AL13" s="31" t="n"/>
+      <c r="AM13" s="31" t="n"/>
+      <c r="AN13" s="31" t="n"/>
+      <c r="AO13" s="31" t="n"/>
+      <c r="AP13" s="31" t="n"/>
+      <c r="AQ13" s="31" t="n"/>
+      <c r="AR13" s="31" t="n"/>
+      <c r="AS13" s="31" t="n"/>
+      <c r="AT13" s="31" t="n"/>
+      <c r="AU13" s="31" t="n"/>
+      <c r="AV13" s="31" t="n"/>
+      <c r="AW13" s="31" t="n"/>
+      <c r="AX13" s="31" t="n"/>
+      <c r="AY13" s="31" t="n"/>
+      <c r="AZ13" s="31" t="n"/>
+      <c r="BA13" s="31" t="n"/>
+      <c r="BB13" s="31" t="n"/>
+      <c r="BC13" s="31" t="n"/>
+      <c r="BD13" s="31" t="n"/>
+      <c r="BE13" s="31" t="n"/>
+      <c r="BF13" s="31" t="n"/>
+      <c r="BG13" s="31" t="n"/>
+      <c r="BH13" s="31" t="n"/>
+      <c r="BI13" s="31" t="n"/>
+      <c r="BJ13" s="31" t="n"/>
+      <c r="BK13" s="31" t="n"/>
+      <c r="BL13" s="31" t="n"/>
+      <c r="BM13" s="31" t="n"/>
+      <c r="BN13" s="31" t="n"/>
+      <c r="BO13" s="31" t="n"/>
+      <c r="BP13" s="31" t="n"/>
+      <c r="BQ13" s="31" t="n"/>
+      <c r="BR13" s="31" t="n"/>
+      <c r="BS13" s="31" t="n"/>
+      <c r="BT13" s="31" t="n"/>
+      <c r="BU13" s="31" t="n"/>
+      <c r="BV13" s="31" t="n"/>
+      <c r="BW13" s="31" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="31" t="n"/>
+      <c r="J14" s="31" t="n"/>
+      <c r="K14" s="31" t="n"/>
+      <c r="L14" s="31" t="n"/>
+      <c r="M14" s="31" t="n"/>
+      <c r="N14" s="31" t="n"/>
+      <c r="O14" s="31" t="n"/>
+      <c r="P14" s="31" t="n"/>
+      <c r="Q14" s="31" t="n"/>
+      <c r="R14" s="31" t="n"/>
+      <c r="S14" s="31" t="n"/>
+      <c r="T14" s="31" t="n"/>
+      <c r="U14" s="31" t="n"/>
+      <c r="V14" s="31" t="n"/>
+      <c r="W14" s="31" t="n"/>
+      <c r="X14" s="31" t="n"/>
+      <c r="Y14" s="31" t="n"/>
+      <c r="Z14" s="31" t="n"/>
+      <c r="AA14" s="31" t="n"/>
+      <c r="AB14" s="31" t="n"/>
+      <c r="AC14" s="31" t="n"/>
+      <c r="AD14" s="31" t="n"/>
+      <c r="AE14" s="31" t="n"/>
+      <c r="AF14" s="31" t="n"/>
+      <c r="AG14" s="31" t="n"/>
+      <c r="AH14" s="31" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="31" t="n"/>
+      <c r="AL14" s="31" t="n"/>
+      <c r="AM14" s="31" t="n"/>
+      <c r="AN14" s="31" t="n"/>
+      <c r="AO14" s="31" t="n"/>
+      <c r="AP14" s="31" t="n"/>
+      <c r="AQ14" s="31" t="n"/>
+      <c r="AR14" s="31" t="n"/>
+      <c r="AS14" s="31" t="n"/>
+      <c r="AT14" s="31" t="n"/>
+      <c r="AU14" s="31" t="n"/>
+      <c r="AV14" s="31" t="n"/>
+      <c r="AW14" s="31" t="n"/>
+      <c r="AX14" s="31" t="n"/>
+      <c r="AY14" s="31" t="n"/>
+      <c r="AZ14" s="31" t="n"/>
+      <c r="BA14" s="31" t="n"/>
+      <c r="BB14" s="31" t="n"/>
+      <c r="BC14" s="31" t="n"/>
+      <c r="BD14" s="31" t="n"/>
+      <c r="BE14" s="31" t="n"/>
+      <c r="BF14" s="31" t="n"/>
+      <c r="BG14" s="31" t="n"/>
+      <c r="BH14" s="31" t="n"/>
+      <c r="BI14" s="31" t="n"/>
+      <c r="BJ14" s="31" t="n"/>
+      <c r="BK14" s="31" t="n"/>
+      <c r="BL14" s="31" t="n"/>
+      <c r="BM14" s="31" t="n"/>
+      <c r="BN14" s="31" t="n"/>
+      <c r="BO14" s="31" t="n"/>
+      <c r="BP14" s="31" t="n"/>
+      <c r="BQ14" s="31" t="n"/>
+      <c r="BR14" s="31" t="n"/>
+      <c r="BS14" s="31" t="n"/>
+      <c r="BT14" s="31" t="n"/>
+      <c r="BU14" s="31" t="n"/>
+      <c r="BV14" s="31" t="n"/>
+      <c r="BW14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>鍵の保管・利用に関する誓約書</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>令和　　　年　　　月　　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>大日産業株式会社　　代表取締役　林　幹根　殿　　　　氏名　　　　　　　㊞</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>わたしは会社より＜　　　　業務＞に関して、　　年　　月　　日に下記の鍵を預託されました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="29" customHeight="1">
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>これらの鍵の保管には細心の注意を払うとともに、店舗の運営管理のために適切に使用し、目的外には使用いたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29" customHeight="1">
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>施錠忘れ又は鍵の紛失により会社に被害が生じた場合は、故意又は重大な過失があるときに限り、会社に生じた現実の損害の範囲で、信義則上相当な限度において賠償します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>業務から外れたとき、あるいは会社の請求があったときは速やかに返還いたします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="AK15" s="31" t="n"/>
+      <c r="AL15" s="31" t="n"/>
+      <c r="AM15" s="31" t="n"/>
+      <c r="AN15" s="31" t="n"/>
+      <c r="AO15" s="31" t="n"/>
+      <c r="AP15" s="31" t="n"/>
+      <c r="AQ15" s="31" t="n"/>
+      <c r="AR15" s="31" t="n"/>
+      <c r="AS15" s="31" t="n"/>
+      <c r="AT15" s="31" t="n"/>
+      <c r="AU15" s="31" t="n"/>
+      <c r="AV15" s="31" t="n"/>
+      <c r="AW15" s="31" t="n"/>
+      <c r="AX15" s="31" t="n"/>
+      <c r="AY15" s="31" t="n"/>
+      <c r="AZ15" s="31" t="n"/>
+      <c r="BA15" s="31" t="n"/>
+      <c r="BB15" s="31" t="n"/>
+      <c r="BC15" s="31" t="n"/>
+      <c r="BD15" s="31" t="n"/>
+      <c r="BE15" s="31" t="n"/>
+      <c r="BF15" s="31" t="n"/>
+      <c r="BG15" s="31" t="n"/>
+      <c r="BH15" s="31" t="n"/>
+      <c r="BI15" s="31" t="n"/>
+      <c r="BJ15" s="31" t="n"/>
+      <c r="BK15" s="31" t="n"/>
+      <c r="BL15" s="31" t="n"/>
+      <c r="BM15" s="31" t="n"/>
+      <c r="BN15" s="31" t="n"/>
+      <c r="BO15" s="31" t="n"/>
+      <c r="BP15" s="31" t="n"/>
+      <c r="BQ15" s="31" t="n"/>
+      <c r="BR15" s="31" t="n"/>
+      <c r="BS15" s="31" t="n"/>
+      <c r="BT15" s="31" t="n"/>
+      <c r="BU15" s="31" t="n"/>
+      <c r="BV15" s="31" t="n"/>
+      <c r="BW15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="31" t="n"/>
+      <c r="AK16" s="31" t="n"/>
+      <c r="AL16" s="31" t="n"/>
+      <c r="AM16" s="31" t="n"/>
+      <c r="AN16" s="31" t="n"/>
+      <c r="AO16" s="31" t="n"/>
+      <c r="AP16" s="31" t="n"/>
+      <c r="AQ16" s="31" t="n"/>
+      <c r="AR16" s="31" t="n"/>
+      <c r="AS16" s="31" t="n"/>
+      <c r="AT16" s="31" t="n"/>
+      <c r="AU16" s="31" t="n"/>
+      <c r="AV16" s="31" t="n"/>
+      <c r="AW16" s="31" t="n"/>
+      <c r="AX16" s="31" t="n"/>
+      <c r="AY16" s="31" t="n"/>
+      <c r="AZ16" s="31" t="n"/>
+      <c r="BA16" s="31" t="n"/>
+      <c r="BB16" s="31" t="n"/>
+      <c r="BC16" s="31" t="n"/>
+      <c r="BD16" s="31" t="n"/>
+      <c r="BE16" s="31" t="n"/>
+      <c r="BF16" s="31" t="n"/>
+      <c r="BG16" s="31" t="n"/>
+      <c r="BH16" s="31" t="n"/>
+      <c r="BI16" s="31" t="n"/>
+      <c r="BJ16" s="31" t="n"/>
+      <c r="BK16" s="31" t="n"/>
+      <c r="BL16" s="31" t="n"/>
+      <c r="BM16" s="31" t="n"/>
+      <c r="BN16" s="31" t="n"/>
+      <c r="BO16" s="31" t="n"/>
+      <c r="BP16" s="31" t="n"/>
+      <c r="BQ16" s="31" t="n"/>
+      <c r="BR16" s="31" t="n"/>
+      <c r="BS16" s="31" t="n"/>
+      <c r="BT16" s="31" t="n"/>
+      <c r="BU16" s="31" t="n"/>
+      <c r="BV16" s="31" t="n"/>
+      <c r="BW16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="35" t="n"/>
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="35" t="n"/>
+      <c r="N17" s="35" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="35" t="n"/>
+      <c r="U17" s="35" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="35" t="n"/>
+      <c r="X17" s="35" t="n"/>
+      <c r="Y17" s="35" t="n"/>
+      <c r="Z17" s="35" t="n"/>
+      <c r="AA17" s="35" t="n"/>
+      <c r="AB17" s="35" t="n"/>
+      <c r="AC17" s="35" t="n"/>
+      <c r="AD17" s="35" t="n"/>
+      <c r="AE17" s="35" t="n"/>
+      <c r="AF17" s="35" t="n"/>
+      <c r="AG17" s="35" t="n"/>
+      <c r="AH17" s="35" t="n"/>
+      <c r="AI17" s="35" t="n"/>
+      <c r="AJ17" s="35" t="n"/>
+      <c r="AK17" s="31" t="n"/>
+      <c r="AL17" s="31" t="n"/>
+      <c r="AM17" s="31" t="n"/>
+      <c r="AN17" s="31" t="n"/>
+      <c r="AO17" s="31" t="n"/>
+      <c r="AP17" s="31" t="n"/>
+      <c r="AQ17" s="31" t="n"/>
+      <c r="AR17" s="31" t="n"/>
+      <c r="AS17" s="31" t="n"/>
+      <c r="AT17" s="31" t="n"/>
+      <c r="AU17" s="31" t="n"/>
+      <c r="AV17" s="31" t="n"/>
+      <c r="AW17" s="31" t="n"/>
+      <c r="AX17" s="31" t="n"/>
+      <c r="AY17" s="31" t="n"/>
+      <c r="AZ17" s="31" t="n"/>
+      <c r="BA17" s="31" t="n"/>
+      <c r="BB17" s="31" t="n"/>
+      <c r="BC17" s="31" t="n"/>
+      <c r="BD17" s="31" t="n"/>
+      <c r="BE17" s="31" t="n"/>
+      <c r="BF17" s="31" t="n"/>
+      <c r="BG17" s="31" t="n"/>
+      <c r="BH17" s="31" t="n"/>
+      <c r="BI17" s="31" t="n"/>
+      <c r="BJ17" s="31" t="n"/>
+      <c r="BK17" s="31" t="n"/>
+      <c r="BL17" s="31" t="n"/>
+      <c r="BM17" s="31" t="n"/>
+      <c r="BN17" s="31" t="n"/>
+      <c r="BO17" s="31" t="n"/>
+      <c r="BP17" s="31" t="n"/>
+      <c r="BQ17" s="31" t="n"/>
+      <c r="BR17" s="31" t="n"/>
+      <c r="BS17" s="31" t="n"/>
+      <c r="BT17" s="31" t="n"/>
+      <c r="BU17" s="31" t="n"/>
+      <c r="BV17" s="31" t="n"/>
+      <c r="BW17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="36" t="n"/>
+      <c r="O18" s="36" t="n"/>
+      <c r="P18" s="36" t="n"/>
+      <c r="Q18" s="36" t="n"/>
+      <c r="R18" s="36" t="n"/>
+      <c r="S18" s="36" t="n"/>
+      <c r="T18" s="36" t="n"/>
+      <c r="U18" s="36" t="n"/>
+      <c r="V18" s="36" t="n"/>
+      <c r="W18" s="36" t="n"/>
+      <c r="X18" s="36" t="n"/>
+      <c r="Y18" s="36" t="n"/>
+      <c r="Z18" s="36" t="n"/>
+      <c r="AA18" s="36" t="n"/>
+      <c r="AB18" s="36" t="n"/>
+      <c r="AC18" s="36" t="n"/>
+      <c r="AD18" s="36" t="n"/>
+      <c r="AE18" s="36" t="n"/>
+      <c r="AF18" s="36" t="n"/>
+      <c r="AG18" s="36" t="n"/>
+      <c r="AH18" s="36" t="n"/>
+      <c r="AI18" s="36" t="n"/>
+      <c r="AJ18" s="36" t="n"/>
+      <c r="AK18" s="31" t="n"/>
+      <c r="AL18" s="31" t="n"/>
+      <c r="AM18" s="31" t="n"/>
+      <c r="AN18" s="31" t="n"/>
+      <c r="AO18" s="31" t="n"/>
+      <c r="AP18" s="31" t="n"/>
+      <c r="AQ18" s="31" t="n"/>
+      <c r="AR18" s="31" t="n"/>
+      <c r="AS18" s="31" t="n"/>
+      <c r="AT18" s="31" t="n"/>
+      <c r="AU18" s="31" t="n"/>
+      <c r="AV18" s="31" t="n"/>
+      <c r="AW18" s="31" t="n"/>
+      <c r="AX18" s="31" t="n"/>
+      <c r="AY18" s="31" t="n"/>
+      <c r="AZ18" s="31" t="n"/>
+      <c r="BA18" s="31" t="n"/>
+      <c r="BB18" s="31" t="n"/>
+      <c r="BC18" s="31" t="n"/>
+      <c r="BD18" s="31" t="n"/>
+      <c r="BE18" s="31" t="n"/>
+      <c r="BF18" s="31" t="n"/>
+      <c r="BG18" s="31" t="n"/>
+      <c r="BH18" s="31" t="n"/>
+      <c r="BI18" s="31" t="n"/>
+      <c r="BJ18" s="31" t="n"/>
+      <c r="BK18" s="31" t="n"/>
+      <c r="BL18" s="31" t="n"/>
+      <c r="BM18" s="31" t="n"/>
+      <c r="BN18" s="31" t="n"/>
+      <c r="BO18" s="31" t="n"/>
+      <c r="BP18" s="31" t="n"/>
+      <c r="BQ18" s="31" t="n"/>
+      <c r="BR18" s="31" t="n"/>
+      <c r="BS18" s="31" t="n"/>
+      <c r="BT18" s="31" t="n"/>
+      <c r="BU18" s="31" t="n"/>
+      <c r="BV18" s="31" t="n"/>
+      <c r="BW18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　わたしは会社より＜羽島店舗運営業務＞に関して、　　　　年　　　月　　　日に</t>
+        </is>
+      </c>
+      <c r="AH19" s="37" t="n"/>
+      <c r="AI19" s="37" t="n"/>
+      <c r="AJ19" s="37" t="n"/>
+      <c r="AK19" s="31" t="n"/>
+      <c r="AL19" s="31" t="n"/>
+      <c r="AM19" s="31" t="n"/>
+      <c r="AN19" s="31" t="n"/>
+      <c r="AO19" s="37" t="n"/>
+      <c r="AP19" s="37" t="n"/>
+      <c r="AQ19" s="37" t="n"/>
+      <c r="AR19" s="37" t="n"/>
+      <c r="AS19" s="37" t="n"/>
+      <c r="AT19" s="37" t="n"/>
+      <c r="AU19" s="37" t="n"/>
+      <c r="AV19" s="37" t="n"/>
+      <c r="AW19" s="37" t="n"/>
+      <c r="AX19" s="37" t="n"/>
+      <c r="AY19" s="37" t="n"/>
+      <c r="AZ19" s="37" t="n"/>
+      <c r="BA19" s="37" t="n"/>
+      <c r="BB19" s="37" t="n"/>
+      <c r="BC19" s="37" t="n"/>
+      <c r="BD19" s="37" t="n"/>
+      <c r="BE19" s="37" t="n"/>
+      <c r="BF19" s="37" t="n"/>
+      <c r="BG19" s="37" t="n"/>
+      <c r="BH19" s="37" t="n"/>
+      <c r="BI19" s="37" t="n"/>
+      <c r="BJ19" s="37" t="n"/>
+      <c r="BK19" s="37" t="n"/>
+      <c r="BL19" s="37" t="n"/>
+      <c r="BM19" s="37" t="n"/>
+      <c r="BN19" s="37" t="n"/>
+      <c r="BO19" s="37" t="n"/>
+      <c r="BP19" s="37" t="n"/>
+      <c r="BQ19" s="37" t="n"/>
+      <c r="BR19" s="37" t="n"/>
+      <c r="BS19" s="37" t="n"/>
+      <c r="BT19" s="37" t="n"/>
+      <c r="BU19" s="37" t="n"/>
+      <c r="BV19" s="37" t="n"/>
+      <c r="BW19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="AH20" s="37" t="n"/>
+      <c r="AI20" s="37" t="n"/>
+      <c r="AJ20" s="37" t="n"/>
+      <c r="AK20" s="31" t="n"/>
+      <c r="AL20" s="31" t="n"/>
+      <c r="AM20" s="31" t="n"/>
+      <c r="AN20" s="31" t="n"/>
+      <c r="AO20" s="37" t="n"/>
+      <c r="AP20" s="37" t="n"/>
+      <c r="AQ20" s="37" t="n"/>
+      <c r="AR20" s="37" t="n"/>
+      <c r="AS20" s="37" t="n"/>
+      <c r="AT20" s="37" t="n"/>
+      <c r="AU20" s="37" t="n"/>
+      <c r="AV20" s="37" t="n"/>
+      <c r="AW20" s="37" t="n"/>
+      <c r="AX20" s="37" t="n"/>
+      <c r="AY20" s="37" t="n"/>
+      <c r="AZ20" s="37" t="n"/>
+      <c r="BA20" s="37" t="n"/>
+      <c r="BB20" s="37" t="n"/>
+      <c r="BC20" s="37" t="n"/>
+      <c r="BD20" s="37" t="n"/>
+      <c r="BE20" s="37" t="n"/>
+      <c r="BF20" s="37" t="n"/>
+      <c r="BG20" s="37" t="n"/>
+      <c r="BH20" s="37" t="n"/>
+      <c r="BI20" s="37" t="n"/>
+      <c r="BJ20" s="37" t="n"/>
+      <c r="BK20" s="37" t="n"/>
+      <c r="BL20" s="37" t="n"/>
+      <c r="BM20" s="37" t="n"/>
+      <c r="BN20" s="37" t="n"/>
+      <c r="BO20" s="37" t="n"/>
+      <c r="BP20" s="37" t="n"/>
+      <c r="BQ20" s="37" t="n"/>
+      <c r="BR20" s="37" t="n"/>
+      <c r="BS20" s="37" t="n"/>
+      <c r="BT20" s="37" t="n"/>
+      <c r="BU20" s="37" t="n"/>
+      <c r="BV20" s="37" t="n"/>
+      <c r="BW20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>下記の鍵を預託されました。</t>
+        </is>
+      </c>
+      <c r="AH21" s="37" t="n"/>
+      <c r="AI21" s="37" t="n"/>
+      <c r="AJ21" s="37" t="n"/>
+      <c r="AK21" s="31" t="n"/>
+      <c r="AL21" s="31" t="n"/>
+      <c r="AM21" s="31" t="n"/>
+      <c r="AN21" s="31" t="n"/>
+      <c r="AO21" s="37" t="n"/>
+      <c r="AP21" s="37" t="n"/>
+      <c r="AQ21" s="37" t="n"/>
+      <c r="AR21" s="37" t="n"/>
+      <c r="AS21" s="37" t="n"/>
+      <c r="AT21" s="37" t="n"/>
+      <c r="AU21" s="37" t="n"/>
+      <c r="AV21" s="37" t="n"/>
+      <c r="AW21" s="37" t="n"/>
+      <c r="AX21" s="37" t="n"/>
+      <c r="AY21" s="37" t="n"/>
+      <c r="AZ21" s="37" t="n"/>
+      <c r="BA21" s="37" t="n"/>
+      <c r="BB21" s="37" t="n"/>
+      <c r="BC21" s="37" t="n"/>
+      <c r="BD21" s="37" t="n"/>
+      <c r="BE21" s="37" t="n"/>
+      <c r="BF21" s="37" t="n"/>
+      <c r="BG21" s="37" t="n"/>
+      <c r="BH21" s="37" t="n"/>
+      <c r="BI21" s="37" t="n"/>
+      <c r="BJ21" s="37" t="n"/>
+      <c r="BK21" s="37" t="n"/>
+      <c r="BL21" s="37" t="n"/>
+      <c r="BM21" s="37" t="n"/>
+      <c r="BN21" s="37" t="n"/>
+      <c r="BO21" s="37" t="n"/>
+      <c r="BP21" s="37" t="n"/>
+      <c r="BQ21" s="37" t="n"/>
+      <c r="BR21" s="37" t="n"/>
+      <c r="BS21" s="37" t="n"/>
+      <c r="BT21" s="37" t="n"/>
+      <c r="BU21" s="37" t="n"/>
+      <c r="BV21" s="37" t="n"/>
+      <c r="BW21" s="37" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="AH22" s="37" t="n"/>
+      <c r="AI22" s="37" t="n"/>
+      <c r="AJ22" s="37" t="n"/>
+      <c r="AK22" s="31" t="n"/>
+      <c r="AL22" s="31" t="n"/>
+      <c r="AM22" s="31" t="n"/>
+      <c r="AN22" s="31" t="n"/>
+      <c r="AO22" s="37" t="n"/>
+      <c r="AP22" s="37" t="n"/>
+      <c r="AQ22" s="37" t="n"/>
+      <c r="AR22" s="37" t="n"/>
+      <c r="AS22" s="37" t="n"/>
+      <c r="AT22" s="37" t="n"/>
+      <c r="AU22" s="37" t="n"/>
+      <c r="AV22" s="37" t="n"/>
+      <c r="AW22" s="37" t="n"/>
+      <c r="AX22" s="37" t="n"/>
+      <c r="AY22" s="37" t="n"/>
+      <c r="AZ22" s="37" t="n"/>
+      <c r="BA22" s="37" t="n"/>
+      <c r="BB22" s="37" t="n"/>
+      <c r="BC22" s="37" t="n"/>
+      <c r="BD22" s="37" t="n"/>
+      <c r="BE22" s="37" t="n"/>
+      <c r="BF22" s="37" t="n"/>
+      <c r="BG22" s="37" t="n"/>
+      <c r="BH22" s="37" t="n"/>
+      <c r="BI22" s="37" t="n"/>
+      <c r="BJ22" s="37" t="n"/>
+      <c r="BK22" s="37" t="n"/>
+      <c r="BL22" s="37" t="n"/>
+      <c r="BM22" s="37" t="n"/>
+      <c r="BN22" s="37" t="n"/>
+      <c r="BO22" s="37" t="n"/>
+      <c r="BP22" s="37" t="n"/>
+      <c r="BQ22" s="37" t="n"/>
+      <c r="BR22" s="37" t="n"/>
+      <c r="BS22" s="37" t="n"/>
+      <c r="BT22" s="37" t="n"/>
+      <c r="BU22" s="37" t="n"/>
+      <c r="BV22" s="37" t="n"/>
+      <c r="BW22" s="37" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　これらの鍵の保管には細心の注意を払うとともに、店舗の運営管理のために</t>
+        </is>
+      </c>
+      <c r="AH23" s="37" t="n"/>
+      <c r="AI23" s="37" t="n"/>
+      <c r="AJ23" s="37" t="n"/>
+      <c r="AK23" s="31" t="n"/>
+      <c r="AL23" s="31" t="n"/>
+      <c r="AM23" s="31" t="n"/>
+      <c r="AN23" s="31" t="n"/>
+      <c r="AO23" s="37" t="n"/>
+      <c r="AP23" s="37" t="n"/>
+      <c r="AQ23" s="37" t="n"/>
+      <c r="AR23" s="37" t="n"/>
+      <c r="AS23" s="37" t="n"/>
+      <c r="AT23" s="37" t="n"/>
+      <c r="AU23" s="37" t="n"/>
+      <c r="AV23" s="37" t="n"/>
+      <c r="AW23" s="37" t="n"/>
+      <c r="AX23" s="37" t="n"/>
+      <c r="AY23" s="37" t="n"/>
+      <c r="AZ23" s="37" t="n"/>
+      <c r="BA23" s="37" t="n"/>
+      <c r="BB23" s="37" t="n"/>
+      <c r="BC23" s="37" t="n"/>
+      <c r="BD23" s="37" t="n"/>
+      <c r="BE23" s="37" t="n"/>
+      <c r="BF23" s="37" t="n"/>
+      <c r="BG23" s="37" t="n"/>
+      <c r="BH23" s="37" t="n"/>
+      <c r="BI23" s="37" t="n"/>
+      <c r="BJ23" s="37" t="n"/>
+      <c r="BK23" s="37" t="n"/>
+      <c r="BL23" s="37" t="n"/>
+      <c r="BM23" s="37" t="n"/>
+      <c r="BN23" s="37" t="n"/>
+      <c r="BO23" s="37" t="n"/>
+      <c r="BP23" s="37" t="n"/>
+      <c r="BQ23" s="37" t="n"/>
+      <c r="BR23" s="37" t="n"/>
+      <c r="BS23" s="37" t="n"/>
+      <c r="BT23" s="37" t="n"/>
+      <c r="BU23" s="37" t="n"/>
+      <c r="BV23" s="37" t="n"/>
+      <c r="BW23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="AH24" s="37" t="n"/>
+      <c r="AI24" s="37" t="n"/>
+      <c r="AJ24" s="37" t="n"/>
+      <c r="AK24" s="31" t="n"/>
+      <c r="AL24" s="31" t="n"/>
+      <c r="AM24" s="31" t="n"/>
+      <c r="AN24" s="31" t="n"/>
+      <c r="AO24" s="37" t="n"/>
+      <c r="AP24" s="37" t="n"/>
+      <c r="AQ24" s="37" t="n"/>
+      <c r="AR24" s="37" t="n"/>
+      <c r="AS24" s="37" t="n"/>
+      <c r="AT24" s="37" t="n"/>
+      <c r="AU24" s="37" t="n"/>
+      <c r="AV24" s="37" t="n"/>
+      <c r="AW24" s="37" t="n"/>
+      <c r="AX24" s="37" t="n"/>
+      <c r="AY24" s="37" t="n"/>
+      <c r="AZ24" s="37" t="n"/>
+      <c r="BA24" s="37" t="n"/>
+      <c r="BB24" s="37" t="n"/>
+      <c r="BC24" s="37" t="n"/>
+      <c r="BD24" s="37" t="n"/>
+      <c r="BE24" s="37" t="n"/>
+      <c r="BF24" s="37" t="n"/>
+      <c r="BG24" s="37" t="n"/>
+      <c r="BH24" s="37" t="n"/>
+      <c r="BI24" s="37" t="n"/>
+      <c r="BJ24" s="37" t="n"/>
+      <c r="BK24" s="37" t="n"/>
+      <c r="BL24" s="37" t="n"/>
+      <c r="BM24" s="37" t="n"/>
+      <c r="BN24" s="37" t="n"/>
+      <c r="BO24" s="37" t="n"/>
+      <c r="BP24" s="37" t="n"/>
+      <c r="BQ24" s="37" t="n"/>
+      <c r="BR24" s="37" t="n"/>
+      <c r="BS24" s="37" t="n"/>
+      <c r="BT24" s="37" t="n"/>
+      <c r="BU24" s="37" t="n"/>
+      <c r="BV24" s="37" t="n"/>
+      <c r="BW24" s="37" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="38" t="inlineStr">
+        <is>
+          <t>適切に使用し、目的外には使用いたしません。</t>
+        </is>
+      </c>
+      <c r="AH25" s="37" t="n"/>
+      <c r="AI25" s="37" t="n"/>
+      <c r="AJ25" s="37" t="n"/>
+      <c r="AK25" s="31" t="n"/>
+      <c r="AL25" s="31" t="n"/>
+      <c r="AM25" s="31" t="n"/>
+      <c r="AN25" s="31" t="n"/>
+      <c r="AO25" s="37" t="n"/>
+      <c r="AP25" s="37" t="n"/>
+      <c r="AQ25" s="37" t="n"/>
+      <c r="AR25" s="37" t="n"/>
+      <c r="AS25" s="37" t="n"/>
+      <c r="AT25" s="37" t="n"/>
+      <c r="AU25" s="37" t="n"/>
+      <c r="AV25" s="37" t="n"/>
+      <c r="AW25" s="37" t="n"/>
+      <c r="AX25" s="37" t="n"/>
+      <c r="AY25" s="37" t="n"/>
+      <c r="AZ25" s="37" t="n"/>
+      <c r="BA25" s="37" t="n"/>
+      <c r="BB25" s="37" t="n"/>
+      <c r="BC25" s="37" t="n"/>
+      <c r="BD25" s="37" t="n"/>
+      <c r="BE25" s="37" t="n"/>
+      <c r="BF25" s="37" t="n"/>
+      <c r="BG25" s="37" t="n"/>
+      <c r="BH25" s="37" t="n"/>
+      <c r="BI25" s="37" t="n"/>
+      <c r="BJ25" s="37" t="n"/>
+      <c r="BK25" s="37" t="n"/>
+      <c r="BL25" s="37" t="n"/>
+      <c r="BM25" s="37" t="n"/>
+      <c r="BN25" s="37" t="n"/>
+      <c r="BO25" s="37" t="n"/>
+      <c r="BP25" s="37" t="n"/>
+      <c r="BQ25" s="37" t="n"/>
+      <c r="BR25" s="37" t="n"/>
+      <c r="BS25" s="37" t="n"/>
+      <c r="BT25" s="37" t="n"/>
+      <c r="BU25" s="37" t="n"/>
+      <c r="BV25" s="37" t="n"/>
+      <c r="BW25" s="37" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="AH26" s="37" t="n"/>
+      <c r="AI26" s="37" t="n"/>
+      <c r="AJ26" s="37" t="n"/>
+      <c r="AK26" s="31" t="n"/>
+      <c r="AL26" s="31" t="n"/>
+      <c r="AM26" s="31" t="n"/>
+      <c r="AN26" s="31" t="n"/>
+      <c r="AO26" s="37" t="n"/>
+      <c r="AP26" s="37" t="n"/>
+      <c r="AQ26" s="37" t="n"/>
+      <c r="AR26" s="37" t="n"/>
+      <c r="AS26" s="37" t="n"/>
+      <c r="AT26" s="37" t="n"/>
+      <c r="AU26" s="37" t="n"/>
+      <c r="AV26" s="37" t="n"/>
+      <c r="AW26" s="37" t="n"/>
+      <c r="AX26" s="37" t="n"/>
+      <c r="AY26" s="37" t="n"/>
+      <c r="AZ26" s="37" t="n"/>
+      <c r="BA26" s="37" t="n"/>
+      <c r="BB26" s="37" t="n"/>
+      <c r="BC26" s="37" t="n"/>
+      <c r="BD26" s="37" t="n"/>
+      <c r="BE26" s="37" t="n"/>
+      <c r="BF26" s="37" t="n"/>
+      <c r="BG26" s="37" t="n"/>
+      <c r="BH26" s="37" t="n"/>
+      <c r="BI26" s="37" t="n"/>
+      <c r="BJ26" s="37" t="n"/>
+      <c r="BK26" s="37" t="n"/>
+      <c r="BL26" s="37" t="n"/>
+      <c r="BM26" s="37" t="n"/>
+      <c r="BN26" s="37" t="n"/>
+      <c r="BO26" s="37" t="n"/>
+      <c r="BP26" s="37" t="n"/>
+      <c r="BQ26" s="37" t="n"/>
+      <c r="BR26" s="37" t="n"/>
+      <c r="BS26" s="37" t="n"/>
+      <c r="BT26" s="37" t="n"/>
+      <c r="BU26" s="37" t="n"/>
+      <c r="BV26" s="37" t="n"/>
+      <c r="BW26" s="37" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="39" t="inlineStr">
+        <is>
+          <t>また、施錠忘れ又は紛失により被害が生じた場合は、故意又は重大な過失があるときに限り、会社に生じた現実の損害の範囲で、信義則上相当な限度において賠償します。</t>
+        </is>
+      </c>
+      <c r="AH27" s="37" t="n"/>
+      <c r="AI27" s="37" t="n"/>
+      <c r="AJ27" s="37" t="n"/>
+      <c r="AK27" s="31" t="n"/>
+      <c r="AL27" s="31" t="n"/>
+      <c r="AM27" s="31" t="n"/>
+      <c r="AN27" s="31" t="n"/>
+      <c r="AO27" s="37" t="n"/>
+      <c r="AP27" s="37" t="n"/>
+      <c r="AQ27" s="37" t="n"/>
+      <c r="AR27" s="37" t="n"/>
+      <c r="AS27" s="37" t="n"/>
+      <c r="AT27" s="37" t="n"/>
+      <c r="AU27" s="37" t="n"/>
+      <c r="AV27" s="37" t="n"/>
+      <c r="AW27" s="37" t="n"/>
+      <c r="AX27" s="37" t="n"/>
+      <c r="AY27" s="37" t="n"/>
+      <c r="AZ27" s="37" t="n"/>
+      <c r="BA27" s="37" t="n"/>
+      <c r="BB27" s="37" t="n"/>
+      <c r="BC27" s="37" t="n"/>
+      <c r="BD27" s="37" t="n"/>
+      <c r="BE27" s="37" t="n"/>
+      <c r="BF27" s="37" t="n"/>
+      <c r="BG27" s="37" t="n"/>
+      <c r="BH27" s="37" t="n"/>
+      <c r="BI27" s="37" t="n"/>
+      <c r="BJ27" s="37" t="n"/>
+      <c r="BK27" s="37" t="n"/>
+      <c r="BL27" s="37" t="n"/>
+      <c r="BM27" s="37" t="n"/>
+      <c r="BN27" s="37" t="n"/>
+      <c r="BO27" s="37" t="n"/>
+      <c r="BP27" s="37" t="n"/>
+      <c r="BQ27" s="37" t="n"/>
+      <c r="BR27" s="37" t="n"/>
+      <c r="BS27" s="37" t="n"/>
+      <c r="BT27" s="37" t="n"/>
+      <c r="BU27" s="37" t="n"/>
+      <c r="BV27" s="37" t="n"/>
+      <c r="BW27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="AH28" s="37" t="n"/>
+      <c r="AI28" s="37" t="n"/>
+      <c r="AJ28" s="37" t="n"/>
+      <c r="AK28" s="31" t="n"/>
+      <c r="AL28" s="31" t="n"/>
+      <c r="AM28" s="31" t="n"/>
+      <c r="AN28" s="31" t="n"/>
+      <c r="AO28" s="37" t="n"/>
+      <c r="AP28" s="37" t="n"/>
+      <c r="AQ28" s="37" t="n"/>
+      <c r="AR28" s="37" t="n"/>
+      <c r="AS28" s="37" t="n"/>
+      <c r="AT28" s="37" t="n"/>
+      <c r="AU28" s="37" t="n"/>
+      <c r="AV28" s="37" t="n"/>
+      <c r="AW28" s="37" t="n"/>
+      <c r="AX28" s="37" t="n"/>
+      <c r="AY28" s="37" t="n"/>
+      <c r="AZ28" s="37" t="n"/>
+      <c r="BA28" s="37" t="n"/>
+      <c r="BB28" s="37" t="n"/>
+      <c r="BC28" s="37" t="n"/>
+      <c r="BD28" s="37" t="n"/>
+      <c r="BE28" s="37" t="n"/>
+      <c r="BF28" s="37" t="n"/>
+      <c r="BG28" s="37" t="n"/>
+      <c r="BH28" s="37" t="n"/>
+      <c r="BI28" s="37" t="n"/>
+      <c r="BJ28" s="37" t="n"/>
+      <c r="BK28" s="37" t="n"/>
+      <c r="BL28" s="37" t="n"/>
+      <c r="BM28" s="37" t="n"/>
+      <c r="BN28" s="37" t="n"/>
+      <c r="BO28" s="37" t="n"/>
+      <c r="BP28" s="37" t="n"/>
+      <c r="BQ28" s="37" t="n"/>
+      <c r="BR28" s="37" t="n"/>
+      <c r="BS28" s="37" t="n"/>
+      <c r="BT28" s="37" t="n"/>
+      <c r="BU28" s="37" t="n"/>
+      <c r="BV28" s="37" t="n"/>
+      <c r="BW28" s="37" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="38" t="inlineStr">
+        <is>
+          <t>わたしが＜羽島店舗運営業務＞から外れた時、あるいは会社により請求があ</t>
+        </is>
+      </c>
+      <c r="AH29" s="37" t="n"/>
+      <c r="AI29" s="37" t="n"/>
+      <c r="AJ29" s="37" t="n"/>
+      <c r="AK29" s="31" t="n"/>
+      <c r="AL29" s="31" t="n"/>
+      <c r="AM29" s="31" t="n"/>
+      <c r="AN29" s="31" t="n"/>
+      <c r="AO29" s="37" t="n"/>
+      <c r="AP29" s="37" t="n"/>
+      <c r="AQ29" s="37" t="n"/>
+      <c r="AR29" s="37" t="n"/>
+      <c r="AS29" s="37" t="n"/>
+      <c r="AT29" s="37" t="n"/>
+      <c r="AU29" s="37" t="n"/>
+      <c r="AV29" s="37" t="n"/>
+      <c r="AW29" s="37" t="n"/>
+      <c r="AX29" s="37" t="n"/>
+      <c r="AY29" s="37" t="n"/>
+      <c r="AZ29" s="37" t="n"/>
+      <c r="BA29" s="37" t="n"/>
+      <c r="BB29" s="37" t="n"/>
+      <c r="BC29" s="37" t="n"/>
+      <c r="BD29" s="37" t="n"/>
+      <c r="BE29" s="37" t="n"/>
+      <c r="BF29" s="37" t="n"/>
+      <c r="BG29" s="37" t="n"/>
+      <c r="BH29" s="37" t="n"/>
+      <c r="BI29" s="37" t="n"/>
+      <c r="BJ29" s="37" t="n"/>
+      <c r="BK29" s="37" t="n"/>
+      <c r="BL29" s="37" t="n"/>
+      <c r="BM29" s="37" t="n"/>
+      <c r="BN29" s="37" t="n"/>
+      <c r="BO29" s="37" t="n"/>
+      <c r="BP29" s="37" t="n"/>
+      <c r="BQ29" s="37" t="n"/>
+      <c r="BR29" s="37" t="n"/>
+      <c r="BS29" s="37" t="n"/>
+      <c r="BT29" s="37" t="n"/>
+      <c r="BU29" s="37" t="n"/>
+      <c r="BV29" s="37" t="n"/>
+      <c r="BW29" s="37" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="31" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="AH30" s="37" t="n"/>
+      <c r="AI30" s="37" t="n"/>
+      <c r="AJ30" s="37" t="n"/>
+      <c r="AK30" s="31" t="n"/>
+      <c r="AL30" s="31" t="n"/>
+      <c r="AM30" s="31" t="n"/>
+      <c r="AN30" s="31" t="n"/>
+      <c r="AO30" s="37" t="n"/>
+      <c r="AP30" s="37" t="n"/>
+      <c r="AQ30" s="37" t="n"/>
+      <c r="AR30" s="37" t="n"/>
+      <c r="AS30" s="37" t="n"/>
+      <c r="AT30" s="37" t="n"/>
+      <c r="AU30" s="37" t="n"/>
+      <c r="AV30" s="37" t="n"/>
+      <c r="AW30" s="37" t="n"/>
+      <c r="AX30" s="37" t="n"/>
+      <c r="AY30" s="37" t="n"/>
+      <c r="AZ30" s="37" t="n"/>
+      <c r="BA30" s="37" t="n"/>
+      <c r="BB30" s="37" t="n"/>
+      <c r="BC30" s="37" t="n"/>
+      <c r="BD30" s="37" t="n"/>
+      <c r="BE30" s="37" t="n"/>
+      <c r="BF30" s="37" t="n"/>
+      <c r="BG30" s="37" t="n"/>
+      <c r="BH30" s="37" t="n"/>
+      <c r="BI30" s="37" t="n"/>
+      <c r="BJ30" s="37" t="n"/>
+      <c r="BK30" s="37" t="n"/>
+      <c r="BL30" s="37" t="n"/>
+      <c r="BM30" s="37" t="n"/>
+      <c r="BN30" s="37" t="n"/>
+      <c r="BO30" s="37" t="n"/>
+      <c r="BP30" s="37" t="n"/>
+      <c r="BQ30" s="37" t="n"/>
+      <c r="BR30" s="37" t="n"/>
+      <c r="BS30" s="37" t="n"/>
+      <c r="BT30" s="37" t="n"/>
+      <c r="BU30" s="37" t="n"/>
+      <c r="BV30" s="37" t="n"/>
+      <c r="BW30" s="37" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="38" t="inlineStr">
+        <is>
+          <t>ったときには速やかに返還いたします。</t>
+        </is>
+      </c>
+      <c r="AH31" s="37" t="n"/>
+      <c r="AI31" s="37" t="n"/>
+      <c r="AJ31" s="37" t="n"/>
+      <c r="AK31" s="31" t="n"/>
+      <c r="AL31" s="31" t="n"/>
+      <c r="AM31" s="31" t="n"/>
+      <c r="AN31" s="31" t="n"/>
+      <c r="AO31" s="37" t="n"/>
+      <c r="AP31" s="37" t="n"/>
+      <c r="AQ31" s="37" t="n"/>
+      <c r="AR31" s="37" t="n"/>
+      <c r="AS31" s="37" t="n"/>
+      <c r="AT31" s="37" t="n"/>
+      <c r="AU31" s="37" t="n"/>
+      <c r="AV31" s="37" t="n"/>
+      <c r="AW31" s="37" t="n"/>
+      <c r="AX31" s="37" t="n"/>
+      <c r="AY31" s="37" t="n"/>
+      <c r="AZ31" s="37" t="n"/>
+      <c r="BA31" s="37" t="n"/>
+      <c r="BB31" s="37" t="n"/>
+      <c r="BC31" s="37" t="n"/>
+      <c r="BD31" s="37" t="n"/>
+      <c r="BE31" s="37" t="n"/>
+      <c r="BF31" s="37" t="n"/>
+      <c r="BG31" s="37" t="n"/>
+      <c r="BH31" s="37" t="n"/>
+      <c r="BI31" s="37" t="n"/>
+      <c r="BJ31" s="37" t="n"/>
+      <c r="BK31" s="37" t="n"/>
+      <c r="BL31" s="37" t="n"/>
+      <c r="BM31" s="37" t="n"/>
+      <c r="BN31" s="37" t="n"/>
+      <c r="BO31" s="37" t="n"/>
+      <c r="BP31" s="37" t="n"/>
+      <c r="BQ31" s="37" t="n"/>
+      <c r="BR31" s="37" t="n"/>
+      <c r="BS31" s="37" t="n"/>
+      <c r="BT31" s="37" t="n"/>
+      <c r="BU31" s="37" t="n"/>
+      <c r="BV31" s="37" t="n"/>
+      <c r="BW31" s="37" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="AH32" s="37" t="n"/>
+      <c r="AI32" s="37" t="n"/>
+      <c r="AJ32" s="37" t="n"/>
+      <c r="AK32" s="31" t="n"/>
+      <c r="AL32" s="31" t="n"/>
+      <c r="AM32" s="31" t="n"/>
+      <c r="AN32" s="31" t="n"/>
+      <c r="AO32" s="37" t="n"/>
+      <c r="AP32" s="37" t="n"/>
+      <c r="AQ32" s="37" t="n"/>
+      <c r="AR32" s="37" t="n"/>
+      <c r="AS32" s="37" t="n"/>
+      <c r="AT32" s="37" t="n"/>
+      <c r="AU32" s="37" t="n"/>
+      <c r="AV32" s="37" t="n"/>
+      <c r="AW32" s="37" t="n"/>
+      <c r="AX32" s="37" t="n"/>
+      <c r="AY32" s="37" t="n"/>
+      <c r="AZ32" s="37" t="n"/>
+      <c r="BA32" s="37" t="n"/>
+      <c r="BB32" s="37" t="n"/>
+      <c r="BC32" s="37" t="n"/>
+      <c r="BD32" s="37" t="n"/>
+      <c r="BE32" s="37" t="n"/>
+      <c r="BF32" s="37" t="n"/>
+      <c r="BG32" s="37" t="n"/>
+      <c r="BH32" s="37" t="n"/>
+      <c r="BI32" s="37" t="n"/>
+      <c r="BJ32" s="37" t="n"/>
+      <c r="BK32" s="37" t="n"/>
+      <c r="BL32" s="37" t="n"/>
+      <c r="BM32" s="37" t="n"/>
+      <c r="BN32" s="37" t="n"/>
+      <c r="BO32" s="37" t="n"/>
+      <c r="BP32" s="37" t="n"/>
+      <c r="BQ32" s="37" t="n"/>
+      <c r="BR32" s="37" t="n"/>
+      <c r="BS32" s="37" t="n"/>
+      <c r="BT32" s="37" t="n"/>
+      <c r="BU32" s="37" t="n"/>
+      <c r="BV32" s="37" t="n"/>
+      <c r="BW32" s="37" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="31" t="n"/>
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="AH33" s="37" t="n"/>
+      <c r="AI33" s="37" t="n"/>
+      <c r="AJ33" s="37" t="n"/>
+      <c r="AK33" s="31" t="n"/>
+      <c r="AL33" s="31" t="n"/>
+      <c r="AM33" s="31" t="n"/>
+      <c r="AN33" s="31" t="n"/>
+      <c r="AO33" s="37" t="n"/>
+      <c r="AP33" s="37" t="n"/>
+      <c r="AQ33" s="37" t="n"/>
+      <c r="AR33" s="37" t="n"/>
+      <c r="AS33" s="37" t="n"/>
+      <c r="AT33" s="37" t="n"/>
+      <c r="AU33" s="37" t="n"/>
+      <c r="AV33" s="37" t="n"/>
+      <c r="AW33" s="37" t="n"/>
+      <c r="AX33" s="37" t="n"/>
+      <c r="AY33" s="37" t="n"/>
+      <c r="AZ33" s="37" t="n"/>
+      <c r="BA33" s="37" t="n"/>
+      <c r="BB33" s="37" t="n"/>
+      <c r="BC33" s="37" t="n"/>
+      <c r="BD33" s="37" t="n"/>
+      <c r="BE33" s="37" t="n"/>
+      <c r="BF33" s="37" t="n"/>
+      <c r="BG33" s="37" t="n"/>
+      <c r="BH33" s="37" t="n"/>
+      <c r="BI33" s="37" t="n"/>
+      <c r="BJ33" s="37" t="n"/>
+      <c r="BK33" s="37" t="n"/>
+      <c r="BL33" s="37" t="n"/>
+      <c r="BM33" s="37" t="n"/>
+      <c r="BN33" s="37" t="n"/>
+      <c r="BO33" s="37" t="n"/>
+      <c r="BP33" s="37" t="n"/>
+      <c r="BQ33" s="37" t="n"/>
+      <c r="BR33" s="37" t="n"/>
+      <c r="BS33" s="37" t="n"/>
+      <c r="BT33" s="37" t="n"/>
+      <c r="BU33" s="37" t="n"/>
+      <c r="BV33" s="37" t="n"/>
+      <c r="BW33" s="37" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="31" t="n"/>
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="AH34" s="37" t="n"/>
+      <c r="AI34" s="37" t="n"/>
+      <c r="AJ34" s="37" t="n"/>
+      <c r="AK34" s="31" t="n"/>
+      <c r="AL34" s="31" t="n"/>
+      <c r="AM34" s="31" t="n"/>
+      <c r="AN34" s="31" t="n"/>
+      <c r="AO34" s="37" t="n"/>
+      <c r="AP34" s="37" t="n"/>
+      <c r="AQ34" s="37" t="n"/>
+      <c r="AR34" s="37" t="n"/>
+      <c r="AS34" s="37" t="n"/>
+      <c r="AT34" s="37" t="n"/>
+      <c r="AU34" s="37" t="n"/>
+      <c r="AV34" s="37" t="n"/>
+      <c r="AW34" s="37" t="n"/>
+      <c r="AX34" s="37" t="n"/>
+      <c r="AY34" s="37" t="n"/>
+      <c r="AZ34" s="37" t="n"/>
+      <c r="BA34" s="37" t="n"/>
+      <c r="BB34" s="37" t="n"/>
+      <c r="BC34" s="37" t="n"/>
+      <c r="BD34" s="37" t="n"/>
+      <c r="BE34" s="37" t="n"/>
+      <c r="BF34" s="37" t="n"/>
+      <c r="BG34" s="37" t="n"/>
+      <c r="BH34" s="37" t="n"/>
+      <c r="BI34" s="37" t="n"/>
+      <c r="BJ34" s="37" t="n"/>
+      <c r="BK34" s="37" t="n"/>
+      <c r="BL34" s="37" t="n"/>
+      <c r="BM34" s="37" t="n"/>
+      <c r="BN34" s="37" t="n"/>
+      <c r="BO34" s="37" t="n"/>
+      <c r="BP34" s="37" t="n"/>
+      <c r="BQ34" s="37" t="n"/>
+      <c r="BR34" s="37" t="n"/>
+      <c r="BS34" s="37" t="n"/>
+      <c r="BT34" s="37" t="n"/>
+      <c r="BU34" s="37" t="n"/>
+      <c r="BV34" s="37" t="n"/>
+      <c r="BW34" s="37" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="38" t="inlineStr">
+        <is>
+          <t>※紛失した場合はカード・鍵は全て取替えなければなりません。</t>
+        </is>
+      </c>
+      <c r="AH35" s="37" t="n"/>
+      <c r="AI35" s="37" t="n"/>
+      <c r="AJ35" s="37" t="n"/>
+      <c r="AK35" s="31" t="n"/>
+      <c r="AL35" s="31" t="n"/>
+      <c r="AM35" s="31" t="n"/>
+      <c r="AN35" s="31" t="n"/>
+      <c r="AO35" s="37" t="n"/>
+      <c r="AP35" s="37" t="n"/>
+      <c r="AQ35" s="37" t="n"/>
+      <c r="AR35" s="37" t="n"/>
+      <c r="AS35" s="37" t="n"/>
+      <c r="AT35" s="37" t="n"/>
+      <c r="AU35" s="37" t="n"/>
+      <c r="AV35" s="37" t="n"/>
+      <c r="AW35" s="37" t="n"/>
+      <c r="AX35" s="37" t="n"/>
+      <c r="AY35" s="37" t="n"/>
+      <c r="AZ35" s="37" t="n"/>
+      <c r="BA35" s="37" t="n"/>
+      <c r="BB35" s="37" t="n"/>
+      <c r="BC35" s="37" t="n"/>
+      <c r="BD35" s="37" t="n"/>
+      <c r="BE35" s="37" t="n"/>
+      <c r="BF35" s="37" t="n"/>
+      <c r="BG35" s="37" t="n"/>
+      <c r="BH35" s="37" t="n"/>
+      <c r="BI35" s="37" t="n"/>
+      <c r="BJ35" s="37" t="n"/>
+      <c r="BK35" s="37" t="n"/>
+      <c r="BL35" s="37" t="n"/>
+      <c r="BM35" s="37" t="n"/>
+      <c r="BN35" s="37" t="n"/>
+      <c r="BO35" s="37" t="n"/>
+      <c r="BP35" s="37" t="n"/>
+      <c r="BQ35" s="37" t="n"/>
+      <c r="BR35" s="37" t="n"/>
+      <c r="BS35" s="37" t="n"/>
+      <c r="BT35" s="37" t="n"/>
+      <c r="BU35" s="37" t="n"/>
+      <c r="BV35" s="37" t="n"/>
+      <c r="BW35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="31" t="n"/>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="37" t="n"/>
+      <c r="AH36" s="37" t="n"/>
+      <c r="AI36" s="37" t="n"/>
+      <c r="AJ36" s="37" t="n"/>
+      <c r="AK36" s="31" t="n"/>
+      <c r="AL36" s="31" t="n"/>
+      <c r="AM36" s="31" t="n"/>
+      <c r="AN36" s="31" t="n"/>
+      <c r="AO36" s="37" t="n"/>
+      <c r="AP36" s="37" t="n"/>
+      <c r="AQ36" s="37" t="n"/>
+      <c r="AR36" s="37" t="n"/>
+      <c r="AS36" s="37" t="n"/>
+      <c r="AT36" s="37" t="n"/>
+      <c r="AU36" s="37" t="n"/>
+      <c r="AV36" s="37" t="n"/>
+      <c r="AW36" s="37" t="n"/>
+      <c r="AX36" s="37" t="n"/>
+      <c r="AY36" s="37" t="n"/>
+      <c r="AZ36" s="37" t="n"/>
+      <c r="BA36" s="37" t="n"/>
+      <c r="BB36" s="37" t="n"/>
+      <c r="BC36" s="37" t="n"/>
+      <c r="BD36" s="37" t="n"/>
+      <c r="BE36" s="37" t="n"/>
+      <c r="BF36" s="37" t="n"/>
+      <c r="BG36" s="37" t="n"/>
+      <c r="BH36" s="37" t="n"/>
+      <c r="BI36" s="37" t="n"/>
+      <c r="BJ36" s="37" t="n"/>
+      <c r="BK36" s="37" t="n"/>
+      <c r="BL36" s="37" t="n"/>
+      <c r="BM36" s="37" t="n"/>
+      <c r="BN36" s="37" t="n"/>
+      <c r="BO36" s="37" t="n"/>
+      <c r="BP36" s="37" t="n"/>
+      <c r="BQ36" s="37" t="n"/>
+      <c r="BR36" s="37" t="n"/>
+      <c r="BS36" s="37" t="n"/>
+      <c r="BT36" s="37" t="n"/>
+      <c r="BU36" s="37" t="n"/>
+      <c r="BV36" s="37" t="n"/>
+      <c r="BW36" s="37" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="31" t="n"/>
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="37" t="n"/>
+      <c r="E37" s="38" t="inlineStr">
+        <is>
+          <t>管理は厳重にする事。</t>
+        </is>
+      </c>
+      <c r="AH37" s="37" t="n"/>
+      <c r="AI37" s="37" t="n"/>
+      <c r="AJ37" s="37" t="n"/>
+      <c r="AK37" s="31" t="n"/>
+      <c r="AL37" s="31" t="n"/>
+      <c r="AM37" s="31" t="n"/>
+      <c r="AN37" s="31" t="n"/>
+      <c r="AO37" s="37" t="n"/>
+      <c r="AP37" s="37" t="n"/>
+      <c r="AQ37" s="37" t="n"/>
+      <c r="AR37" s="37" t="n"/>
+      <c r="AS37" s="37" t="n"/>
+      <c r="AT37" s="37" t="n"/>
+      <c r="AU37" s="37" t="n"/>
+      <c r="AV37" s="37" t="n"/>
+      <c r="AW37" s="37" t="n"/>
+      <c r="AX37" s="37" t="n"/>
+      <c r="AY37" s="37" t="n"/>
+      <c r="AZ37" s="37" t="n"/>
+      <c r="BA37" s="37" t="n"/>
+      <c r="BB37" s="37" t="n"/>
+      <c r="BC37" s="37" t="n"/>
+      <c r="BD37" s="37" t="n"/>
+      <c r="BE37" s="37" t="n"/>
+      <c r="BF37" s="37" t="n"/>
+      <c r="BG37" s="37" t="n"/>
+      <c r="BH37" s="37" t="n"/>
+      <c r="BI37" s="37" t="n"/>
+      <c r="BJ37" s="37" t="n"/>
+      <c r="BK37" s="37" t="n"/>
+      <c r="BL37" s="37" t="n"/>
+      <c r="BM37" s="37" t="n"/>
+      <c r="BN37" s="37" t="n"/>
+      <c r="BO37" s="37" t="n"/>
+      <c r="BP37" s="37" t="n"/>
+      <c r="BQ37" s="37" t="n"/>
+      <c r="BR37" s="37" t="n"/>
+      <c r="BS37" s="37" t="n"/>
+      <c r="BT37" s="37" t="n"/>
+      <c r="BU37" s="37" t="n"/>
+      <c r="BV37" s="37" t="n"/>
+      <c r="BW37" s="37" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="31" t="n"/>
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="37" t="n"/>
+      <c r="AH38" s="37" t="n"/>
+      <c r="AI38" s="37" t="n"/>
+      <c r="AJ38" s="37" t="n"/>
+      <c r="AK38" s="31" t="n"/>
+      <c r="AL38" s="31" t="n"/>
+      <c r="AM38" s="31" t="n"/>
+      <c r="AN38" s="31" t="n"/>
+      <c r="AO38" s="37" t="n"/>
+      <c r="AP38" s="37" t="n"/>
+      <c r="AQ38" s="37" t="n"/>
+      <c r="AR38" s="37" t="n"/>
+      <c r="AS38" s="37" t="n"/>
+      <c r="AT38" s="37" t="n"/>
+      <c r="AU38" s="37" t="n"/>
+      <c r="AV38" s="37" t="n"/>
+      <c r="AW38" s="37" t="n"/>
+      <c r="AX38" s="37" t="n"/>
+      <c r="AY38" s="37" t="n"/>
+      <c r="AZ38" s="37" t="n"/>
+      <c r="BA38" s="37" t="n"/>
+      <c r="BB38" s="37" t="n"/>
+      <c r="BC38" s="37" t="n"/>
+      <c r="BD38" s="37" t="n"/>
+      <c r="BE38" s="37" t="n"/>
+      <c r="BF38" s="37" t="n"/>
+      <c r="BG38" s="37" t="n"/>
+      <c r="BH38" s="37" t="n"/>
+      <c r="BI38" s="37" t="n"/>
+      <c r="BJ38" s="37" t="n"/>
+      <c r="BK38" s="37" t="n"/>
+      <c r="BL38" s="37" t="n"/>
+      <c r="BM38" s="37" t="n"/>
+      <c r="BN38" s="37" t="n"/>
+      <c r="BO38" s="37" t="n"/>
+      <c r="BP38" s="37" t="n"/>
+      <c r="BQ38" s="37" t="n"/>
+      <c r="BR38" s="37" t="n"/>
+      <c r="BS38" s="37" t="n"/>
+      <c r="BT38" s="37" t="n"/>
+      <c r="BU38" s="37" t="n"/>
+      <c r="BV38" s="37" t="n"/>
+      <c r="BW38" s="37" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="36" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="36" t="n"/>
+      <c r="I39" s="36" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="36" t="n"/>
+      <c r="L39" s="36" t="n"/>
+      <c r="M39" s="36" t="n"/>
+      <c r="N39" s="36" t="n"/>
+      <c r="O39" s="36" t="n"/>
+      <c r="P39" s="36" t="n"/>
+      <c r="Q39" s="36" t="n"/>
+      <c r="R39" s="36" t="n"/>
+      <c r="S39" s="36" t="n"/>
+      <c r="T39" s="36" t="n"/>
+      <c r="U39" s="36" t="n"/>
+      <c r="V39" s="36" t="n"/>
+      <c r="W39" s="36" t="n"/>
+      <c r="X39" s="36" t="n"/>
+      <c r="Y39" s="36" t="n"/>
+      <c r="Z39" s="36" t="n"/>
+      <c r="AA39" s="36" t="n"/>
+      <c r="AB39" s="36" t="n"/>
+      <c r="AC39" s="36" t="n"/>
+      <c r="AD39" s="36" t="n"/>
+      <c r="AE39" s="36" t="n"/>
+      <c r="AF39" s="36" t="n"/>
+      <c r="AG39" s="36" t="n"/>
+      <c r="AH39" s="36" t="n"/>
+      <c r="AI39" s="36" t="n"/>
+      <c r="AJ39" s="36" t="n"/>
+      <c r="AK39" s="31" t="n"/>
+      <c r="AL39" s="31" t="n"/>
+      <c r="AM39" s="31" t="n"/>
+      <c r="AN39" s="31" t="n"/>
+      <c r="AO39" s="31" t="n"/>
+      <c r="AP39" s="31" t="n"/>
+      <c r="AQ39" s="31" t="n"/>
+      <c r="AR39" s="31" t="n"/>
+      <c r="AS39" s="31" t="n"/>
+      <c r="AT39" s="31" t="n"/>
+      <c r="AU39" s="31" t="n"/>
+      <c r="AV39" s="31" t="n"/>
+      <c r="AW39" s="31" t="n"/>
+      <c r="AX39" s="31" t="n"/>
+      <c r="AY39" s="31" t="n"/>
+      <c r="AZ39" s="31" t="n"/>
+      <c r="BA39" s="31" t="n"/>
+      <c r="BB39" s="31" t="n"/>
+      <c r="BC39" s="31" t="n"/>
+      <c r="BD39" s="31" t="n"/>
+      <c r="BE39" s="31" t="n"/>
+      <c r="BF39" s="31" t="n"/>
+      <c r="BG39" s="31" t="n"/>
+      <c r="BH39" s="31" t="n"/>
+      <c r="BI39" s="31" t="n"/>
+      <c r="BJ39" s="31" t="n"/>
+      <c r="BK39" s="31" t="n"/>
+      <c r="BL39" s="31" t="n"/>
+      <c r="BM39" s="31" t="n"/>
+      <c r="BN39" s="31" t="n"/>
+      <c r="BO39" s="31" t="n"/>
+      <c r="BP39" s="31" t="n"/>
+      <c r="BQ39" s="31" t="n"/>
+      <c r="BR39" s="31" t="n"/>
+      <c r="BS39" s="31" t="n"/>
+      <c r="BT39" s="31" t="n"/>
+      <c r="BU39" s="31" t="n"/>
+      <c r="BV39" s="31" t="n"/>
+      <c r="BW39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="36" t="n"/>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="36" t="n"/>
+      <c r="E40" s="36" t="n"/>
+      <c r="F40" s="36" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="36" t="n"/>
+      <c r="I40" s="36" t="n"/>
+      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
+      <c r="L40" s="36" t="n"/>
+      <c r="M40" s="36" t="n"/>
+      <c r="N40" s="36" t="n"/>
+      <c r="O40" s="36" t="n"/>
+      <c r="P40" s="36" t="n"/>
+      <c r="Q40" s="36" t="n"/>
+      <c r="R40" s="36" t="n"/>
+      <c r="S40" s="36" t="n"/>
+      <c r="T40" s="36" t="n"/>
+      <c r="U40" s="36" t="n"/>
+      <c r="V40" s="36" t="n"/>
+      <c r="W40" s="36" t="n"/>
+      <c r="X40" s="36" t="n"/>
+      <c r="Y40" s="36" t="n"/>
+      <c r="Z40" s="36" t="n"/>
+      <c r="AA40" s="36" t="n"/>
+      <c r="AB40" s="36" t="n"/>
+      <c r="AC40" s="36" t="n"/>
+      <c r="AD40" s="36" t="n"/>
+      <c r="AE40" s="36" t="n"/>
+      <c r="AF40" s="36" t="n"/>
+      <c r="AG40" s="36" t="n"/>
+      <c r="AH40" s="36" t="n"/>
+      <c r="AI40" s="36" t="n"/>
+      <c r="AJ40" s="36" t="n"/>
+      <c r="AK40" s="31" t="n"/>
+      <c r="AL40" s="31" t="n"/>
+      <c r="AM40" s="31" t="n"/>
+      <c r="AN40" s="31" t="n"/>
+      <c r="AO40" s="31" t="n"/>
+      <c r="AP40" s="31" t="n"/>
+      <c r="AQ40" s="31" t="n"/>
+      <c r="AR40" s="31" t="n"/>
+      <c r="AS40" s="31" t="n"/>
+      <c r="AT40" s="31" t="n"/>
+      <c r="AU40" s="31" t="n"/>
+      <c r="AV40" s="31" t="n"/>
+      <c r="AW40" s="31" t="n"/>
+      <c r="AX40" s="31" t="n"/>
+      <c r="AY40" s="31" t="n"/>
+      <c r="AZ40" s="31" t="n"/>
+      <c r="BA40" s="31" t="n"/>
+      <c r="BB40" s="31" t="n"/>
+      <c r="BC40" s="31" t="n"/>
+      <c r="BD40" s="31" t="n"/>
+      <c r="BE40" s="31" t="n"/>
+      <c r="BF40" s="31" t="n"/>
+      <c r="BG40" s="31" t="n"/>
+      <c r="BH40" s="31" t="n"/>
+      <c r="BI40" s="31" t="n"/>
+      <c r="BJ40" s="31" t="n"/>
+      <c r="BK40" s="31" t="n"/>
+      <c r="BL40" s="31" t="n"/>
+      <c r="BM40" s="31" t="n"/>
+      <c r="BN40" s="31" t="n"/>
+      <c r="BO40" s="31" t="n"/>
+      <c r="BP40" s="31" t="n"/>
+      <c r="BQ40" s="31" t="n"/>
+      <c r="BR40" s="31" t="n"/>
+      <c r="BS40" s="31" t="n"/>
+      <c r="BT40" s="31" t="n"/>
+      <c r="BU40" s="31" t="n"/>
+      <c r="BV40" s="31" t="n"/>
+      <c r="BW40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="31" t="n"/>
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>記</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">セキュリティカード　　　個　　No.　　　　　／　店舗鍵　　　個　　No.　　　　　</t>
-        </is>
-      </c>
+      <c r="AK41" s="31" t="n"/>
+      <c r="AL41" s="31" t="n"/>
+      <c r="AM41" s="31" t="n"/>
+      <c r="AN41" s="31" t="n"/>
+      <c r="AO41" s="31" t="n"/>
+      <c r="AP41" s="31" t="n"/>
+      <c r="AQ41" s="31" t="n"/>
+      <c r="AR41" s="31" t="n"/>
+      <c r="AS41" s="31" t="n"/>
+      <c r="AT41" s="31" t="n"/>
+      <c r="AU41" s="31" t="n"/>
+      <c r="AV41" s="31" t="n"/>
+      <c r="AW41" s="31" t="n"/>
+      <c r="AX41" s="31" t="n"/>
+      <c r="AY41" s="31" t="n"/>
+      <c r="AZ41" s="31" t="n"/>
+      <c r="BA41" s="31" t="n"/>
+      <c r="BB41" s="31" t="n"/>
+      <c r="BC41" s="31" t="n"/>
+      <c r="BD41" s="31" t="n"/>
+      <c r="BE41" s="31" t="n"/>
+      <c r="BF41" s="31" t="n"/>
+      <c r="BG41" s="31" t="n"/>
+      <c r="BH41" s="31" t="n"/>
+      <c r="BI41" s="31" t="n"/>
+      <c r="BJ41" s="31" t="n"/>
+      <c r="BK41" s="31" t="n"/>
+      <c r="BL41" s="31" t="n"/>
+      <c r="BM41" s="31" t="n"/>
+      <c r="BN41" s="31" t="n"/>
+      <c r="BO41" s="31" t="n"/>
+      <c r="BP41" s="31" t="n"/>
+      <c r="BQ41" s="31" t="n"/>
+      <c r="BR41" s="31" t="n"/>
+      <c r="BS41" s="31" t="n"/>
+      <c r="BT41" s="31" t="n"/>
+      <c r="BU41" s="31" t="n"/>
+      <c r="BV41" s="31" t="n"/>
+      <c r="BW41" s="31" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="31" t="n"/>
+      <c r="AK42" s="31" t="n"/>
+      <c r="AL42" s="31" t="n"/>
+      <c r="AM42" s="31" t="n"/>
+      <c r="AN42" s="31" t="n"/>
+      <c r="AO42" s="31" t="n"/>
+      <c r="AP42" s="31" t="n"/>
+      <c r="AQ42" s="31" t="n"/>
+      <c r="AR42" s="31" t="n"/>
+      <c r="AS42" s="31" t="n"/>
+      <c r="AT42" s="31" t="n"/>
+      <c r="AU42" s="31" t="n"/>
+      <c r="AV42" s="31" t="n"/>
+      <c r="AW42" s="31" t="n"/>
+      <c r="AX42" s="31" t="n"/>
+      <c r="AY42" s="31" t="n"/>
+      <c r="AZ42" s="31" t="n"/>
+      <c r="BA42" s="31" t="n"/>
+      <c r="BB42" s="31" t="n"/>
+      <c r="BC42" s="31" t="n"/>
+      <c r="BD42" s="31" t="n"/>
+      <c r="BE42" s="31" t="n"/>
+      <c r="BF42" s="31" t="n"/>
+      <c r="BG42" s="31" t="n"/>
+      <c r="BH42" s="31" t="n"/>
+      <c r="BI42" s="31" t="n"/>
+      <c r="BJ42" s="31" t="n"/>
+      <c r="BK42" s="31" t="n"/>
+      <c r="BL42" s="31" t="n"/>
+      <c r="BM42" s="31" t="n"/>
+      <c r="BN42" s="31" t="n"/>
+      <c r="BO42" s="31" t="n"/>
+      <c r="BP42" s="31" t="n"/>
+      <c r="BQ42" s="31" t="n"/>
+      <c r="BR42" s="31" t="n"/>
+      <c r="BS42" s="31" t="n"/>
+      <c r="BT42" s="31" t="n"/>
+      <c r="BU42" s="31" t="n"/>
+      <c r="BV42" s="31" t="n"/>
+      <c r="BW42" s="31" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="31" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+      <c r="G43" s="36" t="n"/>
+      <c r="H43" s="36" t="n"/>
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="36" t="n"/>
+      <c r="K43" s="36" t="n"/>
+      <c r="L43" s="36" t="n"/>
+      <c r="M43" s="36" t="n"/>
+      <c r="N43" s="36" t="n"/>
+      <c r="O43" s="36" t="n"/>
+      <c r="P43" s="36" t="n"/>
+      <c r="Q43" s="36" t="n"/>
+      <c r="R43" s="36" t="n"/>
+      <c r="S43" s="36" t="n"/>
+      <c r="T43" s="36" t="n"/>
+      <c r="U43" s="36" t="n"/>
+      <c r="V43" s="36" t="n"/>
+      <c r="W43" s="36" t="n"/>
+      <c r="X43" s="36" t="n"/>
+      <c r="Y43" s="36" t="n"/>
+      <c r="Z43" s="36" t="n"/>
+      <c r="AA43" s="36" t="n"/>
+      <c r="AB43" s="36" t="n"/>
+      <c r="AC43" s="36" t="n"/>
+      <c r="AD43" s="36" t="n"/>
+      <c r="AE43" s="36" t="n"/>
+      <c r="AF43" s="36" t="n"/>
+      <c r="AG43" s="36" t="n"/>
+      <c r="AH43" s="36" t="n"/>
+      <c r="AI43" s="36" t="n"/>
+      <c r="AJ43" s="36" t="n"/>
+      <c r="AK43" s="31" t="n"/>
+      <c r="AL43" s="31" t="n"/>
+      <c r="AM43" s="31" t="n"/>
+      <c r="AN43" s="31" t="n"/>
+      <c r="AO43" s="31" t="n"/>
+      <c r="AP43" s="31" t="n"/>
+      <c r="AQ43" s="31" t="n"/>
+      <c r="AR43" s="31" t="n"/>
+      <c r="AS43" s="31" t="n"/>
+      <c r="AT43" s="31" t="n"/>
+      <c r="AU43" s="31" t="n"/>
+      <c r="AV43" s="31" t="n"/>
+      <c r="AW43" s="31" t="n"/>
+      <c r="AX43" s="31" t="n"/>
+      <c r="AY43" s="31" t="n"/>
+      <c r="AZ43" s="31" t="n"/>
+      <c r="BA43" s="31" t="n"/>
+      <c r="BB43" s="31" t="n"/>
+      <c r="BC43" s="31" t="n"/>
+      <c r="BD43" s="31" t="n"/>
+      <c r="BE43" s="31" t="n"/>
+      <c r="BF43" s="31" t="n"/>
+      <c r="BG43" s="31" t="n"/>
+      <c r="BH43" s="31" t="n"/>
+      <c r="BI43" s="31" t="n"/>
+      <c r="BJ43" s="31" t="n"/>
+      <c r="BK43" s="31" t="n"/>
+      <c r="BL43" s="31" t="n"/>
+      <c r="BM43" s="31" t="n"/>
+      <c r="BN43" s="31" t="n"/>
+      <c r="BO43" s="31" t="n"/>
+      <c r="BP43" s="31" t="n"/>
+      <c r="BQ43" s="31" t="n"/>
+      <c r="BR43" s="31" t="n"/>
+      <c r="BS43" s="31" t="n"/>
+      <c r="BT43" s="31" t="n"/>
+      <c r="BU43" s="31" t="n"/>
+      <c r="BV43" s="31" t="n"/>
+      <c r="BW43" s="31" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="36" t="n"/>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="36" t="n"/>
+      <c r="F44" s="36" t="n"/>
+      <c r="G44" s="36" t="n"/>
+      <c r="H44" s="36" t="n"/>
+      <c r="I44" s="36" t="n"/>
+      <c r="J44" s="36" t="n"/>
+      <c r="K44" s="36" t="n"/>
+      <c r="L44" s="36" t="n"/>
+      <c r="M44" s="36" t="n"/>
+      <c r="N44" s="36" t="n"/>
+      <c r="O44" s="36" t="n"/>
+      <c r="P44" s="36" t="n"/>
+      <c r="Q44" s="36" t="n"/>
+      <c r="R44" s="36" t="n"/>
+      <c r="S44" s="36" t="n"/>
+      <c r="T44" s="36" t="n"/>
+      <c r="U44" s="36" t="n"/>
+      <c r="V44" s="36" t="n"/>
+      <c r="W44" s="36" t="n"/>
+      <c r="X44" s="36" t="n"/>
+      <c r="Y44" s="36" t="n"/>
+      <c r="Z44" s="36" t="n"/>
+      <c r="AA44" s="36" t="n"/>
+      <c r="AB44" s="36" t="n"/>
+      <c r="AC44" s="36" t="n"/>
+      <c r="AD44" s="36" t="n"/>
+      <c r="AE44" s="36" t="n"/>
+      <c r="AF44" s="36" t="n"/>
+      <c r="AG44" s="36" t="n"/>
+      <c r="AH44" s="36" t="n"/>
+      <c r="AI44" s="36" t="n"/>
+      <c r="AJ44" s="36" t="n"/>
+      <c r="AK44" s="31" t="n"/>
+      <c r="AL44" s="31" t="n"/>
+      <c r="AM44" s="31" t="n"/>
+      <c r="AN44" s="31" t="n"/>
+      <c r="AO44" s="31" t="n"/>
+      <c r="AP44" s="31" t="n"/>
+      <c r="AQ44" s="31" t="n"/>
+      <c r="AR44" s="31" t="n"/>
+      <c r="AS44" s="31" t="n"/>
+      <c r="AT44" s="31" t="n"/>
+      <c r="AU44" s="31" t="n"/>
+      <c r="AV44" s="31" t="n"/>
+      <c r="AW44" s="31" t="n"/>
+      <c r="AX44" s="31" t="n"/>
+      <c r="AY44" s="31" t="n"/>
+      <c r="AZ44" s="31" t="n"/>
+      <c r="BA44" s="31" t="n"/>
+      <c r="BB44" s="31" t="n"/>
+      <c r="BC44" s="31" t="n"/>
+      <c r="BD44" s="31" t="n"/>
+      <c r="BE44" s="31" t="n"/>
+      <c r="BF44" s="31" t="n"/>
+      <c r="BG44" s="31" t="n"/>
+      <c r="BH44" s="31" t="n"/>
+      <c r="BI44" s="31" t="n"/>
+      <c r="BJ44" s="31" t="n"/>
+      <c r="BK44" s="31" t="n"/>
+      <c r="BL44" s="31" t="n"/>
+      <c r="BM44" s="31" t="n"/>
+      <c r="BN44" s="31" t="n"/>
+      <c r="BO44" s="31" t="n"/>
+      <c r="BP44" s="31" t="n"/>
+      <c r="BQ44" s="31" t="n"/>
+      <c r="BR44" s="31" t="n"/>
+      <c r="BS44" s="31" t="n"/>
+      <c r="BT44" s="31" t="n"/>
+      <c r="BU44" s="31" t="n"/>
+      <c r="BV44" s="31" t="n"/>
+      <c r="BW44" s="31" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="31" t="n"/>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>セキュリティカード　　     　個</t>
+        </is>
+      </c>
+      <c r="P45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">№　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="AA45" s="36" t="n"/>
+      <c r="AB45" s="36" t="n"/>
+      <c r="AC45" s="36" t="n"/>
+      <c r="AD45" s="36" t="n"/>
+      <c r="AE45" s="36" t="n"/>
+      <c r="AF45" s="36" t="n"/>
+      <c r="AG45" s="36" t="n"/>
+      <c r="AH45" s="36" t="n"/>
+      <c r="AI45" s="36" t="n"/>
+      <c r="AJ45" s="36" t="n"/>
+      <c r="AK45" s="31" t="n"/>
+      <c r="AL45" s="31" t="n"/>
+      <c r="AM45" s="31" t="n"/>
+      <c r="AN45" s="31" t="n"/>
+      <c r="AO45" s="31" t="n"/>
+      <c r="AP45" s="31" t="n"/>
+      <c r="AQ45" s="31" t="n"/>
+      <c r="AR45" s="31" t="n"/>
+      <c r="AS45" s="31" t="n"/>
+      <c r="AT45" s="31" t="n"/>
+      <c r="AU45" s="31" t="n"/>
+      <c r="AV45" s="31" t="n"/>
+      <c r="AW45" s="31" t="n"/>
+      <c r="AX45" s="31" t="n"/>
+      <c r="AY45" s="31" t="n"/>
+      <c r="AZ45" s="31" t="n"/>
+      <c r="BA45" s="31" t="n"/>
+      <c r="BB45" s="31" t="n"/>
+      <c r="BC45" s="31" t="n"/>
+      <c r="BD45" s="31" t="n"/>
+      <c r="BE45" s="31" t="n"/>
+      <c r="BF45" s="31" t="n"/>
+      <c r="BG45" s="31" t="n"/>
+      <c r="BH45" s="31" t="n"/>
+      <c r="BI45" s="31" t="n"/>
+      <c r="BJ45" s="31" t="n"/>
+      <c r="BK45" s="31" t="n"/>
+      <c r="BL45" s="31" t="n"/>
+      <c r="BM45" s="31" t="n"/>
+      <c r="BN45" s="31" t="n"/>
+      <c r="BO45" s="31" t="n"/>
+      <c r="BP45" s="31" t="n"/>
+      <c r="BQ45" s="31" t="n"/>
+      <c r="BR45" s="31" t="n"/>
+      <c r="BS45" s="31" t="n"/>
+      <c r="BT45" s="31" t="n"/>
+      <c r="BU45" s="31" t="n"/>
+      <c r="BV45" s="31" t="n"/>
+      <c r="BW45" s="31" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="31" t="n"/>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
+      <c r="R46" s="41" t="n"/>
+      <c r="S46" s="41" t="n"/>
+      <c r="T46" s="41" t="n"/>
+      <c r="U46" s="41" t="n"/>
+      <c r="V46" s="41" t="n"/>
+      <c r="W46" s="41" t="n"/>
+      <c r="X46" s="41" t="n"/>
+      <c r="Y46" s="41" t="n"/>
+      <c r="Z46" s="41" t="n"/>
+      <c r="AA46" s="36" t="n"/>
+      <c r="AB46" s="36" t="n"/>
+      <c r="AC46" s="36" t="n"/>
+      <c r="AD46" s="36" t="n"/>
+      <c r="AE46" s="36" t="n"/>
+      <c r="AF46" s="36" t="n"/>
+      <c r="AG46" s="36" t="n"/>
+      <c r="AH46" s="36" t="n"/>
+      <c r="AI46" s="36" t="n"/>
+      <c r="AJ46" s="36" t="n"/>
+      <c r="AK46" s="31" t="n"/>
+      <c r="AL46" s="31" t="n"/>
+      <c r="AM46" s="31" t="n"/>
+      <c r="AN46" s="31" t="n"/>
+      <c r="AO46" s="31" t="n"/>
+      <c r="AP46" s="31" t="n"/>
+      <c r="AQ46" s="31" t="n"/>
+      <c r="AR46" s="31" t="n"/>
+      <c r="AS46" s="31" t="n"/>
+      <c r="AT46" s="31" t="n"/>
+      <c r="AU46" s="31" t="n"/>
+      <c r="AV46" s="31" t="n"/>
+      <c r="AW46" s="31" t="n"/>
+      <c r="AX46" s="31" t="n"/>
+      <c r="AY46" s="31" t="n"/>
+      <c r="AZ46" s="31" t="n"/>
+      <c r="BA46" s="31" t="n"/>
+      <c r="BB46" s="31" t="n"/>
+      <c r="BC46" s="31" t="n"/>
+      <c r="BD46" s="31" t="n"/>
+      <c r="BE46" s="31" t="n"/>
+      <c r="BF46" s="31" t="n"/>
+      <c r="BG46" s="31" t="n"/>
+      <c r="BH46" s="31" t="n"/>
+      <c r="BI46" s="31" t="n"/>
+      <c r="BJ46" s="31" t="n"/>
+      <c r="BK46" s="31" t="n"/>
+      <c r="BL46" s="31" t="n"/>
+      <c r="BM46" s="31" t="n"/>
+      <c r="BN46" s="31" t="n"/>
+      <c r="BO46" s="31" t="n"/>
+      <c r="BP46" s="31" t="n"/>
+      <c r="BQ46" s="31" t="n"/>
+      <c r="BR46" s="31" t="n"/>
+      <c r="BS46" s="31" t="n"/>
+      <c r="BT46" s="31" t="n"/>
+      <c r="BU46" s="31" t="n"/>
+      <c r="BV46" s="31" t="n"/>
+      <c r="BW46" s="31" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="31" t="n"/>
+      <c r="P47" s="36" t="n"/>
+      <c r="Q47" s="36" t="n"/>
+      <c r="R47" s="36" t="n"/>
+      <c r="S47" s="36" t="n"/>
+      <c r="T47" s="36" t="n"/>
+      <c r="U47" s="36" t="n"/>
+      <c r="V47" s="36" t="n"/>
+      <c r="W47" s="36" t="n"/>
+      <c r="X47" s="36" t="n"/>
+      <c r="Y47" s="36" t="n"/>
+      <c r="Z47" s="36" t="n"/>
+      <c r="AA47" s="36" t="n"/>
+      <c r="AB47" s="36" t="n"/>
+      <c r="AC47" s="36" t="n"/>
+      <c r="AD47" s="36" t="n"/>
+      <c r="AE47" s="36" t="n"/>
+      <c r="AF47" s="36" t="n"/>
+      <c r="AG47" s="36" t="n"/>
+      <c r="AH47" s="36" t="n"/>
+      <c r="AI47" s="36" t="n"/>
+      <c r="AJ47" s="36" t="n"/>
+      <c r="AK47" s="31" t="n"/>
+      <c r="AL47" s="31" t="n"/>
+      <c r="AM47" s="31" t="n"/>
+      <c r="AN47" s="31" t="n"/>
+      <c r="AO47" s="31" t="n"/>
+      <c r="AP47" s="31" t="n"/>
+      <c r="AQ47" s="31" t="n"/>
+      <c r="AR47" s="31" t="n"/>
+      <c r="AS47" s="31" t="n"/>
+      <c r="AT47" s="31" t="n"/>
+      <c r="AU47" s="31" t="n"/>
+      <c r="AV47" s="31" t="n"/>
+      <c r="AW47" s="31" t="n"/>
+      <c r="AX47" s="31" t="n"/>
+      <c r="AY47" s="31" t="n"/>
+      <c r="AZ47" s="31" t="n"/>
+      <c r="BA47" s="31" t="n"/>
+      <c r="BB47" s="31" t="n"/>
+      <c r="BC47" s="31" t="n"/>
+      <c r="BD47" s="31" t="n"/>
+      <c r="BE47" s="31" t="n"/>
+      <c r="BF47" s="31" t="n"/>
+      <c r="BG47" s="31" t="n"/>
+      <c r="BH47" s="31" t="n"/>
+      <c r="BI47" s="31" t="n"/>
+      <c r="BJ47" s="31" t="n"/>
+      <c r="BK47" s="31" t="n"/>
+      <c r="BL47" s="31" t="n"/>
+      <c r="BM47" s="31" t="n"/>
+      <c r="BN47" s="31" t="n"/>
+      <c r="BO47" s="31" t="n"/>
+      <c r="BP47" s="31" t="n"/>
+      <c r="BQ47" s="31" t="n"/>
+      <c r="BR47" s="31" t="n"/>
+      <c r="BS47" s="31" t="n"/>
+      <c r="BT47" s="31" t="n"/>
+      <c r="BU47" s="31" t="n"/>
+      <c r="BV47" s="31" t="n"/>
+      <c r="BW47" s="31" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="31" t="n"/>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>店　　舗　　鍵　 　 　     　個</t>
+        </is>
+      </c>
+      <c r="P48" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">№　　　　　　　　　　　　　　　　　</t>
+        </is>
+      </c>
+      <c r="AA48" s="36" t="n"/>
+      <c r="AB48" s="36" t="n"/>
+      <c r="AC48" s="36" t="n"/>
+      <c r="AD48" s="36" t="n"/>
+      <c r="AE48" s="36" t="n"/>
+      <c r="AF48" s="36" t="n"/>
+      <c r="AG48" s="36" t="n"/>
+      <c r="AH48" s="36" t="n"/>
+      <c r="AI48" s="36" t="n"/>
+      <c r="AJ48" s="36" t="n"/>
+      <c r="AK48" s="31" t="n"/>
+      <c r="AL48" s="31" t="n"/>
+      <c r="AM48" s="31" t="n"/>
+      <c r="AN48" s="31" t="n"/>
+      <c r="AO48" s="31" t="n"/>
+      <c r="AP48" s="31" t="n"/>
+      <c r="AQ48" s="31" t="n"/>
+      <c r="AR48" s="31" t="n"/>
+      <c r="AS48" s="31" t="n"/>
+      <c r="AT48" s="31" t="n"/>
+      <c r="AU48" s="31" t="n"/>
+      <c r="AV48" s="31" t="n"/>
+      <c r="AW48" s="31" t="n"/>
+      <c r="AX48" s="31" t="n"/>
+      <c r="AY48" s="31" t="n"/>
+      <c r="AZ48" s="31" t="n"/>
+      <c r="BA48" s="31" t="n"/>
+      <c r="BB48" s="31" t="n"/>
+      <c r="BC48" s="31" t="n"/>
+      <c r="BD48" s="31" t="n"/>
+      <c r="BE48" s="31" t="n"/>
+      <c r="BF48" s="31" t="n"/>
+      <c r="BG48" s="31" t="n"/>
+      <c r="BH48" s="31" t="n"/>
+      <c r="BI48" s="31" t="n"/>
+      <c r="BJ48" s="31" t="n"/>
+      <c r="BK48" s="31" t="n"/>
+      <c r="BL48" s="31" t="n"/>
+      <c r="BM48" s="31" t="n"/>
+      <c r="BN48" s="31" t="n"/>
+      <c r="BO48" s="31" t="n"/>
+      <c r="BP48" s="31" t="n"/>
+      <c r="BQ48" s="31" t="n"/>
+      <c r="BR48" s="31" t="n"/>
+      <c r="BS48" s="31" t="n"/>
+      <c r="BT48" s="31" t="n"/>
+      <c r="BU48" s="31" t="n"/>
+      <c r="BV48" s="31" t="n"/>
+      <c r="BW48" s="31" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="31" t="n"/>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="41" t="n"/>
+      <c r="R49" s="41" t="n"/>
+      <c r="S49" s="41" t="n"/>
+      <c r="T49" s="41" t="n"/>
+      <c r="U49" s="41" t="n"/>
+      <c r="V49" s="41" t="n"/>
+      <c r="W49" s="41" t="n"/>
+      <c r="X49" s="41" t="n"/>
+      <c r="Y49" s="41" t="n"/>
+      <c r="Z49" s="41" t="n"/>
+      <c r="AA49" s="36" t="n"/>
+      <c r="AB49" s="36" t="n"/>
+      <c r="AC49" s="36" t="n"/>
+      <c r="AD49" s="36" t="n"/>
+      <c r="AE49" s="36" t="n"/>
+      <c r="AF49" s="36" t="n"/>
+      <c r="AG49" s="36" t="n"/>
+      <c r="AH49" s="36" t="n"/>
+      <c r="AI49" s="36" t="n"/>
+      <c r="AJ49" s="36" t="n"/>
+      <c r="AK49" s="31" t="n"/>
+      <c r="AL49" s="31" t="n"/>
+      <c r="AM49" s="31" t="n"/>
+      <c r="AN49" s="31" t="n"/>
+      <c r="AO49" s="31" t="n"/>
+      <c r="AP49" s="31" t="n"/>
+      <c r="AQ49" s="31" t="n"/>
+      <c r="AR49" s="31" t="n"/>
+      <c r="AS49" s="31" t="n"/>
+      <c r="AT49" s="31" t="n"/>
+      <c r="AU49" s="31" t="n"/>
+      <c r="AV49" s="31" t="n"/>
+      <c r="AW49" s="31" t="n"/>
+      <c r="AX49" s="31" t="n"/>
+      <c r="AY49" s="31" t="n"/>
+      <c r="AZ49" s="31" t="n"/>
+      <c r="BA49" s="31" t="n"/>
+      <c r="BB49" s="31" t="n"/>
+      <c r="BC49" s="31" t="n"/>
+      <c r="BD49" s="31" t="n"/>
+      <c r="BE49" s="31" t="n"/>
+      <c r="BF49" s="31" t="n"/>
+      <c r="BG49" s="31" t="n"/>
+      <c r="BH49" s="31" t="n"/>
+      <c r="BI49" s="31" t="n"/>
+      <c r="BJ49" s="31" t="n"/>
+      <c r="BK49" s="31" t="n"/>
+      <c r="BL49" s="31" t="n"/>
+      <c r="BM49" s="31" t="n"/>
+      <c r="BN49" s="31" t="n"/>
+      <c r="BO49" s="31" t="n"/>
+      <c r="BP49" s="31" t="n"/>
+      <c r="BQ49" s="31" t="n"/>
+      <c r="BR49" s="31" t="n"/>
+      <c r="BS49" s="31" t="n"/>
+      <c r="BT49" s="31" t="n"/>
+      <c r="BU49" s="31" t="n"/>
+      <c r="BV49" s="31" t="n"/>
+      <c r="BW49" s="31" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="31" t="n"/>
+      <c r="P50" s="36" t="n"/>
+      <c r="Q50" s="36" t="n"/>
+      <c r="R50" s="36" t="n"/>
+      <c r="S50" s="36" t="n"/>
+      <c r="T50" s="36" t="n"/>
+      <c r="U50" s="36" t="n"/>
+      <c r="V50" s="36" t="n"/>
+      <c r="W50" s="36" t="n"/>
+      <c r="X50" s="36" t="n"/>
+      <c r="Y50" s="36" t="n"/>
+      <c r="Z50" s="36" t="n"/>
+      <c r="AA50" s="36" t="n"/>
+      <c r="AB50" s="36" t="n"/>
+      <c r="AC50" s="36" t="n"/>
+      <c r="AD50" s="36" t="n"/>
+      <c r="AE50" s="36" t="n"/>
+      <c r="AF50" s="36" t="n"/>
+      <c r="AG50" s="36" t="n"/>
+      <c r="AH50" s="36" t="n"/>
+      <c r="AI50" s="36" t="n"/>
+      <c r="AJ50" s="36" t="n"/>
+      <c r="AK50" s="31" t="n"/>
+      <c r="AL50" s="31" t="n"/>
+      <c r="AM50" s="31" t="n"/>
+      <c r="AN50" s="31" t="n"/>
+      <c r="AO50" s="31" t="n"/>
+      <c r="AP50" s="31" t="n"/>
+      <c r="AQ50" s="31" t="n"/>
+      <c r="AR50" s="31" t="n"/>
+      <c r="AS50" s="31" t="n"/>
+      <c r="AT50" s="31" t="n"/>
+      <c r="AU50" s="31" t="n"/>
+      <c r="AV50" s="31" t="n"/>
+      <c r="AW50" s="31" t="n"/>
+      <c r="AX50" s="31" t="n"/>
+      <c r="AY50" s="31" t="n"/>
+      <c r="AZ50" s="31" t="n"/>
+      <c r="BA50" s="31" t="n"/>
+      <c r="BB50" s="31" t="n"/>
+      <c r="BC50" s="31" t="n"/>
+      <c r="BD50" s="31" t="n"/>
+      <c r="BE50" s="31" t="n"/>
+      <c r="BF50" s="31" t="n"/>
+      <c r="BG50" s="31" t="n"/>
+      <c r="BH50" s="31" t="n"/>
+      <c r="BI50" s="31" t="n"/>
+      <c r="BJ50" s="31" t="n"/>
+      <c r="BK50" s="31" t="n"/>
+      <c r="BL50" s="31" t="n"/>
+      <c r="BM50" s="31" t="n"/>
+      <c r="BN50" s="31" t="n"/>
+      <c r="BO50" s="31" t="n"/>
+      <c r="BP50" s="31" t="n"/>
+      <c r="BQ50" s="31" t="n"/>
+      <c r="BR50" s="31" t="n"/>
+      <c r="BS50" s="31" t="n"/>
+      <c r="BT50" s="31" t="n"/>
+      <c r="BU50" s="31" t="n"/>
+      <c r="BV50" s="31" t="n"/>
+      <c r="BW50" s="31" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="31" t="n"/>
+      <c r="B51" s="36" t="n"/>
+      <c r="C51" s="36" t="n"/>
+      <c r="D51" s="36" t="n"/>
+      <c r="E51" s="36" t="n"/>
+      <c r="F51" s="36" t="n"/>
+      <c r="G51" s="36" t="n"/>
+      <c r="H51" s="36" t="n"/>
+      <c r="I51" s="36" t="n"/>
+      <c r="J51" s="36" t="n"/>
+      <c r="K51" s="36" t="n"/>
+      <c r="L51" s="36" t="n"/>
+      <c r="M51" s="36" t="n"/>
+      <c r="N51" s="36" t="n"/>
+      <c r="O51" s="36" t="n"/>
+      <c r="P51" s="36" t="n"/>
+      <c r="Q51" s="36" t="n"/>
+      <c r="R51" s="36" t="n"/>
+      <c r="S51" s="36" t="n"/>
+      <c r="T51" s="36" t="n"/>
+      <c r="U51" s="36" t="n"/>
+      <c r="V51" s="36" t="n"/>
+      <c r="W51" s="36" t="n"/>
+      <c r="X51" s="36" t="n"/>
+      <c r="Y51" s="36" t="n"/>
+      <c r="Z51" s="36" t="n"/>
+      <c r="AA51" s="36" t="n"/>
+      <c r="AB51" s="36" t="n"/>
+      <c r="AC51" s="36" t="n"/>
+      <c r="AD51" s="36" t="n"/>
+      <c r="AE51" s="36" t="n"/>
+      <c r="AF51" s="36" t="n"/>
+      <c r="AG51" s="36" t="n"/>
+      <c r="AH51" s="36" t="n"/>
+      <c r="AI51" s="36" t="n"/>
+      <c r="AJ51" s="36" t="n"/>
+      <c r="AK51" s="31" t="n"/>
+      <c r="AL51" s="31" t="n"/>
+      <c r="AM51" s="31" t="n"/>
+      <c r="AN51" s="31" t="n"/>
+      <c r="AO51" s="31" t="n"/>
+      <c r="AP51" s="31" t="n"/>
+      <c r="AQ51" s="31" t="n"/>
+      <c r="AR51" s="31" t="n"/>
+      <c r="AS51" s="31" t="n"/>
+      <c r="AT51" s="31" t="n"/>
+      <c r="AU51" s="31" t="n"/>
+      <c r="AV51" s="31" t="n"/>
+      <c r="AW51" s="31" t="n"/>
+      <c r="AX51" s="31" t="n"/>
+      <c r="AY51" s="31" t="n"/>
+      <c r="AZ51" s="31" t="n"/>
+      <c r="BA51" s="31" t="n"/>
+      <c r="BB51" s="31" t="n"/>
+      <c r="BC51" s="31" t="n"/>
+      <c r="BD51" s="31" t="n"/>
+      <c r="BE51" s="31" t="n"/>
+      <c r="BF51" s="31" t="n"/>
+      <c r="BG51" s="31" t="n"/>
+      <c r="BH51" s="31" t="n"/>
+      <c r="BI51" s="31" t="n"/>
+      <c r="BJ51" s="31" t="n"/>
+      <c r="BK51" s="31" t="n"/>
+      <c r="BL51" s="31" t="n"/>
+      <c r="BM51" s="31" t="n"/>
+      <c r="BN51" s="31" t="n"/>
+      <c r="BO51" s="31" t="n"/>
+      <c r="BP51" s="31" t="n"/>
+      <c r="BQ51" s="31" t="n"/>
+      <c r="BR51" s="31" t="n"/>
+      <c r="BS51" s="31" t="n"/>
+      <c r="BT51" s="31" t="n"/>
+      <c r="BU51" s="31" t="n"/>
+      <c r="BV51" s="31" t="n"/>
+      <c r="BW51" s="31" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="31" t="n"/>
+      <c r="B52" s="36" t="n"/>
+      <c r="C52" s="36" t="n"/>
+      <c r="D52" s="36" t="n"/>
+      <c r="E52" s="36" t="n"/>
+      <c r="F52" s="36" t="n"/>
+      <c r="G52" s="36" t="n"/>
+      <c r="H52" s="36" t="n"/>
+      <c r="I52" s="36" t="n"/>
+      <c r="J52" s="36" t="n"/>
+      <c r="K52" s="36" t="n"/>
+      <c r="L52" s="36" t="n"/>
+      <c r="M52" s="36" t="n"/>
+      <c r="N52" s="36" t="n"/>
+      <c r="O52" s="36" t="n"/>
+      <c r="P52" s="36" t="n"/>
+      <c r="Q52" s="36" t="n"/>
+      <c r="R52" s="36" t="n"/>
+      <c r="S52" s="36" t="n"/>
+      <c r="T52" s="36" t="n"/>
+      <c r="U52" s="36" t="n"/>
+      <c r="V52" s="36" t="n"/>
+      <c r="W52" s="36" t="n"/>
+      <c r="X52" s="36" t="n"/>
+      <c r="Y52" s="36" t="n"/>
+      <c r="Z52" s="36" t="n"/>
+      <c r="AA52" s="36" t="n"/>
+      <c r="AB52" s="36" t="n"/>
+      <c r="AC52" s="36" t="n"/>
+      <c r="AD52" s="36" t="n"/>
+      <c r="AE52" s="37" t="inlineStr">
+        <is>
+          <t>以上</t>
+        </is>
+      </c>
+      <c r="AF52" s="36" t="n"/>
+      <c r="AG52" s="36" t="n"/>
+      <c r="AH52" s="36" t="n"/>
+      <c r="AI52" s="36" t="n"/>
+      <c r="AJ52" s="36" t="n"/>
+      <c r="AK52" s="31" t="n"/>
+      <c r="AL52" s="31" t="n"/>
+      <c r="AM52" s="31" t="n"/>
+      <c r="AN52" s="31" t="n"/>
+      <c r="AO52" s="31" t="n"/>
+      <c r="AP52" s="31" t="n"/>
+      <c r="AQ52" s="31" t="n"/>
+      <c r="AR52" s="31" t="n"/>
+      <c r="AS52" s="31" t="n"/>
+      <c r="AT52" s="31" t="n"/>
+      <c r="AU52" s="31" t="n"/>
+      <c r="AV52" s="31" t="n"/>
+      <c r="AW52" s="31" t="n"/>
+      <c r="AX52" s="31" t="n"/>
+      <c r="AY52" s="31" t="n"/>
+      <c r="AZ52" s="31" t="n"/>
+      <c r="BA52" s="31" t="n"/>
+      <c r="BB52" s="31" t="n"/>
+      <c r="BC52" s="31" t="n"/>
+      <c r="BD52" s="31" t="n"/>
+      <c r="BE52" s="31" t="n"/>
+      <c r="BF52" s="31" t="n"/>
+      <c r="BG52" s="31" t="n"/>
+      <c r="BH52" s="31" t="n"/>
+      <c r="BI52" s="31" t="n"/>
+      <c r="BJ52" s="31" t="n"/>
+      <c r="BK52" s="31" t="n"/>
+      <c r="BL52" s="31" t="n"/>
+      <c r="BM52" s="31" t="n"/>
+      <c r="BN52" s="31" t="n"/>
+      <c r="BO52" s="31" t="n"/>
+      <c r="BP52" s="31" t="n"/>
+      <c r="BQ52" s="31" t="n"/>
+      <c r="BR52" s="31" t="n"/>
+      <c r="BS52" s="31" t="n"/>
+      <c r="BT52" s="31" t="n"/>
+      <c r="BU52" s="31" t="n"/>
+      <c r="BV52" s="31" t="n"/>
+      <c r="BW52" s="31" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="36" t="n"/>
+      <c r="C53" s="36" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
+      <c r="F53" s="36" t="n"/>
+      <c r="G53" s="36" t="n"/>
+      <c r="H53" s="36" t="n"/>
+      <c r="I53" s="36" t="n"/>
+      <c r="J53" s="36" t="n"/>
+      <c r="K53" s="36" t="n"/>
+      <c r="L53" s="36" t="n"/>
+      <c r="M53" s="36" t="n"/>
+      <c r="N53" s="36" t="n"/>
+      <c r="O53" s="36" t="n"/>
+      <c r="P53" s="36" t="n"/>
+      <c r="Q53" s="36" t="n"/>
+      <c r="R53" s="36" t="n"/>
+      <c r="S53" s="36" t="n"/>
+      <c r="T53" s="36" t="n"/>
+      <c r="U53" s="36" t="n"/>
+      <c r="V53" s="36" t="n"/>
+      <c r="W53" s="36" t="n"/>
+      <c r="X53" s="36" t="n"/>
+      <c r="Y53" s="36" t="n"/>
+      <c r="Z53" s="36" t="n"/>
+      <c r="AA53" s="36" t="n"/>
+      <c r="AB53" s="36" t="n"/>
+      <c r="AC53" s="36" t="n"/>
+      <c r="AD53" s="36" t="n"/>
+      <c r="AE53" s="36" t="n"/>
+      <c r="AF53" s="36" t="n"/>
+      <c r="AG53" s="36" t="n"/>
+      <c r="AH53" s="36" t="n"/>
+      <c r="AI53" s="36" t="n"/>
+      <c r="AJ53" s="36" t="n"/>
+      <c r="AK53" s="31" t="n"/>
+      <c r="AL53" s="31" t="n"/>
+      <c r="AM53" s="31" t="n"/>
+      <c r="AN53" s="31" t="n"/>
+      <c r="AO53" s="31" t="n"/>
+      <c r="AP53" s="31" t="n"/>
+      <c r="AQ53" s="31" t="n"/>
+      <c r="AR53" s="31" t="n"/>
+      <c r="AS53" s="31" t="n"/>
+      <c r="AT53" s="31" t="n"/>
+      <c r="AU53" s="31" t="n"/>
+      <c r="AV53" s="31" t="n"/>
+      <c r="AW53" s="31" t="n"/>
+      <c r="AX53" s="31" t="n"/>
+      <c r="AY53" s="31" t="n"/>
+      <c r="AZ53" s="31" t="n"/>
+      <c r="BA53" s="31" t="n"/>
+      <c r="BB53" s="31" t="n"/>
+      <c r="BC53" s="31" t="n"/>
+      <c r="BD53" s="31" t="n"/>
+      <c r="BE53" s="31" t="n"/>
+      <c r="BF53" s="31" t="n"/>
+      <c r="BG53" s="31" t="n"/>
+      <c r="BH53" s="31" t="n"/>
+      <c r="BI53" s="31" t="n"/>
+      <c r="BJ53" s="31" t="n"/>
+      <c r="BK53" s="31" t="n"/>
+      <c r="BL53" s="31" t="n"/>
+      <c r="BM53" s="31" t="n"/>
+      <c r="BN53" s="31" t="n"/>
+      <c r="BO53" s="31" t="n"/>
+      <c r="BP53" s="31" t="n"/>
+      <c r="BQ53" s="31" t="n"/>
+      <c r="BR53" s="31" t="n"/>
+      <c r="BS53" s="31" t="n"/>
+      <c r="BT53" s="31" t="n"/>
+      <c r="BU53" s="31" t="n"/>
+      <c r="BV53" s="31" t="n"/>
+      <c r="BW53" s="31" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="36" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
+      <c r="J54" s="36" t="n"/>
+      <c r="K54" s="36" t="n"/>
+      <c r="L54" s="36" t="n"/>
+      <c r="M54" s="36" t="n"/>
+      <c r="N54" s="36" t="n"/>
+      <c r="O54" s="36" t="n"/>
+      <c r="P54" s="36" t="n"/>
+      <c r="Q54" s="36" t="n"/>
+      <c r="R54" s="36" t="n"/>
+      <c r="S54" s="36" t="n"/>
+      <c r="T54" s="36" t="n"/>
+      <c r="U54" s="36" t="n"/>
+      <c r="V54" s="36" t="n"/>
+      <c r="W54" s="36" t="n"/>
+      <c r="X54" s="36" t="n"/>
+      <c r="Y54" s="36" t="n"/>
+      <c r="Z54" s="36" t="n"/>
+      <c r="AA54" s="36" t="n"/>
+      <c r="AB54" s="36" t="n"/>
+      <c r="AC54" s="36" t="n"/>
+      <c r="AD54" s="36" t="n"/>
+      <c r="AE54" s="37" t="n"/>
+      <c r="AF54" s="37" t="n"/>
+      <c r="AG54" s="36" t="n"/>
+      <c r="AH54" s="36" t="n"/>
+      <c r="AI54" s="36" t="n"/>
+      <c r="AJ54" s="36" t="n"/>
+      <c r="AK54" s="31" t="n"/>
+      <c r="AL54" s="31" t="n"/>
+      <c r="AM54" s="31" t="n"/>
+      <c r="AN54" s="31" t="n"/>
+      <c r="AO54" s="31" t="n"/>
+      <c r="AP54" s="31" t="n"/>
+      <c r="AQ54" s="31" t="n"/>
+      <c r="AR54" s="31" t="n"/>
+      <c r="AS54" s="31" t="n"/>
+      <c r="AT54" s="31" t="n"/>
+      <c r="AU54" s="31" t="n"/>
+      <c r="AV54" s="31" t="n"/>
+      <c r="AW54" s="31" t="n"/>
+      <c r="AX54" s="31" t="n"/>
+      <c r="AY54" s="31" t="n"/>
+      <c r="AZ54" s="31" t="n"/>
+      <c r="BA54" s="31" t="n"/>
+      <c r="BB54" s="31" t="n"/>
+      <c r="BC54" s="31" t="n"/>
+      <c r="BD54" s="31" t="n"/>
+      <c r="BE54" s="31" t="n"/>
+      <c r="BF54" s="31" t="n"/>
+      <c r="BG54" s="31" t="n"/>
+      <c r="BH54" s="31" t="n"/>
+      <c r="BI54" s="31" t="n"/>
+      <c r="BJ54" s="31" t="n"/>
+      <c r="BK54" s="31" t="n"/>
+      <c r="BL54" s="31" t="n"/>
+      <c r="BM54" s="31" t="n"/>
+      <c r="BN54" s="31" t="n"/>
+      <c r="BO54" s="31" t="n"/>
+      <c r="BP54" s="31" t="n"/>
+      <c r="BQ54" s="31" t="n"/>
+      <c r="BR54" s="31" t="n"/>
+      <c r="BS54" s="31" t="n"/>
+      <c r="BT54" s="31" t="n"/>
+      <c r="BU54" s="31" t="n"/>
+      <c r="BV54" s="31" t="n"/>
+      <c r="BW54" s="31" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="31" t="n"/>
+      <c r="B55" s="36" t="n"/>
+      <c r="C55" s="36" t="n"/>
+      <c r="D55" s="36" t="n"/>
+      <c r="E55" s="36" t="n"/>
+      <c r="F55" s="36" t="n"/>
+      <c r="G55" s="36" t="n"/>
+      <c r="H55" s="36" t="n"/>
+      <c r="I55" s="36" t="n"/>
+      <c r="J55" s="36" t="n"/>
+      <c r="K55" s="36" t="n"/>
+      <c r="L55" s="36" t="n"/>
+      <c r="M55" s="36" t="n"/>
+      <c r="N55" s="36" t="n"/>
+      <c r="O55" s="36" t="n"/>
+      <c r="P55" s="36" t="n"/>
+      <c r="Q55" s="36" t="n"/>
+      <c r="R55" s="36" t="n"/>
+      <c r="S55" s="36" t="n"/>
+      <c r="T55" s="36" t="n"/>
+      <c r="U55" s="36" t="n"/>
+      <c r="V55" s="36" t="n"/>
+      <c r="W55" s="36" t="n"/>
+      <c r="X55" s="36" t="n"/>
+      <c r="Y55" s="36" t="n"/>
+      <c r="Z55" s="36" t="n"/>
+      <c r="AA55" s="36" t="n"/>
+      <c r="AB55" s="36" t="n"/>
+      <c r="AC55" s="36" t="n"/>
+      <c r="AD55" s="36" t="n"/>
+      <c r="AE55" s="36" t="n"/>
+      <c r="AF55" s="36" t="n"/>
+      <c r="AG55" s="36" t="n"/>
+      <c r="AH55" s="36" t="n"/>
+      <c r="AI55" s="36" t="n"/>
+      <c r="AJ55" s="36" t="n"/>
+      <c r="AK55" s="31" t="n"/>
+      <c r="AL55" s="31" t="n"/>
+      <c r="AM55" s="31" t="n"/>
+      <c r="AN55" s="31" t="n"/>
+      <c r="AO55" s="31" t="n"/>
+      <c r="AP55" s="31" t="n"/>
+      <c r="AQ55" s="31" t="n"/>
+      <c r="AR55" s="31" t="n"/>
+      <c r="AS55" s="31" t="n"/>
+      <c r="AT55" s="31" t="n"/>
+      <c r="AU55" s="31" t="n"/>
+      <c r="AV55" s="31" t="n"/>
+      <c r="AW55" s="31" t="n"/>
+      <c r="AX55" s="31" t="n"/>
+      <c r="AY55" s="31" t="n"/>
+      <c r="AZ55" s="31" t="n"/>
+      <c r="BA55" s="31" t="n"/>
+      <c r="BB55" s="31" t="n"/>
+      <c r="BC55" s="31" t="n"/>
+      <c r="BD55" s="31" t="n"/>
+      <c r="BE55" s="31" t="n"/>
+      <c r="BF55" s="31" t="n"/>
+      <c r="BG55" s="31" t="n"/>
+      <c r="BH55" s="31" t="n"/>
+      <c r="BI55" s="31" t="n"/>
+      <c r="BJ55" s="31" t="n"/>
+      <c r="BK55" s="31" t="n"/>
+      <c r="BL55" s="31" t="n"/>
+      <c r="BM55" s="31" t="n"/>
+      <c r="BN55" s="31" t="n"/>
+      <c r="BO55" s="31" t="n"/>
+      <c r="BP55" s="31" t="n"/>
+      <c r="BQ55" s="31" t="n"/>
+      <c r="BR55" s="31" t="n"/>
+      <c r="BS55" s="31" t="n"/>
+      <c r="BT55" s="31" t="n"/>
+      <c r="BU55" s="31" t="n"/>
+      <c r="BV55" s="31" t="n"/>
+      <c r="BW55" s="31" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="31" t="n"/>
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="36" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
+      <c r="I56" s="36" t="n"/>
+      <c r="J56" s="36" t="n"/>
+      <c r="K56" s="36" t="n"/>
+      <c r="L56" s="36" t="n"/>
+      <c r="M56" s="36" t="n"/>
+      <c r="N56" s="36" t="n"/>
+      <c r="O56" s="36" t="n"/>
+      <c r="P56" s="36" t="n"/>
+      <c r="Q56" s="36" t="n"/>
+      <c r="R56" s="36" t="n"/>
+      <c r="S56" s="36" t="n"/>
+      <c r="T56" s="36" t="n"/>
+      <c r="U56" s="36" t="n"/>
+      <c r="V56" s="36" t="n"/>
+      <c r="W56" s="36" t="n"/>
+      <c r="X56" s="36" t="n"/>
+      <c r="Y56" s="36" t="n"/>
+      <c r="Z56" s="36" t="n"/>
+      <c r="AA56" s="36" t="n"/>
+      <c r="AB56" s="36" t="n"/>
+      <c r="AC56" s="36" t="n"/>
+      <c r="AD56" s="36" t="n"/>
+      <c r="AE56" s="36" t="n"/>
+      <c r="AF56" s="36" t="n"/>
+      <c r="AG56" s="36" t="n"/>
+      <c r="AH56" s="36" t="n"/>
+      <c r="AI56" s="36" t="n"/>
+      <c r="AJ56" s="36" t="n"/>
+      <c r="AK56" s="31" t="n"/>
+      <c r="AL56" s="31" t="n"/>
+      <c r="AM56" s="31" t="n"/>
+      <c r="AN56" s="31" t="n"/>
+      <c r="AO56" s="31" t="n"/>
+      <c r="AP56" s="31" t="n"/>
+      <c r="AQ56" s="31" t="n"/>
+      <c r="AR56" s="31" t="n"/>
+      <c r="AS56" s="31" t="n"/>
+      <c r="AT56" s="31" t="n"/>
+      <c r="AU56" s="31" t="n"/>
+      <c r="AV56" s="31" t="n"/>
+      <c r="AW56" s="31" t="n"/>
+      <c r="AX56" s="31" t="n"/>
+      <c r="AY56" s="31" t="n"/>
+      <c r="AZ56" s="31" t="n"/>
+      <c r="BA56" s="31" t="n"/>
+      <c r="BB56" s="31" t="n"/>
+      <c r="BC56" s="31" t="n"/>
+      <c r="BD56" s="31" t="n"/>
+      <c r="BE56" s="31" t="n"/>
+      <c r="BF56" s="31" t="n"/>
+      <c r="BG56" s="31" t="n"/>
+      <c r="BH56" s="31" t="n"/>
+      <c r="BI56" s="31" t="n"/>
+      <c r="BJ56" s="31" t="n"/>
+      <c r="BK56" s="31" t="n"/>
+      <c r="BL56" s="31" t="n"/>
+      <c r="BM56" s="31" t="n"/>
+      <c r="BN56" s="31" t="n"/>
+      <c r="BO56" s="31" t="n"/>
+      <c r="BP56" s="31" t="n"/>
+      <c r="BQ56" s="31" t="n"/>
+      <c r="BR56" s="31" t="n"/>
+      <c r="BS56" s="31" t="n"/>
+      <c r="BT56" s="31" t="n"/>
+      <c r="BU56" s="31" t="n"/>
+      <c r="BV56" s="31" t="n"/>
+      <c r="BW56" s="31" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="36" t="n"/>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="36" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="36" t="n"/>
+      <c r="I57" s="36" t="n"/>
+      <c r="J57" s="36" t="n"/>
+      <c r="K57" s="36" t="n"/>
+      <c r="L57" s="36" t="n"/>
+      <c r="M57" s="36" t="n"/>
+      <c r="N57" s="36" t="n"/>
+      <c r="O57" s="36" t="n"/>
+      <c r="P57" s="36" t="n"/>
+      <c r="Q57" s="36" t="n"/>
+      <c r="R57" s="36" t="n"/>
+      <c r="S57" s="36" t="n"/>
+      <c r="T57" s="36" t="n"/>
+      <c r="U57" s="36" t="n"/>
+      <c r="V57" s="36" t="n"/>
+      <c r="W57" s="36" t="n"/>
+      <c r="X57" s="36" t="n"/>
+      <c r="Y57" s="36" t="n"/>
+      <c r="Z57" s="36" t="n"/>
+      <c r="AA57" s="36" t="n"/>
+      <c r="AB57" s="36" t="n"/>
+      <c r="AC57" s="36" t="n"/>
+      <c r="AD57" s="36" t="n"/>
+      <c r="AE57" s="36" t="n"/>
+      <c r="AF57" s="36" t="n"/>
+      <c r="AG57" s="36" t="n"/>
+      <c r="AH57" s="36" t="n"/>
+      <c r="AI57" s="36" t="n"/>
+      <c r="AJ57" s="36" t="n"/>
+      <c r="AK57" s="31" t="n"/>
+      <c r="AL57" s="31" t="n"/>
+      <c r="AM57" s="31" t="n"/>
+      <c r="AN57" s="31" t="n"/>
+      <c r="AO57" s="31" t="n"/>
+      <c r="AP57" s="31" t="n"/>
+      <c r="AQ57" s="31" t="n"/>
+      <c r="AR57" s="31" t="n"/>
+      <c r="AS57" s="31" t="n"/>
+      <c r="AT57" s="31" t="n"/>
+      <c r="AU57" s="31" t="n"/>
+      <c r="AV57" s="31" t="n"/>
+      <c r="AW57" s="31" t="n"/>
+      <c r="AX57" s="31" t="n"/>
+      <c r="AY57" s="31" t="n"/>
+      <c r="AZ57" s="31" t="n"/>
+      <c r="BA57" s="31" t="n"/>
+      <c r="BB57" s="31" t="n"/>
+      <c r="BC57" s="31" t="n"/>
+      <c r="BD57" s="31" t="n"/>
+      <c r="BE57" s="31" t="n"/>
+      <c r="BF57" s="31" t="n"/>
+      <c r="BG57" s="31" t="n"/>
+      <c r="BH57" s="31" t="n"/>
+      <c r="BI57" s="31" t="n"/>
+      <c r="BJ57" s="31" t="n"/>
+      <c r="BK57" s="31" t="n"/>
+      <c r="BL57" s="31" t="n"/>
+      <c r="BM57" s="31" t="n"/>
+      <c r="BN57" s="31" t="n"/>
+      <c r="BO57" s="31" t="n"/>
+      <c r="BP57" s="31" t="n"/>
+      <c r="BQ57" s="31" t="n"/>
+      <c r="BR57" s="31" t="n"/>
+      <c r="BS57" s="31" t="n"/>
+      <c r="BT57" s="31" t="n"/>
+      <c r="BU57" s="31" t="n"/>
+      <c r="BV57" s="31" t="n"/>
+      <c r="BW57" s="31" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="36" t="n"/>
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="36" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="36" t="n"/>
+      <c r="I58" s="36" t="n"/>
+      <c r="J58" s="36" t="n"/>
+      <c r="K58" s="36" t="n"/>
+      <c r="L58" s="36" t="n"/>
+      <c r="M58" s="36" t="n"/>
+      <c r="N58" s="36" t="n"/>
+      <c r="O58" s="36" t="n"/>
+      <c r="P58" s="36" t="n"/>
+      <c r="Q58" s="36" t="n"/>
+      <c r="R58" s="36" t="n"/>
+      <c r="S58" s="36" t="n"/>
+      <c r="T58" s="36" t="n"/>
+      <c r="U58" s="36" t="n"/>
+      <c r="V58" s="36" t="n"/>
+      <c r="W58" s="36" t="n"/>
+      <c r="X58" s="36" t="n"/>
+      <c r="Y58" s="36" t="n"/>
+      <c r="Z58" s="36" t="n"/>
+      <c r="AA58" s="36" t="n"/>
+      <c r="AB58" s="36" t="n"/>
+      <c r="AC58" s="36" t="n"/>
+      <c r="AD58" s="36" t="n"/>
+      <c r="AE58" s="36" t="n"/>
+      <c r="AF58" s="36" t="n"/>
+      <c r="AG58" s="36" t="n"/>
+      <c r="AH58" s="36" t="n"/>
+      <c r="AI58" s="36" t="n"/>
+      <c r="AJ58" s="36" t="n"/>
+      <c r="AK58" s="31" t="n"/>
+      <c r="AL58" s="31" t="n"/>
+      <c r="AM58" s="31" t="n"/>
+      <c r="AN58" s="31" t="n"/>
+      <c r="AO58" s="31" t="n"/>
+      <c r="AP58" s="31" t="n"/>
+      <c r="AQ58" s="31" t="n"/>
+      <c r="AR58" s="31" t="n"/>
+      <c r="AS58" s="31" t="n"/>
+      <c r="AT58" s="31" t="n"/>
+      <c r="AU58" s="31" t="n"/>
+      <c r="AV58" s="31" t="n"/>
+      <c r="AW58" s="31" t="n"/>
+      <c r="AX58" s="31" t="n"/>
+      <c r="AY58" s="31" t="n"/>
+      <c r="AZ58" s="31" t="n"/>
+      <c r="BA58" s="31" t="n"/>
+      <c r="BB58" s="31" t="n"/>
+      <c r="BC58" s="31" t="n"/>
+      <c r="BD58" s="31" t="n"/>
+      <c r="BE58" s="31" t="n"/>
+      <c r="BF58" s="31" t="n"/>
+      <c r="BG58" s="31" t="n"/>
+      <c r="BH58" s="31" t="n"/>
+      <c r="BI58" s="31" t="n"/>
+      <c r="BJ58" s="31" t="n"/>
+      <c r="BK58" s="31" t="n"/>
+      <c r="BL58" s="31" t="n"/>
+      <c r="BM58" s="31" t="n"/>
+      <c r="BN58" s="31" t="n"/>
+      <c r="BO58" s="31" t="n"/>
+      <c r="BP58" s="31" t="n"/>
+      <c r="BQ58" s="31" t="n"/>
+      <c r="BR58" s="31" t="n"/>
+      <c r="BS58" s="31" t="n"/>
+      <c r="BT58" s="31" t="n"/>
+      <c r="BU58" s="31" t="n"/>
+      <c r="BV58" s="31" t="n"/>
+      <c r="BW58" s="31" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="E19:AG20"/>
+    <mergeCell ref="E35:AG36"/>
+    <mergeCell ref="P48:Z49"/>
+    <mergeCell ref="E31:AG32"/>
+    <mergeCell ref="B1:AJ2"/>
+    <mergeCell ref="E27:AG28"/>
+    <mergeCell ref="B15:AJ16"/>
+    <mergeCell ref="B48:O50"/>
+    <mergeCell ref="V10:AJ11"/>
+    <mergeCell ref="P45:Z46"/>
+    <mergeCell ref="E25:AG26"/>
+    <mergeCell ref="B4:AJ5"/>
+    <mergeCell ref="E21:AG22"/>
+    <mergeCell ref="B6:L8"/>
+    <mergeCell ref="E37:AG38"/>
+    <mergeCell ref="B41:AJ42"/>
+    <mergeCell ref="E33:AG34"/>
+    <mergeCell ref="E29:AG30"/>
+    <mergeCell ref="E23:AG24"/>
+    <mergeCell ref="B45:O47"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1169,84 +5917,984 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B14"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="1" max="1"/>
+    <col width="2.77734375" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="3" max="3"/>
+    <col width="2.77734375" customWidth="1" min="4" max="4"/>
+    <col width="2.77734375" customWidth="1" min="5" max="5"/>
+    <col width="2.77734375" customWidth="1" min="6" max="6"/>
+    <col width="2.77734375" customWidth="1" min="7" max="7"/>
+    <col width="2.77734375" customWidth="1" min="8" max="8"/>
+    <col width="2.77734375" customWidth="1" min="9" max="9"/>
+    <col width="2.77734375" customWidth="1" min="10" max="10"/>
+    <col width="2.77734375" customWidth="1" min="11" max="11"/>
+    <col width="2.77734375" customWidth="1" min="12" max="12"/>
+    <col width="2.77734375" customWidth="1" min="13" max="13"/>
+    <col width="2.77734375" customWidth="1" min="14" max="14"/>
+    <col width="2.77734375" customWidth="1" min="15" max="15"/>
+    <col width="2.77734375" customWidth="1" min="16" max="16"/>
+    <col width="2.77734375" customWidth="1" min="17" max="17"/>
+    <col width="2.77734375" customWidth="1" min="18" max="18"/>
+    <col width="2.77734375" customWidth="1" min="19" max="19"/>
+    <col width="2.77734375" customWidth="1" min="20" max="20"/>
+    <col width="2.77734375" customWidth="1" min="21" max="21"/>
+    <col width="2.77734375" customWidth="1" min="22" max="22"/>
+    <col width="2.77734375" customWidth="1" min="23" max="23"/>
+    <col width="2.77734375" customWidth="1" min="24" max="24"/>
+    <col width="2.77734375" customWidth="1" min="25" max="25"/>
+    <col width="2.77734375" customWidth="1" min="26" max="26"/>
+    <col width="2.77734375" customWidth="1" min="27" max="27"/>
+    <col width="2.77734375" customWidth="1" min="28" max="28"/>
+    <col width="2.77734375" customWidth="1" min="29" max="29"/>
+    <col width="2.77734375" customWidth="1" min="30" max="30"/>
+    <col width="2.77734375" customWidth="1" min="31" max="31"/>
+    <col width="2.77734375" customWidth="1" min="32" max="32"/>
+    <col width="2.77734375" customWidth="1" min="33" max="33"/>
+    <col width="2.77734375" customWidth="1" min="34" max="34"/>
+    <col width="2.77734375" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>※ 黄色ハイライト＝今回の変更箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
+    <row r="1" ht="29.25" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>大日産業株式会社</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="21" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="21" t="n"/>
+      <c r="J1" s="21" t="n"/>
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="21" t="n"/>
+      <c r="M1" s="21" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="21" t="n"/>
+      <c r="P1" s="21" t="n"/>
+      <c r="Q1" s="21" t="n"/>
+      <c r="R1" s="21" t="n"/>
+      <c r="S1" s="21" t="n"/>
+      <c r="T1" s="21" t="n"/>
+      <c r="U1" s="21" t="n"/>
+      <c r="V1" s="21" t="n"/>
+      <c r="W1" s="21" t="n"/>
+      <c r="X1" s="21" t="n"/>
+      <c r="Y1" s="21" t="n"/>
+      <c r="Z1" s="21" t="n"/>
+      <c r="AA1" s="21" t="n"/>
+      <c r="AB1" s="21" t="n"/>
+      <c r="AC1" s="21" t="n"/>
+      <c r="AD1" s="21" t="n"/>
+      <c r="AE1" s="21" t="n"/>
+      <c r="AF1" s="21" t="n"/>
+      <c r="AG1" s="21" t="n"/>
+      <c r="AH1" s="21" t="n"/>
+      <c r="AI1" s="21" t="n"/>
+    </row>
+    <row r="2" ht="29.25" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>総務担当者殿</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="21" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="21" t="n"/>
+      <c r="P2" s="21" t="n"/>
+      <c r="Q2" s="21" t="n"/>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+      <c r="U2" s="21" t="n"/>
+      <c r="V2" s="21" t="n"/>
+      <c r="W2" s="21" t="n"/>
+      <c r="X2" s="21" t="n"/>
+      <c r="Y2" s="21" t="n"/>
+      <c r="Z2" s="21" t="n"/>
+      <c r="AA2" s="21" t="n"/>
+      <c r="AB2" s="21" t="n"/>
+      <c r="AC2" s="21" t="n"/>
+      <c r="AD2" s="21" t="n"/>
+      <c r="AE2" s="21" t="n"/>
+      <c r="AF2" s="21" t="n"/>
+      <c r="AG2" s="21" t="n"/>
+      <c r="AH2" s="21" t="n"/>
+      <c r="AI2" s="21" t="n"/>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>届出書⑨-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="29.25" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="21" t="n"/>
+      <c r="M5" s="21" t="n"/>
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="21" t="n"/>
+      <c r="P5" s="21" t="n"/>
+      <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="n"/>
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="21" t="n"/>
+      <c r="U5" s="21" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="21" t="n"/>
+      <c r="X5" s="21" t="n"/>
+      <c r="Y5" s="21" t="n"/>
+      <c r="Z5" s="21" t="n"/>
+      <c r="AA5" s="21" t="n"/>
+      <c r="AB5" s="21" t="n"/>
+      <c r="AC5" s="21" t="n"/>
+      <c r="AD5" s="21" t="n"/>
+      <c r="AE5" s="21" t="n"/>
+      <c r="AF5" s="21" t="n"/>
+      <c r="AG5" s="21" t="n"/>
+      <c r="AH5" s="21" t="n"/>
+      <c r="AI5" s="21" t="n"/>
+    </row>
+    <row r="6" ht="29.25" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>物品借用書</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">令和　　　年　　　月　　　日　　　氏名　　　　　　㊞　　所属　　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="21" t="n"/>
+      <c r="Y7" s="21" t="n"/>
+      <c r="Z7" s="21" t="n"/>
+      <c r="AA7" s="21" t="n"/>
+      <c r="AB7" s="21" t="n"/>
+      <c r="AC7" s="21" t="n"/>
+      <c r="AD7" s="21" t="n"/>
+      <c r="AE7" s="21" t="n"/>
+      <c r="AF7" s="21" t="n"/>
+      <c r="AG7" s="21" t="n"/>
+      <c r="AH7" s="21" t="n"/>
+      <c r="AI7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="29.25" customHeight="1">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="Z8" s="25" t="n"/>
+      <c r="AA8" s="25" t="n"/>
+      <c r="AB8" s="25" t="n"/>
+      <c r="AC8" s="25" t="n"/>
+      <c r="AD8" s="25" t="n"/>
+      <c r="AE8" s="25" t="n"/>
+      <c r="AF8" s="25" t="n"/>
+      <c r="AG8" s="25" t="n"/>
+      <c r="AH8" s="25" t="n"/>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29.25" customHeight="1">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="21" t="n"/>
+      <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>所属</t>
+        </is>
+      </c>
+      <c r="Z9" s="25" t="n"/>
+      <c r="AA9" s="25" t="n"/>
+      <c r="AB9" s="25" t="n"/>
+      <c r="AC9" s="25" t="n"/>
+      <c r="AD9" s="25" t="n"/>
+      <c r="AE9" s="25" t="n"/>
+      <c r="AF9" s="25" t="n"/>
+      <c r="AG9" s="25" t="n"/>
+      <c r="AH9" s="25" t="n"/>
+      <c r="AI9" s="25" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
+      <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+      <c r="U10" s="21" t="n"/>
+      <c r="V10" s="21" t="n"/>
+      <c r="W10" s="21" t="n"/>
+      <c r="X10" s="21" t="n"/>
+      <c r="Y10" s="21" t="n"/>
+      <c r="Z10" s="21" t="n"/>
+      <c r="AA10" s="21" t="n"/>
+      <c r="AB10" s="21" t="n"/>
+      <c r="AC10" s="21" t="n"/>
+      <c r="AD10" s="21" t="n"/>
+      <c r="AE10" s="21" t="n"/>
+      <c r="AF10" s="21" t="n"/>
+      <c r="AG10" s="21" t="n"/>
+      <c r="AH10" s="21" t="n"/>
+      <c r="AI10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="29.25" customHeight="1">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>私は、下記の物品を下記のとおりお借り入れます。</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>1. 使用目的　／　2. 借用期間　／　3. 借用物品　／　5. 備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>【留意点】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="21" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="21" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="21" t="n"/>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="21" t="n"/>
+      <c r="AF11" s="21" t="n"/>
+      <c r="AG11" s="21" t="n"/>
+      <c r="AH11" s="21" t="n"/>
+      <c r="AI11" s="21" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="21" t="n"/>
+      <c r="P12" s="21" t="n"/>
+      <c r="Q12" s="21" t="n"/>
+      <c r="R12" s="21" t="n"/>
+      <c r="S12" s="21" t="n"/>
+      <c r="T12" s="21" t="n"/>
+      <c r="U12" s="21" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="21" t="n"/>
+      <c r="X12" s="21" t="n"/>
+      <c r="Y12" s="21" t="n"/>
+      <c r="Z12" s="21" t="n"/>
+      <c r="AA12" s="21" t="n"/>
+      <c r="AB12" s="21" t="n"/>
+      <c r="AC12" s="21" t="n"/>
+      <c r="AD12" s="21" t="n"/>
+      <c r="AE12" s="21" t="n"/>
+      <c r="AF12" s="21" t="n"/>
+      <c r="AG12" s="21" t="n"/>
+      <c r="AH12" s="21" t="n"/>
+      <c r="AI12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="29.25" customHeight="1">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>1.使用目的</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="42" t="n"/>
+      <c r="J13" s="42" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="L13" s="42" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="42" t="n"/>
+      <c r="O13" s="42" t="n"/>
+      <c r="P13" s="42" t="n"/>
+      <c r="Q13" s="42" t="n"/>
+      <c r="R13" s="42" t="n"/>
+      <c r="S13" s="42" t="n"/>
+      <c r="T13" s="42" t="n"/>
+      <c r="U13" s="42" t="n"/>
+      <c r="V13" s="42" t="n"/>
+      <c r="W13" s="42" t="n"/>
+      <c r="X13" s="42" t="n"/>
+      <c r="Y13" s="42" t="n"/>
+      <c r="Z13" s="42" t="n"/>
+      <c r="AA13" s="42" t="n"/>
+      <c r="AB13" s="42" t="n"/>
+      <c r="AC13" s="42" t="n"/>
+      <c r="AD13" s="42" t="n"/>
+      <c r="AE13" s="42" t="n"/>
+      <c r="AF13" s="42" t="n"/>
+      <c r="AG13" s="42" t="n"/>
+      <c r="AH13" s="42" t="n"/>
+      <c r="AI13" s="42" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="21" t="n"/>
+      <c r="P14" s="21" t="n"/>
+      <c r="Q14" s="21" t="n"/>
+      <c r="R14" s="21" t="n"/>
+      <c r="S14" s="21" t="n"/>
+      <c r="T14" s="21" t="n"/>
+      <c r="U14" s="21" t="n"/>
+      <c r="V14" s="21" t="n"/>
+      <c r="W14" s="21" t="n"/>
+      <c r="X14" s="21" t="n"/>
+      <c r="Y14" s="21" t="n"/>
+      <c r="Z14" s="21" t="n"/>
+      <c r="AA14" s="21" t="n"/>
+      <c r="AB14" s="21" t="n"/>
+      <c r="AC14" s="21" t="n"/>
+      <c r="AD14" s="21" t="n"/>
+      <c r="AE14" s="21" t="n"/>
+      <c r="AF14" s="21" t="n"/>
+      <c r="AG14" s="21" t="n"/>
+      <c r="AH14" s="21" t="n"/>
+      <c r="AI14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="29.25" customHeight="1">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>2.借用機関　自　令和　　　年　　　月　　　日　　 ～ 　　至　令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="21" t="n"/>
+      <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
+      <c r="R15" s="21" t="n"/>
+      <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+      <c r="U15" s="21" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="21" t="n"/>
+      <c r="X15" s="21" t="n"/>
+      <c r="Y15" s="21" t="n"/>
+      <c r="Z15" s="21" t="n"/>
+      <c r="AA15" s="21" t="n"/>
+      <c r="AB15" s="21" t="n"/>
+      <c r="AC15" s="21" t="n"/>
+      <c r="AD15" s="21" t="n"/>
+      <c r="AE15" s="21" t="n"/>
+      <c r="AF15" s="21" t="n"/>
+      <c r="AG15" s="21" t="n"/>
+      <c r="AH15" s="21" t="n"/>
+      <c r="AI15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="21" t="n"/>
+      <c r="L16" s="21" t="n"/>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="21" t="n"/>
+      <c r="O16" s="21" t="n"/>
+      <c r="P16" s="21" t="n"/>
+      <c r="Q16" s="21" t="n"/>
+      <c r="R16" s="21" t="n"/>
+      <c r="S16" s="21" t="n"/>
+      <c r="T16" s="21" t="n"/>
+      <c r="U16" s="21" t="n"/>
+      <c r="V16" s="21" t="n"/>
+      <c r="W16" s="21" t="n"/>
+      <c r="X16" s="21" t="n"/>
+      <c r="Y16" s="21" t="n"/>
+      <c r="Z16" s="21" t="n"/>
+      <c r="AA16" s="21" t="n"/>
+      <c r="AB16" s="21" t="n"/>
+      <c r="AC16" s="21" t="n"/>
+      <c r="AD16" s="21" t="n"/>
+      <c r="AE16" s="21" t="n"/>
+      <c r="AF16" s="21" t="n"/>
+      <c r="AG16" s="21" t="n"/>
+      <c r="AH16" s="21" t="n"/>
+      <c r="AI16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="29.25" customHeight="1">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>3.借用物品</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n"/>
+      <c r="I17" s="42" t="n"/>
+      <c r="J17" s="42" t="n"/>
+      <c r="K17" s="42" t="n"/>
+      <c r="L17" s="42" t="n"/>
+      <c r="M17" s="42" t="n"/>
+      <c r="N17" s="42" t="n"/>
+      <c r="O17" s="42" t="n"/>
+      <c r="P17" s="42" t="n"/>
+      <c r="Q17" s="42" t="n"/>
+      <c r="R17" s="42" t="n"/>
+      <c r="S17" s="42" t="n"/>
+      <c r="T17" s="42" t="n"/>
+      <c r="U17" s="42" t="n"/>
+      <c r="V17" s="42" t="n"/>
+      <c r="W17" s="42" t="n"/>
+      <c r="X17" s="42" t="n"/>
+      <c r="Y17" s="42" t="n"/>
+      <c r="Z17" s="42" t="n"/>
+      <c r="AA17" s="42" t="n"/>
+      <c r="AB17" s="42" t="n"/>
+      <c r="AC17" s="42" t="n"/>
+      <c r="AD17" s="42" t="n"/>
+      <c r="AE17" s="42" t="n"/>
+      <c r="AF17" s="42" t="n"/>
+      <c r="AG17" s="42" t="n"/>
+      <c r="AH17" s="42" t="n"/>
+      <c r="AI17" s="42" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="21" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="21" t="n"/>
+      <c r="O18" s="21" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
+      <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="21" t="n"/>
+      <c r="X18" s="21" t="n"/>
+      <c r="Y18" s="21" t="n"/>
+      <c r="Z18" s="21" t="n"/>
+      <c r="AA18" s="21" t="n"/>
+      <c r="AB18" s="21" t="n"/>
+      <c r="AC18" s="21" t="n"/>
+      <c r="AD18" s="21" t="n"/>
+      <c r="AE18" s="21" t="n"/>
+      <c r="AF18" s="21" t="n"/>
+      <c r="AG18" s="21" t="n"/>
+      <c r="AH18" s="21" t="n"/>
+      <c r="AI18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="29.25" customHeight="1">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>４.留意点</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="21" t="n"/>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="21" t="n"/>
+      <c r="O19" s="21" t="n"/>
+      <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
+      <c r="R19" s="21" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+      <c r="U19" s="21" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="21" t="n"/>
+      <c r="X19" s="21" t="n"/>
+      <c r="Y19" s="21" t="n"/>
+      <c r="Z19" s="21" t="n"/>
+      <c r="AA19" s="21" t="n"/>
+      <c r="AB19" s="21" t="n"/>
+      <c r="AC19" s="21" t="n"/>
+      <c r="AD19" s="21" t="n"/>
+      <c r="AE19" s="21" t="n"/>
+      <c r="AF19" s="21" t="n"/>
+      <c r="AG19" s="21" t="n"/>
+      <c r="AH19" s="21" t="n"/>
+      <c r="AI19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="29.25" customHeight="1">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>・使用目的に沿って使用してください。</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>・本人限り使用可。他に貸与・貸出する行為は禁止です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>・使用の必要がなくなった場合は速やかに本社総務まで返納してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="29" customHeight="1">
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>・故意又は重大な過失により紛失・破損した場合は、会社に生じた現実の損害の範囲で、相当な限度において負担していただくことがあります。</t>
-        </is>
-      </c>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="42" t="n"/>
+      <c r="O20" s="42" t="n"/>
+      <c r="P20" s="42" t="n"/>
+      <c r="Q20" s="42" t="n"/>
+      <c r="R20" s="42" t="n"/>
+      <c r="S20" s="42" t="n"/>
+      <c r="T20" s="42" t="n"/>
+      <c r="U20" s="42" t="n"/>
+      <c r="V20" s="42" t="n"/>
+      <c r="W20" s="42" t="n"/>
+      <c r="X20" s="42" t="n"/>
+      <c r="Y20" s="42" t="n"/>
+      <c r="Z20" s="42" t="n"/>
+      <c r="AA20" s="42" t="n"/>
+      <c r="AB20" s="42" t="n"/>
+      <c r="AC20" s="42" t="n"/>
+      <c r="AD20" s="42" t="n"/>
+      <c r="AE20" s="42" t="n"/>
+      <c r="AF20" s="42" t="n"/>
+      <c r="AG20" s="42" t="n"/>
+      <c r="AH20" s="42" t="n"/>
+      <c r="AI20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="29.25" customHeight="1">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>・本人限り使用可となりますので、他に貸与・貸出する行為は禁止です。</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="42" t="n"/>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="42" t="n"/>
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="42" t="n"/>
+      <c r="N21" s="42" t="n"/>
+      <c r="O21" s="42" t="n"/>
+      <c r="P21" s="42" t="n"/>
+      <c r="Q21" s="42" t="n"/>
+      <c r="R21" s="42" t="n"/>
+      <c r="S21" s="42" t="n"/>
+      <c r="T21" s="42" t="n"/>
+      <c r="U21" s="42" t="n"/>
+      <c r="V21" s="42" t="n"/>
+      <c r="W21" s="42" t="n"/>
+      <c r="X21" s="42" t="n"/>
+      <c r="Y21" s="42" t="n"/>
+      <c r="Z21" s="42" t="n"/>
+      <c r="AA21" s="42" t="n"/>
+      <c r="AB21" s="42" t="n"/>
+      <c r="AC21" s="42" t="n"/>
+      <c r="AD21" s="42" t="n"/>
+      <c r="AE21" s="42" t="n"/>
+      <c r="AF21" s="42" t="n"/>
+      <c r="AG21" s="42" t="n"/>
+      <c r="AH21" s="42" t="n"/>
+      <c r="AI21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="29.25" customHeight="1">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>・使用する必要がなくなった場合は速やかに、本社総務まで返納してください。</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="25" t="n"/>
+      <c r="O22" s="25" t="n"/>
+      <c r="P22" s="25" t="n"/>
+      <c r="Q22" s="25" t="n"/>
+      <c r="R22" s="25" t="n"/>
+      <c r="S22" s="25" t="n"/>
+      <c r="T22" s="25" t="n"/>
+      <c r="U22" s="25" t="n"/>
+      <c r="V22" s="25" t="n"/>
+      <c r="W22" s="25" t="n"/>
+      <c r="X22" s="25" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="25" t="n"/>
+      <c r="AA22" s="25" t="n"/>
+      <c r="AB22" s="25" t="n"/>
+      <c r="AC22" s="25" t="n"/>
+      <c r="AD22" s="25" t="n"/>
+      <c r="AE22" s="25" t="n"/>
+      <c r="AF22" s="25" t="n"/>
+      <c r="AG22" s="25" t="n"/>
+      <c r="AH22" s="25" t="n"/>
+      <c r="AI22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="29.25" customHeight="1">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>・故意又は重大な過失により紛失・破損した場合は、会社に生じた現実の損害の範囲で相当な限度において負担いただくことがあります。</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
+      <c r="N23" s="25" t="n"/>
+      <c r="O23" s="25" t="n"/>
+      <c r="P23" s="25" t="n"/>
+      <c r="Q23" s="25" t="n"/>
+      <c r="R23" s="25" t="n"/>
+      <c r="S23" s="25" t="n"/>
+      <c r="T23" s="25" t="n"/>
+      <c r="U23" s="25" t="n"/>
+      <c r="V23" s="25" t="n"/>
+      <c r="W23" s="25" t="n"/>
+      <c r="X23" s="25" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="25" t="n"/>
+      <c r="AA23" s="25" t="n"/>
+      <c r="AB23" s="25" t="n"/>
+      <c r="AC23" s="25" t="n"/>
+      <c r="AD23" s="25" t="n"/>
+      <c r="AE23" s="25" t="n"/>
+      <c r="AF23" s="25" t="n"/>
+      <c r="AG23" s="25" t="n"/>
+      <c r="AH23" s="25" t="n"/>
+      <c r="AI23" s="25" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
+      <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="21" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="21" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="21" t="n"/>
+      <c r="X24" s="21" t="n"/>
+      <c r="Y24" s="21" t="n"/>
+      <c r="Z24" s="21" t="n"/>
+      <c r="AA24" s="21" t="n"/>
+      <c r="AB24" s="21" t="n"/>
+      <c r="AC24" s="21" t="n"/>
+      <c r="AD24" s="21" t="n"/>
+      <c r="AE24" s="21" t="n"/>
+      <c r="AF24" s="21" t="n"/>
+      <c r="AG24" s="21" t="n"/>
+      <c r="AH24" s="21" t="n"/>
+      <c r="AI24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="29.25" customHeight="1">
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>5.備考</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="21" t="n"/>
+      <c r="O25" s="21" t="n"/>
+      <c r="P25" s="21" t="n"/>
+      <c r="Q25" s="21" t="n"/>
+      <c r="R25" s="21" t="n"/>
+      <c r="S25" s="21" t="n"/>
+      <c r="T25" s="21" t="n"/>
+      <c r="U25" s="21" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="21" t="n"/>
+      <c r="X25" s="21" t="n"/>
+      <c r="Y25" s="21" t="n"/>
+      <c r="Z25" s="21" t="n"/>
+      <c r="AA25" s="21" t="n"/>
+      <c r="AB25" s="21" t="n"/>
+      <c r="AC25" s="21" t="n"/>
+      <c r="AD25" s="21" t="n"/>
+      <c r="AE25" s="21" t="n"/>
+      <c r="AF25" s="21" t="n"/>
+      <c r="AG25" s="21" t="n"/>
+      <c r="AH25" s="21" t="n"/>
+      <c r="AI25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="29.25" customHeight="1">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="21" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="21" t="n"/>
+      <c r="X26" s="21" t="n"/>
+      <c r="Y26" s="21" t="n"/>
+      <c r="Z26" s="21" t="n"/>
+      <c r="AA26" s="21" t="n"/>
+      <c r="AB26" s="21" t="n"/>
+      <c r="AC26" s="21" t="n"/>
+      <c r="AD26" s="21" t="n"/>
+      <c r="AE26" s="21" t="n"/>
+      <c r="AF26" s="21" t="n"/>
+      <c r="AG26" s="21" t="inlineStr">
+        <is>
+          <t>以上</t>
+        </is>
+      </c>
+      <c r="AH26" s="21" t="n"/>
+      <c r="AI26" s="21" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="A6:AI6"/>
+    <mergeCell ref="A4:AI4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1257,84 +6905,862 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B14"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="1" max="1"/>
+    <col width="2.77734375" customWidth="1" min="2" max="2"/>
+    <col width="2.77734375" customWidth="1" min="3" max="3"/>
+    <col width="2.77734375" customWidth="1" min="4" max="4"/>
+    <col width="2.77734375" customWidth="1" min="5" max="5"/>
+    <col width="2.77734375" customWidth="1" min="6" max="6"/>
+    <col width="2.77734375" customWidth="1" min="7" max="7"/>
+    <col width="2.77734375" customWidth="1" min="8" max="8"/>
+    <col width="2.77734375" customWidth="1" min="9" max="9"/>
+    <col width="2.77734375" customWidth="1" min="10" max="10"/>
+    <col width="2.77734375" customWidth="1" min="11" max="11"/>
+    <col width="2.77734375" customWidth="1" min="12" max="12"/>
+    <col width="2.77734375" customWidth="1" min="13" max="13"/>
+    <col width="2.77734375" customWidth="1" min="14" max="14"/>
+    <col width="2.77734375" customWidth="1" min="15" max="15"/>
+    <col width="2.77734375" customWidth="1" min="16" max="16"/>
+    <col width="2.77734375" customWidth="1" min="17" max="17"/>
+    <col width="2.77734375" customWidth="1" min="18" max="18"/>
+    <col width="2.77734375" customWidth="1" min="19" max="19"/>
+    <col width="2.77734375" customWidth="1" min="20" max="20"/>
+    <col width="2.77734375" customWidth="1" min="21" max="21"/>
+    <col width="2.77734375" customWidth="1" min="22" max="22"/>
+    <col width="2.77734375" customWidth="1" min="23" max="23"/>
+    <col width="2.77734375" customWidth="1" min="24" max="24"/>
+    <col width="2.77734375" customWidth="1" min="25" max="25"/>
+    <col width="2.77734375" customWidth="1" min="26" max="26"/>
+    <col width="2.77734375" customWidth="1" min="27" max="27"/>
+    <col width="2.77734375" customWidth="1" min="28" max="28"/>
+    <col width="2.77734375" customWidth="1" min="29" max="29"/>
+    <col width="2.77734375" customWidth="1" min="30" max="30"/>
+    <col width="2.77734375" customWidth="1" min="31" max="31"/>
+    <col width="2.77734375" customWidth="1" min="32" max="32"/>
+    <col width="2.77734375" customWidth="1" min="33" max="33"/>
+    <col width="2.77734375" customWidth="1" min="34" max="34"/>
+    <col width="2.77734375" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>※ 黄色ハイライト＝今回の変更箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>大日産業株式会社</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="21" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="21" t="n"/>
+      <c r="J1" s="21" t="n"/>
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="21" t="n"/>
+      <c r="M1" s="21" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="21" t="n"/>
+      <c r="P1" s="21" t="n"/>
+      <c r="Q1" s="21" t="n"/>
+      <c r="R1" s="21" t="n"/>
+      <c r="S1" s="21" t="n"/>
+      <c r="T1" s="21" t="n"/>
+      <c r="U1" s="21" t="n"/>
+      <c r="V1" s="21" t="n"/>
+      <c r="W1" s="21" t="n"/>
+      <c r="X1" s="21" t="n"/>
+      <c r="Y1" s="21" t="n"/>
+      <c r="Z1" s="21" t="n"/>
+      <c r="AA1" s="21" t="n"/>
+      <c r="AB1" s="21" t="n"/>
+      <c r="AC1" s="21" t="n"/>
+      <c r="AD1" s="21" t="n"/>
+      <c r="AE1" s="21" t="n"/>
+      <c r="AF1" s="21" t="n"/>
+      <c r="AG1" s="21" t="n"/>
+      <c r="AH1" s="21" t="n"/>
+      <c r="AI1" s="21" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>総務担当者殿</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="21" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="21" t="n"/>
+      <c r="P2" s="21" t="n"/>
+      <c r="Q2" s="21" t="n"/>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+      <c r="U2" s="21" t="n"/>
+      <c r="V2" s="21" t="n"/>
+      <c r="W2" s="21" t="n"/>
+      <c r="X2" s="21" t="n"/>
+      <c r="Y2" s="21" t="n"/>
+      <c r="Z2" s="21" t="n"/>
+      <c r="AA2" s="21" t="n"/>
+      <c r="AB2" s="21" t="n"/>
+      <c r="AC2" s="21" t="n"/>
+      <c r="AD2" s="21" t="n"/>
+      <c r="AE2" s="21" t="n"/>
+      <c r="AF2" s="21" t="n"/>
+      <c r="AG2" s="21" t="n"/>
+      <c r="AH2" s="21" t="n"/>
+      <c r="AI2" s="21" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>届出書⑪-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="21" t="n"/>
+      <c r="M5" s="21" t="n"/>
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="21" t="n"/>
+      <c r="P5" s="21" t="n"/>
+      <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="n"/>
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="21" t="n"/>
+      <c r="U5" s="21" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="21" t="n"/>
+      <c r="X5" s="21" t="n"/>
+      <c r="Y5" s="21" t="n"/>
+      <c r="Z5" s="21" t="n"/>
+      <c r="AA5" s="21" t="n"/>
+      <c r="AB5" s="21" t="n"/>
+      <c r="AC5" s="21" t="n"/>
+      <c r="AD5" s="21" t="n"/>
+      <c r="AE5" s="21" t="n"/>
+      <c r="AF5" s="21" t="n"/>
+      <c r="AG5" s="21" t="n"/>
+      <c r="AH5" s="21" t="n"/>
+      <c r="AI5" s="21" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>メールアドレス申請書</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">令和　　　年　　　月　　　日　　　氏名　　　　　　㊞　　所属　　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>2. 希望アドレス</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　第一希望　[　　　　　　　　　]@eurostar-2000.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　第二希望　[　　　　　　　　　]@eurostar-2000.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>注意：アドレスにはアルファベット・英数字以外は使用しないでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>3. アカウント情報　アカウント名：[　　　　　　　　　]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>※ パスワードは紙には記載しません。初回ログイン時にご本人が設定してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>（旧様式の「パスワード：[　]」記入欄は削除しました）</t>
-        </is>
-      </c>
+    <row r="7">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="21" t="n"/>
+      <c r="Y7" s="21" t="n"/>
+      <c r="Z7" s="21" t="n"/>
+      <c r="AA7" s="21" t="n"/>
+      <c r="AB7" s="21" t="n"/>
+      <c r="AC7" s="21" t="n"/>
+      <c r="AD7" s="21" t="n"/>
+      <c r="AE7" s="21" t="n"/>
+      <c r="AF7" s="21" t="n"/>
+      <c r="AG7" s="21" t="n"/>
+      <c r="AH7" s="21" t="n"/>
+      <c r="AI7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="Z8" s="25" t="n"/>
+      <c r="AA8" s="25" t="n"/>
+      <c r="AB8" s="25" t="n"/>
+      <c r="AC8" s="25" t="n"/>
+      <c r="AD8" s="25" t="n"/>
+      <c r="AE8" s="25" t="n"/>
+      <c r="AF8" s="25" t="n"/>
+      <c r="AG8" s="25" t="n"/>
+      <c r="AH8" s="25" t="n"/>
+      <c r="AI8" s="25" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="21" t="n"/>
+      <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="21" t="n"/>
+      <c r="X9" s="21" t="n"/>
+      <c r="Y9" s="21" t="n"/>
+      <c r="Z9" s="21" t="n"/>
+      <c r="AA9" s="21" t="n"/>
+      <c r="AB9" s="21" t="n"/>
+      <c r="AC9" s="21" t="n"/>
+      <c r="AD9" s="21" t="n"/>
+      <c r="AE9" s="21" t="n"/>
+      <c r="AF9" s="21" t="n"/>
+      <c r="AG9" s="21" t="n"/>
+      <c r="AH9" s="21" t="n"/>
+      <c r="AI9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>1.所属</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
+      <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
+      <c r="U10" s="21" t="n"/>
+      <c r="V10" s="21" t="n"/>
+      <c r="W10" s="21" t="n"/>
+      <c r="X10" s="21" t="n"/>
+      <c r="Y10" s="21" t="n"/>
+      <c r="Z10" s="21" t="n"/>
+      <c r="AA10" s="21" t="n"/>
+      <c r="AB10" s="21" t="n"/>
+      <c r="AC10" s="21" t="n"/>
+      <c r="AD10" s="21" t="n"/>
+      <c r="AE10" s="21" t="n"/>
+      <c r="AF10" s="21" t="n"/>
+      <c r="AG10" s="21" t="n"/>
+      <c r="AH10" s="21" t="n"/>
+      <c r="AI10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="21" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="21" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="21" t="n"/>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="21" t="n"/>
+      <c r="AF11" s="21" t="n"/>
+      <c r="AG11" s="21" t="n"/>
+      <c r="AH11" s="21" t="n"/>
+      <c r="AI11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>２.希望アドレス</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="21" t="n"/>
+      <c r="P12" s="21" t="n"/>
+      <c r="Q12" s="21" t="n"/>
+      <c r="R12" s="21" t="n"/>
+      <c r="S12" s="21" t="n"/>
+      <c r="T12" s="21" t="n"/>
+      <c r="U12" s="21" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="21" t="n"/>
+      <c r="X12" s="21" t="n"/>
+      <c r="Y12" s="21" t="n"/>
+      <c r="Z12" s="21" t="n"/>
+      <c r="AA12" s="21" t="n"/>
+      <c r="AB12" s="21" t="n"/>
+      <c r="AC12" s="21" t="n"/>
+      <c r="AD12" s="21" t="n"/>
+      <c r="AE12" s="21" t="n"/>
+      <c r="AF12" s="21" t="n"/>
+      <c r="AG12" s="21" t="n"/>
+      <c r="AH12" s="21" t="n"/>
+      <c r="AI12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>1)第一希望</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="21" t="n"/>
+      <c r="P13" s="21" t="n"/>
+      <c r="Q13" s="21" t="n"/>
+      <c r="R13" s="21" t="n"/>
+      <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
+      <c r="U13" s="21" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="21" t="n"/>
+      <c r="X13" s="21" t="n"/>
+      <c r="Y13" s="21" t="n"/>
+      <c r="Z13" s="21" t="n"/>
+      <c r="AA13" s="21" t="n"/>
+      <c r="AB13" s="21" t="n"/>
+      <c r="AC13" s="21" t="n"/>
+      <c r="AD13" s="21" t="n"/>
+      <c r="AE13" s="21" t="n"/>
+      <c r="AF13" s="21" t="n"/>
+      <c r="AG13" s="21" t="n"/>
+      <c r="AH13" s="21" t="n"/>
+      <c r="AI13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>[　　　　　　　　　　　　　　　　　　　　]@eurostar-2000.com</t>
+        </is>
+      </c>
+      <c r="AI14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="21" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>2)第二希望</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="21" t="n"/>
+      <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
+      <c r="R15" s="21" t="n"/>
+      <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+      <c r="U15" s="21" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="21" t="n"/>
+      <c r="X15" s="21" t="n"/>
+      <c r="Y15" s="21" t="n"/>
+      <c r="Z15" s="21" t="n"/>
+      <c r="AA15" s="21" t="n"/>
+      <c r="AB15" s="21" t="n"/>
+      <c r="AC15" s="21" t="n"/>
+      <c r="AD15" s="21" t="n"/>
+      <c r="AE15" s="21" t="n"/>
+      <c r="AF15" s="21" t="n"/>
+      <c r="AG15" s="21" t="n"/>
+      <c r="AH15" s="21" t="n"/>
+      <c r="AI15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>[　　　　　　　　　　　　　　　　　　　　]@eurostar-2000.com</t>
+        </is>
+      </c>
+      <c r="AI16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>注意：アドレスにはアルファベット、英数字以外は使用しないでください。</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="21" t="n"/>
+      <c r="L17" s="21" t="n"/>
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="21" t="n"/>
+      <c r="O17" s="21" t="n"/>
+      <c r="P17" s="21" t="n"/>
+      <c r="Q17" s="21" t="n"/>
+      <c r="R17" s="21" t="n"/>
+      <c r="S17" s="21" t="n"/>
+      <c r="T17" s="21" t="n"/>
+      <c r="U17" s="21" t="n"/>
+      <c r="V17" s="21" t="n"/>
+      <c r="W17" s="21" t="n"/>
+      <c r="X17" s="21" t="n"/>
+      <c r="Y17" s="21" t="n"/>
+      <c r="Z17" s="21" t="n"/>
+      <c r="AA17" s="21" t="n"/>
+      <c r="AB17" s="21" t="n"/>
+      <c r="AC17" s="21" t="n"/>
+      <c r="AD17" s="21" t="n"/>
+      <c r="AE17" s="21" t="n"/>
+      <c r="AF17" s="21" t="n"/>
+      <c r="AG17" s="21" t="n"/>
+      <c r="AH17" s="21" t="n"/>
+      <c r="AI17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="21" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="21" t="n"/>
+      <c r="O18" s="21" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
+      <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="21" t="n"/>
+      <c r="X18" s="21" t="n"/>
+      <c r="Y18" s="21" t="n"/>
+      <c r="Z18" s="21" t="n"/>
+      <c r="AA18" s="21" t="n"/>
+      <c r="AB18" s="21" t="n"/>
+      <c r="AC18" s="21" t="n"/>
+      <c r="AD18" s="21" t="n"/>
+      <c r="AE18" s="21" t="n"/>
+      <c r="AF18" s="21" t="n"/>
+      <c r="AG18" s="21" t="n"/>
+      <c r="AH18" s="21" t="n"/>
+      <c r="AI18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>3.アカウント情報</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="21" t="n"/>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="21" t="n"/>
+      <c r="O19" s="21" t="n"/>
+      <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
+      <c r="R19" s="21" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+      <c r="U19" s="21" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="21" t="n"/>
+      <c r="X19" s="21" t="n"/>
+      <c r="Y19" s="21" t="n"/>
+      <c r="Z19" s="21" t="n"/>
+      <c r="AA19" s="21" t="n"/>
+      <c r="AB19" s="21" t="n"/>
+      <c r="AC19" s="21" t="n"/>
+      <c r="AD19" s="21" t="n"/>
+      <c r="AE19" s="21" t="n"/>
+      <c r="AF19" s="21" t="n"/>
+      <c r="AG19" s="21" t="n"/>
+      <c r="AH19" s="21" t="n"/>
+      <c r="AI19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>アカウント名</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>：</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>[</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="21" t="n"/>
+      <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="21" t="n"/>
+      <c r="R20" s="21" t="n"/>
+      <c r="S20" s="21" t="inlineStr">
+        <is>
+          <t>]</t>
+        </is>
+      </c>
+      <c r="T20" s="21" t="n"/>
+      <c r="U20" s="21" t="n"/>
+      <c r="V20" s="21" t="n"/>
+      <c r="W20" s="21" t="n"/>
+      <c r="X20" s="21" t="n"/>
+      <c r="Y20" s="21" t="n"/>
+      <c r="Z20" s="21" t="n"/>
+      <c r="AA20" s="21" t="n"/>
+      <c r="AB20" s="21" t="n"/>
+      <c r="AC20" s="21" t="n"/>
+      <c r="AD20" s="21" t="n"/>
+      <c r="AE20" s="21" t="n"/>
+      <c r="AF20" s="21" t="n"/>
+      <c r="AG20" s="21" t="n"/>
+      <c r="AH20" s="21" t="n"/>
+      <c r="AI20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>※パスワードは初回ログイン時にご本人が設定（紙には記載しません）</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="21" t="n"/>
+      <c r="N21" s="21" t="n"/>
+      <c r="O21" s="21" t="n"/>
+      <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+      <c r="U21" s="21" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="21" t="n"/>
+      <c r="X21" s="21" t="n"/>
+      <c r="Y21" s="21" t="n"/>
+      <c r="Z21" s="21" t="n"/>
+      <c r="AA21" s="21" t="n"/>
+      <c r="AB21" s="21" t="n"/>
+      <c r="AC21" s="21" t="n"/>
+      <c r="AD21" s="21" t="n"/>
+      <c r="AE21" s="21" t="n"/>
+      <c r="AF21" s="21" t="n"/>
+      <c r="AG21" s="21" t="n"/>
+      <c r="AH21" s="21" t="n"/>
+      <c r="AI21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+      <c r="N22" s="42" t="n"/>
+      <c r="O22" s="42" t="n"/>
+      <c r="P22" s="42" t="n"/>
+      <c r="Q22" s="42" t="n"/>
+      <c r="R22" s="42" t="n"/>
+      <c r="S22" s="42" t="n"/>
+      <c r="T22" s="42" t="n"/>
+      <c r="U22" s="42" t="n"/>
+      <c r="V22" s="42" t="n"/>
+      <c r="W22" s="42" t="n"/>
+      <c r="X22" s="42" t="n"/>
+      <c r="Y22" s="42" t="n"/>
+      <c r="Z22" s="42" t="n"/>
+      <c r="AA22" s="42" t="n"/>
+      <c r="AB22" s="42" t="n"/>
+      <c r="AC22" s="42" t="n"/>
+      <c r="AD22" s="42" t="n"/>
+      <c r="AE22" s="42" t="n"/>
+      <c r="AF22" s="42" t="n"/>
+      <c r="AG22" s="42" t="n"/>
+      <c r="AH22" s="42" t="n"/>
+      <c r="AI22" s="42" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="21" t="n"/>
+      <c r="P23" s="21" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="21" t="n"/>
+      <c r="X23" s="21" t="n"/>
+      <c r="Y23" s="21" t="n"/>
+      <c r="Z23" s="21" t="n"/>
+      <c r="AA23" s="21" t="n"/>
+      <c r="AB23" s="21" t="n"/>
+      <c r="AC23" s="21" t="n"/>
+      <c r="AD23" s="21" t="n"/>
+      <c r="AE23" s="21" t="n"/>
+      <c r="AF23" s="21" t="n"/>
+      <c r="AG23" s="21" t="n"/>
+      <c r="AH23" s="21" t="n"/>
+      <c r="AI23" s="21" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
+      <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="21" t="n"/>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="21" t="n"/>
+      <c r="V24" s="21" t="n"/>
+      <c r="W24" s="21" t="n"/>
+      <c r="X24" s="21" t="n"/>
+      <c r="Y24" s="21" t="n"/>
+      <c r="Z24" s="21" t="n"/>
+      <c r="AA24" s="21" t="n"/>
+      <c r="AB24" s="21" t="n"/>
+      <c r="AC24" s="21" t="n"/>
+      <c r="AD24" s="21" t="n"/>
+      <c r="AE24" s="21" t="n"/>
+      <c r="AF24" s="21" t="n"/>
+      <c r="AG24" s="21" t="n"/>
+      <c r="AH24" s="21" t="n"/>
+      <c r="AI24" s="21" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D16:AH16"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="A3:AI3"/>
+    <mergeCell ref="D14:AH14"/>
+    <mergeCell ref="A6:AI6"/>
+    <mergeCell ref="A4:AI4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1345,56 +7771,860 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B9"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13.109375" customWidth="1" min="2" max="2"/>
+    <col width="10.21875" customWidth="1" min="3" max="3"/>
+    <col width="6.88671875" customWidth="1" min="4" max="4"/>
+    <col width="6.88671875" customWidth="1" min="5" max="5"/>
+    <col width="6.88671875" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="11.21875" customWidth="1" min="8" max="8"/>
+    <col width="11.21875" customWidth="1" min="9" max="9"/>
+    <col width="11.21875" customWidth="1" min="10" max="10"/>
+    <col width="11.21875" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>※ 黄色ハイライト＝今回の変更箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="12" t="inlineStr">
+    <row r="1" ht="14.4" customHeight="1">
+      <c r="A1" s="45" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+      <c r="F1" s="45" t="n"/>
+      <c r="G1" s="45" t="n"/>
+      <c r="H1" s="45" t="n"/>
+      <c r="I1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　届出書①1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="45" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　発行　令和　　　 　年　　　　月　   　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>大日産業株式会社</t>
+        </is>
+      </c>
+      <c r="B3" s="45" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+      <c r="F3" s="45" t="n"/>
+      <c r="G3" s="45" t="n"/>
+      <c r="H3" s="45" t="n"/>
+      <c r="I3" s="48" t="n"/>
+      <c r="J3" s="48" t="n"/>
+      <c r="K3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　総務担当者　殿</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>勤務・休暇届出書</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="29" customHeight="1">
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>届出事項（該当にㇾ印）：　□遅刻　□早退　□時間外勤務　□年次有給休暇　□慶弔休暇　□特別休暇　□欠勤　□振替休日出勤　□代休休日出勤</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>《理由》欄について</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="29" customHeight="1">
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>※ 年次有給休暇は取得理由の記入は不要です（労基法39条・時季指定権）。《理由》欄の対象外とします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>※ 《理由》欄は、慶弔休暇・特別休暇・欠勤など理由確認が必要な区分のみ記入してください。</t>
-        </is>
-      </c>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="48" t="n"/>
+      <c r="J4" s="48" t="n"/>
+      <c r="K4" s="48" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="45" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="45" t="n"/>
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="50" t="n"/>
+      <c r="J5" s="45" t="n"/>
+      <c r="K5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>部　署</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>社員</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>バイト</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="inlineStr">
+        <is>
+          <t>派遣</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="n"/>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>社長</t>
+        </is>
+      </c>
+      <c r="I6" s="57" t="inlineStr">
+        <is>
+          <t>専務</t>
+        </is>
+      </c>
+      <c r="J6" s="57" t="inlineStr">
+        <is>
+          <t>上司</t>
+        </is>
+      </c>
+      <c r="K6" s="57" t="inlineStr">
+        <is>
+          <t>部門</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>氏　名</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="n"/>
+      <c r="C7" s="59" t="n"/>
+      <c r="D7" s="59" t="n"/>
+      <c r="E7" s="59" t="n"/>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="61" t="n"/>
+      <c r="J7" s="61" t="n"/>
+      <c r="K7" s="61" t="n"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1">
+      <c r="A8" s="31" t="n"/>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="62" t="n"/>
+      <c r="I8" s="62" t="n"/>
+      <c r="J8" s="62" t="n"/>
+      <c r="K8" s="62" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>届出事項（ㇾ印）</t>
+        </is>
+      </c>
+      <c r="C9" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　内容記入欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□遅刻　　□早退</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="n"/>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　月　　　日　　　時　　　分</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="n"/>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="66" t="n"/>
+      <c r="G10" s="66" t="n"/>
+      <c r="H10" s="66" t="n"/>
+      <c r="I10" s="66" t="n"/>
+      <c r="J10" s="66" t="n"/>
+      <c r="K10" s="53" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□時間外勤務</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="n"/>
+      <c r="C11" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　月　　　日　　　時　　　分　～　　　　時　　　分　（　　　　　時間）</t>
+        </is>
+      </c>
+      <c r="D11" s="68" t="n"/>
+      <c r="E11" s="68" t="n"/>
+      <c r="F11" s="68" t="n"/>
+      <c r="G11" s="68" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="68" t="n"/>
+      <c r="J11" s="68" t="n"/>
+      <c r="K11" s="69" t="n"/>
+    </row>
+    <row r="12" ht="33" customHeight="1">
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="41" t="n"/>
+      <c r="K12" s="71" t="n"/>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□年次有給休暇</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="n"/>
+      <c r="C14" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　令和　 　年　 　月　  　日　～　　　　年　　　月　　　日　（　 　日間）</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="66" t="n"/>
+      <c r="G14" s="66" t="n"/>
+      <c r="H14" s="66" t="n"/>
+      <c r="I14" s="66" t="n"/>
+      <c r="J14" s="66" t="n"/>
+      <c r="K14" s="53" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□慶弔休暇</t>
+        </is>
+      </c>
+      <c r="B15" s="73" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="K15" s="75" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□特別休暇　□欠勤</t>
+        </is>
+      </c>
+      <c r="B16" s="76" t="n"/>
+      <c r="C16" s="77" t="n"/>
+      <c r="D16" s="78" t="n"/>
+      <c r="E16" s="78" t="n"/>
+      <c r="F16" s="78" t="n"/>
+      <c r="G16" s="78" t="n"/>
+      <c r="H16" s="78" t="n"/>
+      <c r="I16" s="78" t="n"/>
+      <c r="J16" s="78" t="n"/>
+      <c r="K16" s="79" t="n"/>
+    </row>
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》　　</t>
+        </is>
+      </c>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+      <c r="G17" s="59" t="n"/>
+      <c r="H17" s="59" t="n"/>
+      <c r="I17" s="59" t="n"/>
+      <c r="J17" s="59" t="n"/>
+      <c r="K17" s="60" t="n"/>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="31" t="n"/>
+      <c r="K18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□振替休日出勤</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="n"/>
+      <c r="C19" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　令和　　　年　　　月　　　日　（　振替休日　　　年　　　月　　　日　）</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="n"/>
+      <c r="E19" s="66" t="n"/>
+      <c r="F19" s="66" t="n"/>
+      <c r="G19" s="66" t="n"/>
+      <c r="H19" s="66" t="n"/>
+      <c r="I19" s="66" t="n"/>
+      <c r="J19" s="66" t="n"/>
+      <c r="K19" s="53" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□代休休日出勤</t>
+        </is>
+      </c>
+      <c r="B20" s="81" t="n"/>
+      <c r="C20" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　休日出勤日　令和　　　年　　　月　　　日　</t>
+        </is>
+      </c>
+      <c r="D20" s="83" t="n"/>
+      <c r="E20" s="83" t="n"/>
+      <c r="F20" s="83" t="n"/>
+      <c r="G20" s="83" t="n"/>
+      <c r="H20" s="83" t="n"/>
+      <c r="I20" s="83" t="n"/>
+      <c r="J20" s="83" t="n"/>
+      <c r="K20" s="81" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="77" t="n"/>
+      <c r="B21" s="79" t="n"/>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　代休日　令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+      <c r="D21" s="78" t="n"/>
+      <c r="E21" s="78" t="n"/>
+      <c r="F21" s="78" t="n"/>
+      <c r="G21" s="78" t="n"/>
+      <c r="H21" s="78" t="n"/>
+      <c r="I21" s="78" t="n"/>
+      <c r="J21" s="78" t="n"/>
+      <c r="K21" s="79" t="n"/>
+    </row>
+    <row r="22" ht="33" customHeight="1">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="41" t="n"/>
+      <c r="J22" s="41" t="n"/>
+      <c r="K22" s="71" t="n"/>
+    </row>
+    <row r="23" ht="10.5" customHeight="1">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="31" t="n"/>
+      <c r="K23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="10.5" customHeight="1">
+      <c r="A24" s="84" t="inlineStr">
+        <is>
+          <t>※年次有給休暇は取得理由の記入は不要です（《理由》欄の対象外・労基法39条）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="14.4" customHeight="1">
+      <c r="A25" s="45" t="n"/>
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="45" t="n"/>
+      <c r="G25" s="45" t="n"/>
+      <c r="H25" s="45" t="n"/>
+      <c r="I25" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　届出書①1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="45" t="n"/>
+      <c r="B26" s="45" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　発行　令和　　　　年　　　　月　　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>大日産業株式会社</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="31" t="n"/>
+      <c r="I27" s="63" t="n"/>
+      <c r="J27" s="63" t="n"/>
+      <c r="K27" s="63" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　総務担当者　殿</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>勤務・休暇届出書</t>
+        </is>
+      </c>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="63" t="n"/>
+      <c r="J28" s="63" t="n"/>
+      <c r="K28" s="63" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="50" t="n"/>
+      <c r="J29" s="31" t="n"/>
+      <c r="K29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>部　署</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>社員</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>バイト</t>
+        </is>
+      </c>
+      <c r="F30" s="56" t="inlineStr">
+        <is>
+          <t>派遣</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="57" t="inlineStr">
+        <is>
+          <t>社長</t>
+        </is>
+      </c>
+      <c r="I30" s="57" t="inlineStr">
+        <is>
+          <t>専務</t>
+        </is>
+      </c>
+      <c r="J30" s="57" t="inlineStr">
+        <is>
+          <t>上司</t>
+        </is>
+      </c>
+      <c r="K30" s="57" t="inlineStr">
+        <is>
+          <t>部門</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="58" t="inlineStr">
+        <is>
+          <t>氏　名</t>
+        </is>
+      </c>
+      <c r="B31" s="80" t="n"/>
+      <c r="C31" s="59" t="n"/>
+      <c r="D31" s="59" t="n"/>
+      <c r="E31" s="59" t="n"/>
+      <c r="F31" s="60" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="57" t="n"/>
+      <c r="I31" s="61" t="n"/>
+      <c r="J31" s="61" t="n"/>
+      <c r="K31" s="61" t="n"/>
+    </row>
+    <row r="32" ht="20.25" customHeight="1">
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="62" t="n"/>
+      <c r="I32" s="62" t="n"/>
+      <c r="J32" s="62" t="n"/>
+      <c r="K32" s="62" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>届出事項（ㇾ印）</t>
+        </is>
+      </c>
+      <c r="C33" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　　内容記入欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□遅刻　　□早退</t>
+        </is>
+      </c>
+      <c r="B34" s="65" t="n"/>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　月　　　日　　　時　　　分</t>
+        </is>
+      </c>
+      <c r="D34" s="66" t="n"/>
+      <c r="E34" s="66" t="n"/>
+      <c r="F34" s="66" t="n"/>
+      <c r="G34" s="66" t="n"/>
+      <c r="H34" s="66" t="n"/>
+      <c r="I34" s="66" t="n"/>
+      <c r="J34" s="66" t="n"/>
+      <c r="K34" s="53" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□時間外勤務</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="n"/>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　月　　　日　　　時　　　分　～　　　　時　　　分　（　　　　　時間）</t>
+        </is>
+      </c>
+      <c r="D35" s="68" t="n"/>
+      <c r="E35" s="68" t="n"/>
+      <c r="F35" s="68" t="n"/>
+      <c r="G35" s="68" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="68" t="n"/>
+      <c r="J35" s="68" t="n"/>
+      <c r="K35" s="69" t="n"/>
+    </row>
+    <row r="36" ht="33" customHeight="1">
+      <c r="A36" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="n"/>
+      <c r="C36" s="41" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="41" t="n"/>
+      <c r="G36" s="41" t="n"/>
+      <c r="H36" s="41" t="n"/>
+      <c r="I36" s="41" t="n"/>
+      <c r="J36" s="41" t="n"/>
+      <c r="K36" s="71" t="n"/>
+    </row>
+    <row r="37" ht="12" customHeight="1">
+      <c r="A37" s="31" t="n"/>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="31" t="n"/>
+      <c r="K37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□年次有給休暇</t>
+        </is>
+      </c>
+      <c r="B38" s="65" t="n"/>
+      <c r="C38" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　令和　　　年　　　月　　　日　～　　　　年　　　月　　　日　（　　　日間）</t>
+        </is>
+      </c>
+      <c r="D38" s="66" t="n"/>
+      <c r="E38" s="66" t="n"/>
+      <c r="F38" s="66" t="n"/>
+      <c r="G38" s="66" t="n"/>
+      <c r="H38" s="66" t="n"/>
+      <c r="I38" s="66" t="n"/>
+      <c r="J38" s="66" t="n"/>
+      <c r="K38" s="53" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□慶弔休暇</t>
+        </is>
+      </c>
+      <c r="B39" s="73" t="n"/>
+      <c r="C39" s="74" t="n"/>
+      <c r="K39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□特別休暇　□欠勤</t>
+        </is>
+      </c>
+      <c r="B40" s="76" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="78" t="n"/>
+      <c r="E40" s="78" t="n"/>
+      <c r="F40" s="78" t="n"/>
+      <c r="G40" s="78" t="n"/>
+      <c r="H40" s="78" t="n"/>
+      <c r="I40" s="78" t="n"/>
+      <c r="J40" s="78" t="n"/>
+      <c r="K40" s="79" t="n"/>
+    </row>
+    <row r="41" ht="33" customHeight="1">
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》</t>
+        </is>
+      </c>
+      <c r="B41" s="59" t="n"/>
+      <c r="C41" s="59" t="n"/>
+      <c r="D41" s="59" t="n"/>
+      <c r="E41" s="59" t="n"/>
+      <c r="F41" s="59" t="n"/>
+      <c r="G41" s="59" t="n"/>
+      <c r="H41" s="59" t="n"/>
+      <c r="I41" s="59" t="n"/>
+      <c r="J41" s="59" t="n"/>
+      <c r="K41" s="60" t="n"/>
+    </row>
+    <row r="42" ht="12" customHeight="1">
+      <c r="A42" s="31" t="n"/>
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="31" t="n"/>
+      <c r="K42" s="31" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□振替休日出勤</t>
+        </is>
+      </c>
+      <c r="B43" s="65" t="n"/>
+      <c r="C43" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　令和　　　年　　　月　　　日　（　振替休日　　　年　　　月　　　日　）</t>
+        </is>
+      </c>
+      <c r="D43" s="66" t="n"/>
+      <c r="E43" s="66" t="n"/>
+      <c r="F43" s="66" t="n"/>
+      <c r="G43" s="66" t="n"/>
+      <c r="H43" s="66" t="n"/>
+      <c r="I43" s="66" t="n"/>
+      <c r="J43" s="66" t="n"/>
+      <c r="K43" s="53" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□代休休日出勤</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="n"/>
+      <c r="C44" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　休日出勤日　令和　　　年　　　月　　　日　</t>
+        </is>
+      </c>
+      <c r="D44" s="83" t="n"/>
+      <c r="E44" s="83" t="n"/>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="83" t="n"/>
+      <c r="H44" s="83" t="n"/>
+      <c r="I44" s="83" t="n"/>
+      <c r="J44" s="83" t="n"/>
+      <c r="K44" s="81" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="77" t="n"/>
+      <c r="B45" s="79" t="n"/>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　代休日　令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+      <c r="D45" s="78" t="n"/>
+      <c r="E45" s="78" t="n"/>
+      <c r="F45" s="78" t="n"/>
+      <c r="G45" s="78" t="n"/>
+      <c r="H45" s="78" t="n"/>
+      <c r="I45" s="78" t="n"/>
+      <c r="J45" s="78" t="n"/>
+      <c r="K45" s="79" t="n"/>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　《理由》</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="n"/>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="41" t="n"/>
+      <c r="E46" s="41" t="n"/>
+      <c r="F46" s="41" t="n"/>
+      <c r="G46" s="41" t="n"/>
+      <c r="H46" s="41" t="n"/>
+      <c r="I46" s="41" t="n"/>
+      <c r="J46" s="41" t="n"/>
+      <c r="K46" s="71" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="C14:K16"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="D4:G5"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="A44:B45"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="D28:G29"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="C38:K40"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="C34:K34"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="C33:K33"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="C35:K35"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="I25:K25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/forms/届出書_法的リスク見直し提案_v2.xlsx
+++ b/forms/届出書_法的リスク見直し提案_v2.xlsx
@@ -403,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -618,6 +618,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1236,10 +1243,11 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>年休は理由欄の対象外と明記、または年休行を理由欄から分離する。</t>
-        </is>
-      </c>
-    </row>
+          <t>年次有給休暇の《理由》欄は「任意記入」とし、記入がなくても取得できる旨を明記する（理由の記入を必須としない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
@@ -1959,128 +1967,128 @@
       <c r="AH23" s="21" t="n"/>
       <c r="AI23" s="21" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="29" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="85" t="inlineStr">
         <is>
           <t>【身元保証】　保証期間：5年（身元保証法の上限）</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="n"/>
-      <c r="T24" s="21" t="n"/>
-      <c r="U24" s="21" t="n"/>
-      <c r="V24" s="21" t="n"/>
-      <c r="W24" s="21" t="n"/>
-      <c r="X24" s="21" t="n"/>
-      <c r="Y24" s="21" t="n"/>
-      <c r="Z24" s="21" t="n"/>
-      <c r="AA24" s="21" t="n"/>
-      <c r="AB24" s="21" t="n"/>
-      <c r="AC24" s="21" t="n"/>
-      <c r="AD24" s="21" t="n"/>
-      <c r="AE24" s="21" t="n"/>
-      <c r="AF24" s="21" t="n"/>
-      <c r="AG24" s="21" t="n"/>
-      <c r="AH24" s="21" t="n"/>
-      <c r="AI24" s="21" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="n"/>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="86" t="n"/>
+      <c r="D24" s="86" t="n"/>
+      <c r="E24" s="86" t="n"/>
+      <c r="F24" s="86" t="n"/>
+      <c r="G24" s="86" t="n"/>
+      <c r="H24" s="86" t="n"/>
+      <c r="I24" s="86" t="n"/>
+      <c r="J24" s="86" t="n"/>
+      <c r="K24" s="86" t="n"/>
+      <c r="L24" s="86" t="n"/>
+      <c r="M24" s="86" t="n"/>
+      <c r="N24" s="86" t="n"/>
+      <c r="O24" s="86" t="n"/>
+      <c r="P24" s="86" t="n"/>
+      <c r="Q24" s="86" t="n"/>
+      <c r="R24" s="86" t="n"/>
+      <c r="S24" s="86" t="n"/>
+      <c r="T24" s="86" t="n"/>
+      <c r="U24" s="86" t="n"/>
+      <c r="V24" s="86" t="n"/>
+      <c r="W24" s="86" t="n"/>
+      <c r="X24" s="86" t="n"/>
+      <c r="Y24" s="86" t="n"/>
+      <c r="Z24" s="86" t="n"/>
+      <c r="AA24" s="86" t="n"/>
+      <c r="AB24" s="86" t="n"/>
+      <c r="AC24" s="86" t="n"/>
+      <c r="AD24" s="86" t="n"/>
+      <c r="AE24" s="86" t="n"/>
+      <c r="AF24" s="86" t="n"/>
+      <c r="AG24" s="86" t="n"/>
+      <c r="AH24" s="86" t="n"/>
+      <c r="AI24" s="86" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　極度額：金　　　　　　　　円</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
-      <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="21" t="n"/>
-      <c r="S25" s="21" t="n"/>
-      <c r="T25" s="21" t="n"/>
-      <c r="U25" s="21" t="n"/>
-      <c r="V25" s="21" t="n"/>
-      <c r="W25" s="21" t="n"/>
-      <c r="X25" s="21" t="n"/>
-      <c r="Y25" s="21" t="n"/>
-      <c r="Z25" s="21" t="n"/>
-      <c r="AA25" s="21" t="n"/>
-      <c r="AB25" s="21" t="n"/>
-      <c r="AC25" s="21" t="n"/>
-      <c r="AD25" s="21" t="n"/>
-      <c r="AE25" s="21" t="n"/>
-      <c r="AF25" s="21" t="n"/>
-      <c r="AG25" s="21" t="n"/>
-      <c r="AH25" s="21" t="n"/>
-      <c r="AI25" s="21" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（目安：幹部＝月総支給×24／役職×12／一般×6ヶ月。具体的金額を記入＝民法465条の2）</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
-      <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="21" t="n"/>
-      <c r="S26" s="21" t="n"/>
-      <c r="T26" s="21" t="n"/>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
-      <c r="X26" s="21" t="n"/>
-      <c r="Y26" s="21" t="n"/>
-      <c r="Z26" s="21" t="n"/>
-      <c r="AA26" s="21" t="n"/>
-      <c r="AB26" s="21" t="n"/>
-      <c r="AC26" s="21" t="n"/>
-      <c r="AD26" s="21" t="n"/>
-      <c r="AE26" s="21" t="n"/>
-      <c r="AF26" s="21" t="n"/>
-      <c r="AG26" s="21" t="n"/>
-      <c r="AH26" s="21" t="n"/>
-      <c r="AI26" s="21" t="n"/>
+      <c r="B25" s="86" t="n"/>
+      <c r="C25" s="86" t="n"/>
+      <c r="D25" s="86" t="n"/>
+      <c r="E25" s="86" t="n"/>
+      <c r="F25" s="86" t="n"/>
+      <c r="G25" s="86" t="n"/>
+      <c r="H25" s="86" t="n"/>
+      <c r="I25" s="86" t="n"/>
+      <c r="J25" s="86" t="n"/>
+      <c r="K25" s="86" t="n"/>
+      <c r="L25" s="86" t="n"/>
+      <c r="M25" s="86" t="n"/>
+      <c r="N25" s="86" t="n"/>
+      <c r="O25" s="86" t="n"/>
+      <c r="P25" s="86" t="n"/>
+      <c r="Q25" s="86" t="n"/>
+      <c r="R25" s="86" t="n"/>
+      <c r="S25" s="86" t="n"/>
+      <c r="T25" s="86" t="n"/>
+      <c r="U25" s="86" t="n"/>
+      <c r="V25" s="86" t="n"/>
+      <c r="W25" s="86" t="n"/>
+      <c r="X25" s="86" t="n"/>
+      <c r="Y25" s="86" t="n"/>
+      <c r="Z25" s="86" t="n"/>
+      <c r="AA25" s="86" t="n"/>
+      <c r="AB25" s="86" t="n"/>
+      <c r="AC25" s="86" t="n"/>
+      <c r="AD25" s="86" t="n"/>
+      <c r="AE25" s="86" t="n"/>
+      <c r="AF25" s="86" t="n"/>
+      <c r="AG25" s="86" t="n"/>
+      <c r="AH25" s="86" t="n"/>
+      <c r="AI25" s="86" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="87" t="inlineStr">
+        <is>
+          <t>（目安：幹部＝月総支給×24／役職×12／一般×6ヶ月。具体的な金額を記入＝民法465条の2）</t>
+        </is>
+      </c>
+      <c r="B26" s="86" t="n"/>
+      <c r="C26" s="86" t="n"/>
+      <c r="D26" s="86" t="n"/>
+      <c r="E26" s="86" t="n"/>
+      <c r="F26" s="86" t="n"/>
+      <c r="G26" s="86" t="n"/>
+      <c r="H26" s="86" t="n"/>
+      <c r="I26" s="86" t="n"/>
+      <c r="J26" s="86" t="n"/>
+      <c r="K26" s="86" t="n"/>
+      <c r="L26" s="86" t="n"/>
+      <c r="M26" s="86" t="n"/>
+      <c r="N26" s="86" t="n"/>
+      <c r="O26" s="86" t="n"/>
+      <c r="P26" s="86" t="n"/>
+      <c r="Q26" s="86" t="n"/>
+      <c r="R26" s="86" t="n"/>
+      <c r="S26" s="86" t="n"/>
+      <c r="T26" s="86" t="n"/>
+      <c r="U26" s="86" t="n"/>
+      <c r="V26" s="86" t="n"/>
+      <c r="W26" s="86" t="n"/>
+      <c r="X26" s="86" t="n"/>
+      <c r="Y26" s="86" t="n"/>
+      <c r="Z26" s="86" t="n"/>
+      <c r="AA26" s="86" t="n"/>
+      <c r="AB26" s="86" t="n"/>
+      <c r="AC26" s="86" t="n"/>
+      <c r="AD26" s="86" t="n"/>
+      <c r="AE26" s="86" t="n"/>
+      <c r="AF26" s="86" t="n"/>
+      <c r="AG26" s="86" t="n"/>
+      <c r="AH26" s="86" t="n"/>
+      <c r="AI26" s="86" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="21" t="n"/>
@@ -2242,7 +2250,7 @@
       <c r="AI30" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="Y28:AH28"/>
     <mergeCell ref="B18:AH18"/>
@@ -2255,7 +2263,10 @@
     <mergeCell ref="V10:Y10"/>
     <mergeCell ref="A4:AI4"/>
     <mergeCell ref="B20:AH20"/>
+    <mergeCell ref="A26:AI26"/>
+    <mergeCell ref="A24:AI24"/>
     <mergeCell ref="B22:AH22"/>
+    <mergeCell ref="A25:AI25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8186,10 +8197,10 @@
       <c r="J23" s="31" t="n"/>
       <c r="K23" s="31" t="n"/>
     </row>
-    <row r="24" ht="10.5" customHeight="1">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="84" t="inlineStr">
         <is>
-          <t>※年次有給休暇は取得理由の記入は不要です（《理由》欄の対象外・労基法39条）</t>
+          <t>※年次有給休暇の《理由》欄は任意記入です（記入がなくても取得できます／労基法39条）</t>
         </is>
       </c>
     </row>

--- a/forms/届出書_法的リスク見直し提案_v2.xlsx
+++ b/forms/届出書_法的リスク見直し提案_v2.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,6 +135,10 @@
       <color rgb="00B91C1C"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -169,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -399,11 +403,16 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -626,6 +635,14 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1247,7 +1264,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
@@ -1973,40 +1989,6 @@
           <t>【身元保証】　保証期間：5年（身元保証法の上限）</t>
         </is>
       </c>
-      <c r="B24" s="86" t="n"/>
-      <c r="C24" s="86" t="n"/>
-      <c r="D24" s="86" t="n"/>
-      <c r="E24" s="86" t="n"/>
-      <c r="F24" s="86" t="n"/>
-      <c r="G24" s="86" t="n"/>
-      <c r="H24" s="86" t="n"/>
-      <c r="I24" s="86" t="n"/>
-      <c r="J24" s="86" t="n"/>
-      <c r="K24" s="86" t="n"/>
-      <c r="L24" s="86" t="n"/>
-      <c r="M24" s="86" t="n"/>
-      <c r="N24" s="86" t="n"/>
-      <c r="O24" s="86" t="n"/>
-      <c r="P24" s="86" t="n"/>
-      <c r="Q24" s="86" t="n"/>
-      <c r="R24" s="86" t="n"/>
-      <c r="S24" s="86" t="n"/>
-      <c r="T24" s="86" t="n"/>
-      <c r="U24" s="86" t="n"/>
-      <c r="V24" s="86" t="n"/>
-      <c r="W24" s="86" t="n"/>
-      <c r="X24" s="86" t="n"/>
-      <c r="Y24" s="86" t="n"/>
-      <c r="Z24" s="86" t="n"/>
-      <c r="AA24" s="86" t="n"/>
-      <c r="AB24" s="86" t="n"/>
-      <c r="AC24" s="86" t="n"/>
-      <c r="AD24" s="86" t="n"/>
-      <c r="AE24" s="86" t="n"/>
-      <c r="AF24" s="86" t="n"/>
-      <c r="AG24" s="86" t="n"/>
-      <c r="AH24" s="86" t="n"/>
-      <c r="AI24" s="86" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="85" t="inlineStr">
@@ -2014,40 +1996,6 @@
           <t xml:space="preserve">　　　　　　　極度額：金　　　　　　　　円</t>
         </is>
       </c>
-      <c r="B25" s="86" t="n"/>
-      <c r="C25" s="86" t="n"/>
-      <c r="D25" s="86" t="n"/>
-      <c r="E25" s="86" t="n"/>
-      <c r="F25" s="86" t="n"/>
-      <c r="G25" s="86" t="n"/>
-      <c r="H25" s="86" t="n"/>
-      <c r="I25" s="86" t="n"/>
-      <c r="J25" s="86" t="n"/>
-      <c r="K25" s="86" t="n"/>
-      <c r="L25" s="86" t="n"/>
-      <c r="M25" s="86" t="n"/>
-      <c r="N25" s="86" t="n"/>
-      <c r="O25" s="86" t="n"/>
-      <c r="P25" s="86" t="n"/>
-      <c r="Q25" s="86" t="n"/>
-      <c r="R25" s="86" t="n"/>
-      <c r="S25" s="86" t="n"/>
-      <c r="T25" s="86" t="n"/>
-      <c r="U25" s="86" t="n"/>
-      <c r="V25" s="86" t="n"/>
-      <c r="W25" s="86" t="n"/>
-      <c r="X25" s="86" t="n"/>
-      <c r="Y25" s="86" t="n"/>
-      <c r="Z25" s="86" t="n"/>
-      <c r="AA25" s="86" t="n"/>
-      <c r="AB25" s="86" t="n"/>
-      <c r="AC25" s="86" t="n"/>
-      <c r="AD25" s="86" t="n"/>
-      <c r="AE25" s="86" t="n"/>
-      <c r="AF25" s="86" t="n"/>
-      <c r="AG25" s="86" t="n"/>
-      <c r="AH25" s="86" t="n"/>
-      <c r="AI25" s="86" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="87" t="inlineStr">
@@ -2055,40 +2003,6 @@
           <t>（目安：幹部＝月総支給×24／役職×12／一般×6ヶ月。具体的な金額を記入＝民法465条の2）</t>
         </is>
       </c>
-      <c r="B26" s="86" t="n"/>
-      <c r="C26" s="86" t="n"/>
-      <c r="D26" s="86" t="n"/>
-      <c r="E26" s="86" t="n"/>
-      <c r="F26" s="86" t="n"/>
-      <c r="G26" s="86" t="n"/>
-      <c r="H26" s="86" t="n"/>
-      <c r="I26" s="86" t="n"/>
-      <c r="J26" s="86" t="n"/>
-      <c r="K26" s="86" t="n"/>
-      <c r="L26" s="86" t="n"/>
-      <c r="M26" s="86" t="n"/>
-      <c r="N26" s="86" t="n"/>
-      <c r="O26" s="86" t="n"/>
-      <c r="P26" s="86" t="n"/>
-      <c r="Q26" s="86" t="n"/>
-      <c r="R26" s="86" t="n"/>
-      <c r="S26" s="86" t="n"/>
-      <c r="T26" s="86" t="n"/>
-      <c r="U26" s="86" t="n"/>
-      <c r="V26" s="86" t="n"/>
-      <c r="W26" s="86" t="n"/>
-      <c r="X26" s="86" t="n"/>
-      <c r="Y26" s="86" t="n"/>
-      <c r="Z26" s="86" t="n"/>
-      <c r="AA26" s="86" t="n"/>
-      <c r="AB26" s="86" t="n"/>
-      <c r="AC26" s="86" t="n"/>
-      <c r="AD26" s="86" t="n"/>
-      <c r="AE26" s="86" t="n"/>
-      <c r="AF26" s="86" t="n"/>
-      <c r="AG26" s="86" t="n"/>
-      <c r="AH26" s="86" t="n"/>
-      <c r="AI26" s="86" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="21" t="n"/>
@@ -3900,16 +3814,44 @@
       <c r="BV26" s="37" t="n"/>
       <c r="BW26" s="37" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="31" t="n"/>
       <c r="B27" s="37" t="n"/>
       <c r="C27" s="37" t="n"/>
       <c r="D27" s="37" t="n"/>
-      <c r="E27" s="39" t="inlineStr">
+      <c r="E27" s="88" t="inlineStr">
         <is>
           <t>また、施錠忘れ又は紛失により被害が生じた場合は、故意又は重大な過失があるときに限り、会社に生じた現実の損害の範囲で、信義則上相当な限度において賠償します。</t>
         </is>
       </c>
+      <c r="F27" s="86" t="n"/>
+      <c r="G27" s="86" t="n"/>
+      <c r="H27" s="86" t="n"/>
+      <c r="I27" s="86" t="n"/>
+      <c r="J27" s="86" t="n"/>
+      <c r="K27" s="86" t="n"/>
+      <c r="L27" s="86" t="n"/>
+      <c r="M27" s="86" t="n"/>
+      <c r="N27" s="86" t="n"/>
+      <c r="O27" s="86" t="n"/>
+      <c r="P27" s="86" t="n"/>
+      <c r="Q27" s="86" t="n"/>
+      <c r="R27" s="86" t="n"/>
+      <c r="S27" s="86" t="n"/>
+      <c r="T27" s="86" t="n"/>
+      <c r="U27" s="86" t="n"/>
+      <c r="V27" s="86" t="n"/>
+      <c r="W27" s="86" t="n"/>
+      <c r="X27" s="86" t="n"/>
+      <c r="Y27" s="86" t="n"/>
+      <c r="Z27" s="86" t="n"/>
+      <c r="AA27" s="86" t="n"/>
+      <c r="AB27" s="86" t="n"/>
+      <c r="AC27" s="86" t="n"/>
+      <c r="AD27" s="86" t="n"/>
+      <c r="AE27" s="86" t="n"/>
+      <c r="AF27" s="86" t="n"/>
+      <c r="AG27" s="86" t="n"/>
       <c r="AH27" s="37" t="n"/>
       <c r="AI27" s="37" t="n"/>
       <c r="AJ27" s="37" t="n"/>
@@ -3953,11 +3895,40 @@
       <c r="BV27" s="37" t="n"/>
       <c r="BW27" s="37" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="31" t="n"/>
       <c r="B28" s="37" t="n"/>
       <c r="C28" s="37" t="n"/>
       <c r="D28" s="37" t="n"/>
+      <c r="E28" s="86" t="n"/>
+      <c r="F28" s="86" t="n"/>
+      <c r="G28" s="86" t="n"/>
+      <c r="H28" s="86" t="n"/>
+      <c r="I28" s="86" t="n"/>
+      <c r="J28" s="86" t="n"/>
+      <c r="K28" s="86" t="n"/>
+      <c r="L28" s="86" t="n"/>
+      <c r="M28" s="86" t="n"/>
+      <c r="N28" s="86" t="n"/>
+      <c r="O28" s="86" t="n"/>
+      <c r="P28" s="86" t="n"/>
+      <c r="Q28" s="86" t="n"/>
+      <c r="R28" s="86" t="n"/>
+      <c r="S28" s="86" t="n"/>
+      <c r="T28" s="86" t="n"/>
+      <c r="U28" s="86" t="n"/>
+      <c r="V28" s="86" t="n"/>
+      <c r="W28" s="86" t="n"/>
+      <c r="X28" s="86" t="n"/>
+      <c r="Y28" s="86" t="n"/>
+      <c r="Z28" s="86" t="n"/>
+      <c r="AA28" s="86" t="n"/>
+      <c r="AB28" s="86" t="n"/>
+      <c r="AC28" s="86" t="n"/>
+      <c r="AD28" s="86" t="n"/>
+      <c r="AE28" s="86" t="n"/>
+      <c r="AF28" s="86" t="n"/>
+      <c r="AG28" s="86" t="n"/>
       <c r="AH28" s="37" t="n"/>
       <c r="AI28" s="37" t="n"/>
       <c r="AJ28" s="37" t="n"/>
@@ -6738,83 +6709,83 @@
       <c r="AH22" s="25" t="n"/>
       <c r="AI22" s="25" t="n"/>
     </row>
-    <row r="23" ht="29.25" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="21" t="n"/>
       <c r="B23" s="21" t="n"/>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="89" t="inlineStr">
         <is>
           <t>・故意又は重大な過失により紛失・破損した場合は、会社に生じた現実の損害の範囲で相当な限度において負担いただくことがあります。</t>
         </is>
       </c>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="25" t="n"/>
-      <c r="M23" s="25" t="n"/>
-      <c r="N23" s="25" t="n"/>
-      <c r="O23" s="25" t="n"/>
-      <c r="P23" s="25" t="n"/>
-      <c r="Q23" s="25" t="n"/>
-      <c r="R23" s="25" t="n"/>
-      <c r="S23" s="25" t="n"/>
-      <c r="T23" s="25" t="n"/>
-      <c r="U23" s="25" t="n"/>
-      <c r="V23" s="25" t="n"/>
-      <c r="W23" s="25" t="n"/>
-      <c r="X23" s="25" t="n"/>
-      <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="25" t="n"/>
-      <c r="AA23" s="25" t="n"/>
-      <c r="AB23" s="25" t="n"/>
-      <c r="AC23" s="25" t="n"/>
-      <c r="AD23" s="25" t="n"/>
-      <c r="AE23" s="25" t="n"/>
-      <c r="AF23" s="25" t="n"/>
-      <c r="AG23" s="25" t="n"/>
-      <c r="AH23" s="25" t="n"/>
-      <c r="AI23" s="25" t="n"/>
-    </row>
-    <row r="24">
+      <c r="D23" s="90" t="n"/>
+      <c r="E23" s="90" t="n"/>
+      <c r="F23" s="90" t="n"/>
+      <c r="G23" s="90" t="n"/>
+      <c r="H23" s="90" t="n"/>
+      <c r="I23" s="90" t="n"/>
+      <c r="J23" s="90" t="n"/>
+      <c r="K23" s="90" t="n"/>
+      <c r="L23" s="90" t="n"/>
+      <c r="M23" s="90" t="n"/>
+      <c r="N23" s="90" t="n"/>
+      <c r="O23" s="90" t="n"/>
+      <c r="P23" s="90" t="n"/>
+      <c r="Q23" s="90" t="n"/>
+      <c r="R23" s="90" t="n"/>
+      <c r="S23" s="90" t="n"/>
+      <c r="T23" s="90" t="n"/>
+      <c r="U23" s="90" t="n"/>
+      <c r="V23" s="90" t="n"/>
+      <c r="W23" s="90" t="n"/>
+      <c r="X23" s="90" t="n"/>
+      <c r="Y23" s="90" t="n"/>
+      <c r="Z23" s="90" t="n"/>
+      <c r="AA23" s="90" t="n"/>
+      <c r="AB23" s="90" t="n"/>
+      <c r="AC23" s="90" t="n"/>
+      <c r="AD23" s="90" t="n"/>
+      <c r="AE23" s="90" t="n"/>
+      <c r="AF23" s="90" t="n"/>
+      <c r="AG23" s="90" t="n"/>
+      <c r="AH23" s="90" t="n"/>
+      <c r="AI23" s="90" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="21" t="n"/>
       <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="21" t="n"/>
-      <c r="T24" s="21" t="n"/>
-      <c r="U24" s="21" t="n"/>
-      <c r="V24" s="21" t="n"/>
-      <c r="W24" s="21" t="n"/>
-      <c r="X24" s="21" t="n"/>
-      <c r="Y24" s="21" t="n"/>
-      <c r="Z24" s="21" t="n"/>
-      <c r="AA24" s="21" t="n"/>
-      <c r="AB24" s="21" t="n"/>
-      <c r="AC24" s="21" t="n"/>
-      <c r="AD24" s="21" t="n"/>
-      <c r="AE24" s="21" t="n"/>
-      <c r="AF24" s="21" t="n"/>
-      <c r="AG24" s="21" t="n"/>
-      <c r="AH24" s="21" t="n"/>
-      <c r="AI24" s="21" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="91" t="n"/>
+      <c r="E24" s="91" t="n"/>
+      <c r="F24" s="91" t="n"/>
+      <c r="G24" s="91" t="n"/>
+      <c r="H24" s="91" t="n"/>
+      <c r="I24" s="91" t="n"/>
+      <c r="J24" s="91" t="n"/>
+      <c r="K24" s="91" t="n"/>
+      <c r="L24" s="91" t="n"/>
+      <c r="M24" s="91" t="n"/>
+      <c r="N24" s="91" t="n"/>
+      <c r="O24" s="91" t="n"/>
+      <c r="P24" s="91" t="n"/>
+      <c r="Q24" s="91" t="n"/>
+      <c r="R24" s="91" t="n"/>
+      <c r="S24" s="91" t="n"/>
+      <c r="T24" s="91" t="n"/>
+      <c r="U24" s="91" t="n"/>
+      <c r="V24" s="91" t="n"/>
+      <c r="W24" s="91" t="n"/>
+      <c r="X24" s="91" t="n"/>
+      <c r="Y24" s="91" t="n"/>
+      <c r="Z24" s="91" t="n"/>
+      <c r="AA24" s="91" t="n"/>
+      <c r="AB24" s="91" t="n"/>
+      <c r="AC24" s="91" t="n"/>
+      <c r="AD24" s="91" t="n"/>
+      <c r="AE24" s="91" t="n"/>
+      <c r="AF24" s="91" t="n"/>
+      <c r="AG24" s="91" t="n"/>
+      <c r="AH24" s="91" t="n"/>
+      <c r="AI24" s="91" t="n"/>
     </row>
     <row r="25" ht="29.25" customHeight="1">
       <c r="A25" s="21" t="n"/>
@@ -6899,7 +6870,8 @@
       <c r="AI26" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C23:AI24"/>
     <mergeCell ref="V9:Y9"/>
     <mergeCell ref="V8:Y8"/>
     <mergeCell ref="A3:AI3"/>

--- a/forms/届出書_法的リスク見直し提案_v2.xlsx
+++ b/forms/届出書_法的リスク見直し提案_v2.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後③物品借用書" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後④メアド申請書" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後⑤勤務休暇届" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善後⑥身元保証書" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,6 +140,12 @@
       <name val="Yu Gothic"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001E3A6B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -173,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -408,11 +415,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00666666"/>
+      </left>
+      <right style="thin">
+        <color rgb="00666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="00666666"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00666666"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -643,6 +664,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1096,7 +1145,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>「如何なる損害賠償にも応じ」→「法令の範囲内で、会社に生じた現実の損害について、下記の極度額を上限として応分の賠償責任を負う」に変更。身元保証は「保証期間：5年（身元保証法の上限）」と「極度額」を必ず明記する。極度額は月の総支給額を基準に、幹部24ヶ月／役職12ヶ月／一般社員6ヶ月とする（下表）。推奨は連帯保証・身元保証を外し守秘義務誓約書にすること。</t>
+          <t>身元保証は別紙「身元保証書」（保証人が記入・署名）に分離。誓約書は守秘義務＋本人の賠償条項（現実の損害・法令の範囲内）に限定。身元保証書に保証期間5年・極度額（幹部24/役職12/一般6ヶ月から算出した具体的金額）を明記。</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1990,7 @@
       <c r="A22" s="21" t="n"/>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">　上記誓約に違反し、故意又は重大な過失により会社に損害を与えた場合は、法令の範囲内で、会社に生じた現実の損害について、下記の極度額を上限として応分の賠償責任を負います。</t>
+          <t xml:space="preserve">　上記誓約に違反し、故意又は重大な過失により会社に損害を与えた場合は、法令の範囲内で、会社に生じた現実の損害について応分の賠償責任を負います。</t>
         </is>
       </c>
       <c r="AI22" s="21" t="n"/>
@@ -1984,25 +2033,18 @@
       <c r="AI23" s="21" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="85" t="inlineStr">
-        <is>
-          <t>【身元保証】　保証期間：5年（身元保証法の上限）</t>
+      <c r="A24" s="92" t="n"/>
+      <c r="B24" s="93" t="inlineStr">
+        <is>
+          <t>※ 身元保証は別紙「身元保証書」（保証人が記入・署名）に分離しました。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　　　　　　極度額：金　　　　　　　　円</t>
-        </is>
-      </c>
+      <c r="A25" s="92" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="87" t="inlineStr">
-        <is>
-          <t>（目安：幹部＝月総支給×24／役職×12／一般×6ヶ月。具体的な金額を記入＝民法465条の2）</t>
-        </is>
-      </c>
+      <c r="A26" s="94" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="21" t="n"/>
@@ -2029,11 +2071,7 @@
       <c r="V27" s="21" t="n"/>
       <c r="W27" s="21" t="n"/>
       <c r="X27" s="21" t="n"/>
-      <c r="Y27" s="21" t="inlineStr">
-        <is>
-          <t>【保証人】</t>
-        </is>
-      </c>
+      <c r="Y27" s="21" t="n"/>
       <c r="Z27" s="21" t="n"/>
       <c r="AA27" s="21" t="n"/>
       <c r="AB27" s="21" t="n"/>
@@ -2065,11 +2103,7 @@
       <c r="Q28" s="21" t="n"/>
       <c r="R28" s="21" t="n"/>
       <c r="S28" s="21" t="n"/>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
+      <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
       <c r="V28" s="21" t="n"/>
       <c r="W28" s="21" t="n"/>
@@ -2097,11 +2131,7 @@
       <c r="Q29" s="21" t="n"/>
       <c r="R29" s="21" t="n"/>
       <c r="S29" s="21" t="n"/>
-      <c r="T29" s="21" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
+      <c r="T29" s="21" t="n"/>
       <c r="U29" s="21" t="n"/>
       <c r="V29" s="21" t="n"/>
       <c r="W29" s="21" t="n"/>
@@ -2115,11 +2145,7 @@
       <c r="AE29" s="21" t="n"/>
       <c r="AF29" s="21" t="n"/>
       <c r="AG29" s="21" t="n"/>
-      <c r="AH29" s="21" t="inlineStr">
-        <is>
-          <t>印</t>
-        </is>
-      </c>
+      <c r="AH29" s="21" t="n"/>
       <c r="AI29" s="21" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
@@ -2142,11 +2168,7 @@
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
       <c r="S30" s="21" t="n"/>
-      <c r="T30" s="21" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
+      <c r="T30" s="21" t="n"/>
       <c r="U30" s="21" t="n"/>
       <c r="V30" s="21" t="n"/>
       <c r="W30" s="21" t="n"/>
@@ -2164,7 +2186,7 @@
       <c r="AI30" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="14">
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="Y28:AH28"/>
     <mergeCell ref="B18:AH18"/>
@@ -2173,14 +2195,12 @@
     <mergeCell ref="A14:AI14"/>
     <mergeCell ref="B12:AH12"/>
     <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="B24:AH24"/>
     <mergeCell ref="B16:AH16"/>
     <mergeCell ref="V10:Y10"/>
     <mergeCell ref="A4:AI4"/>
     <mergeCell ref="B20:AH20"/>
-    <mergeCell ref="A26:AI26"/>
-    <mergeCell ref="A24:AI24"/>
     <mergeCell ref="B22:AH22"/>
-    <mergeCell ref="A25:AI25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3824,34 +3844,6 @@
           <t>また、施錠忘れ又は紛失により被害が生じた場合は、故意又は重大な過失があるときに限り、会社に生じた現実の損害の範囲で、信義則上相当な限度において賠償します。</t>
         </is>
       </c>
-      <c r="F27" s="86" t="n"/>
-      <c r="G27" s="86" t="n"/>
-      <c r="H27" s="86" t="n"/>
-      <c r="I27" s="86" t="n"/>
-      <c r="J27" s="86" t="n"/>
-      <c r="K27" s="86" t="n"/>
-      <c r="L27" s="86" t="n"/>
-      <c r="M27" s="86" t="n"/>
-      <c r="N27" s="86" t="n"/>
-      <c r="O27" s="86" t="n"/>
-      <c r="P27" s="86" t="n"/>
-      <c r="Q27" s="86" t="n"/>
-      <c r="R27" s="86" t="n"/>
-      <c r="S27" s="86" t="n"/>
-      <c r="T27" s="86" t="n"/>
-      <c r="U27" s="86" t="n"/>
-      <c r="V27" s="86" t="n"/>
-      <c r="W27" s="86" t="n"/>
-      <c r="X27" s="86" t="n"/>
-      <c r="Y27" s="86" t="n"/>
-      <c r="Z27" s="86" t="n"/>
-      <c r="AA27" s="86" t="n"/>
-      <c r="AB27" s="86" t="n"/>
-      <c r="AC27" s="86" t="n"/>
-      <c r="AD27" s="86" t="n"/>
-      <c r="AE27" s="86" t="n"/>
-      <c r="AF27" s="86" t="n"/>
-      <c r="AG27" s="86" t="n"/>
       <c r="AH27" s="37" t="n"/>
       <c r="AI27" s="37" t="n"/>
       <c r="AJ27" s="37" t="n"/>
@@ -3900,35 +3892,6 @@
       <c r="B28" s="37" t="n"/>
       <c r="C28" s="37" t="n"/>
       <c r="D28" s="37" t="n"/>
-      <c r="E28" s="86" t="n"/>
-      <c r="F28" s="86" t="n"/>
-      <c r="G28" s="86" t="n"/>
-      <c r="H28" s="86" t="n"/>
-      <c r="I28" s="86" t="n"/>
-      <c r="J28" s="86" t="n"/>
-      <c r="K28" s="86" t="n"/>
-      <c r="L28" s="86" t="n"/>
-      <c r="M28" s="86" t="n"/>
-      <c r="N28" s="86" t="n"/>
-      <c r="O28" s="86" t="n"/>
-      <c r="P28" s="86" t="n"/>
-      <c r="Q28" s="86" t="n"/>
-      <c r="R28" s="86" t="n"/>
-      <c r="S28" s="86" t="n"/>
-      <c r="T28" s="86" t="n"/>
-      <c r="U28" s="86" t="n"/>
-      <c r="V28" s="86" t="n"/>
-      <c r="W28" s="86" t="n"/>
-      <c r="X28" s="86" t="n"/>
-      <c r="Y28" s="86" t="n"/>
-      <c r="Z28" s="86" t="n"/>
-      <c r="AA28" s="86" t="n"/>
-      <c r="AB28" s="86" t="n"/>
-      <c r="AC28" s="86" t="n"/>
-      <c r="AD28" s="86" t="n"/>
-      <c r="AE28" s="86" t="n"/>
-      <c r="AF28" s="86" t="n"/>
-      <c r="AG28" s="86" t="n"/>
       <c r="AH28" s="37" t="n"/>
       <c r="AI28" s="37" t="n"/>
       <c r="AJ28" s="37" t="n"/>
@@ -6717,75 +6680,75 @@
           <t>・故意又は重大な過失により紛失・破損した場合は、会社に生じた現実の損害の範囲で相当な限度において負担いただくことがあります。</t>
         </is>
       </c>
-      <c r="D23" s="90" t="n"/>
-      <c r="E23" s="90" t="n"/>
-      <c r="F23" s="90" t="n"/>
-      <c r="G23" s="90" t="n"/>
-      <c r="H23" s="90" t="n"/>
-      <c r="I23" s="90" t="n"/>
-      <c r="J23" s="90" t="n"/>
-      <c r="K23" s="90" t="n"/>
-      <c r="L23" s="90" t="n"/>
-      <c r="M23" s="90" t="n"/>
-      <c r="N23" s="90" t="n"/>
-      <c r="O23" s="90" t="n"/>
-      <c r="P23" s="90" t="n"/>
-      <c r="Q23" s="90" t="n"/>
-      <c r="R23" s="90" t="n"/>
-      <c r="S23" s="90" t="n"/>
-      <c r="T23" s="90" t="n"/>
-      <c r="U23" s="90" t="n"/>
-      <c r="V23" s="90" t="n"/>
-      <c r="W23" s="90" t="n"/>
-      <c r="X23" s="90" t="n"/>
-      <c r="Y23" s="90" t="n"/>
-      <c r="Z23" s="90" t="n"/>
-      <c r="AA23" s="90" t="n"/>
-      <c r="AB23" s="90" t="n"/>
-      <c r="AC23" s="90" t="n"/>
-      <c r="AD23" s="90" t="n"/>
-      <c r="AE23" s="90" t="n"/>
-      <c r="AF23" s="90" t="n"/>
-      <c r="AG23" s="90" t="n"/>
-      <c r="AH23" s="90" t="n"/>
-      <c r="AI23" s="90" t="n"/>
+      <c r="D23" s="66" t="n"/>
+      <c r="E23" s="66" t="n"/>
+      <c r="F23" s="66" t="n"/>
+      <c r="G23" s="66" t="n"/>
+      <c r="H23" s="66" t="n"/>
+      <c r="I23" s="66" t="n"/>
+      <c r="J23" s="66" t="n"/>
+      <c r="K23" s="66" t="n"/>
+      <c r="L23" s="66" t="n"/>
+      <c r="M23" s="66" t="n"/>
+      <c r="N23" s="66" t="n"/>
+      <c r="O23" s="66" t="n"/>
+      <c r="P23" s="66" t="n"/>
+      <c r="Q23" s="66" t="n"/>
+      <c r="R23" s="66" t="n"/>
+      <c r="S23" s="66" t="n"/>
+      <c r="T23" s="66" t="n"/>
+      <c r="U23" s="66" t="n"/>
+      <c r="V23" s="66" t="n"/>
+      <c r="W23" s="66" t="n"/>
+      <c r="X23" s="66" t="n"/>
+      <c r="Y23" s="66" t="n"/>
+      <c r="Z23" s="66" t="n"/>
+      <c r="AA23" s="66" t="n"/>
+      <c r="AB23" s="66" t="n"/>
+      <c r="AC23" s="66" t="n"/>
+      <c r="AD23" s="66" t="n"/>
+      <c r="AE23" s="66" t="n"/>
+      <c r="AF23" s="66" t="n"/>
+      <c r="AG23" s="66" t="n"/>
+      <c r="AH23" s="66" t="n"/>
+      <c r="AI23" s="66" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="21" t="n"/>
       <c r="B24" s="21" t="n"/>
-      <c r="C24" s="91" t="n"/>
-      <c r="D24" s="91" t="n"/>
-      <c r="E24" s="91" t="n"/>
-      <c r="F24" s="91" t="n"/>
-      <c r="G24" s="91" t="n"/>
-      <c r="H24" s="91" t="n"/>
-      <c r="I24" s="91" t="n"/>
-      <c r="J24" s="91" t="n"/>
-      <c r="K24" s="91" t="n"/>
-      <c r="L24" s="91" t="n"/>
-      <c r="M24" s="91" t="n"/>
-      <c r="N24" s="91" t="n"/>
-      <c r="O24" s="91" t="n"/>
-      <c r="P24" s="91" t="n"/>
-      <c r="Q24" s="91" t="n"/>
-      <c r="R24" s="91" t="n"/>
-      <c r="S24" s="91" t="n"/>
-      <c r="T24" s="91" t="n"/>
-      <c r="U24" s="91" t="n"/>
-      <c r="V24" s="91" t="n"/>
-      <c r="W24" s="91" t="n"/>
-      <c r="X24" s="91" t="n"/>
-      <c r="Y24" s="91" t="n"/>
-      <c r="Z24" s="91" t="n"/>
-      <c r="AA24" s="91" t="n"/>
-      <c r="AB24" s="91" t="n"/>
-      <c r="AC24" s="91" t="n"/>
-      <c r="AD24" s="91" t="n"/>
-      <c r="AE24" s="91" t="n"/>
-      <c r="AF24" s="91" t="n"/>
-      <c r="AG24" s="91" t="n"/>
-      <c r="AH24" s="91" t="n"/>
-      <c r="AI24" s="91" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="41" t="n"/>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="41" t="n"/>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="n"/>
+      <c r="I24" s="41" t="n"/>
+      <c r="J24" s="41" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="41" t="n"/>
+      <c r="M24" s="41" t="n"/>
+      <c r="N24" s="41" t="n"/>
+      <c r="O24" s="41" t="n"/>
+      <c r="P24" s="41" t="n"/>
+      <c r="Q24" s="41" t="n"/>
+      <c r="R24" s="41" t="n"/>
+      <c r="S24" s="41" t="n"/>
+      <c r="T24" s="41" t="n"/>
+      <c r="U24" s="41" t="n"/>
+      <c r="V24" s="41" t="n"/>
+      <c r="W24" s="41" t="n"/>
+      <c r="X24" s="41" t="n"/>
+      <c r="Y24" s="41" t="n"/>
+      <c r="Z24" s="41" t="n"/>
+      <c r="AA24" s="41" t="n"/>
+      <c r="AB24" s="41" t="n"/>
+      <c r="AC24" s="41" t="n"/>
+      <c r="AD24" s="41" t="n"/>
+      <c r="AE24" s="41" t="n"/>
+      <c r="AF24" s="41" t="n"/>
+      <c r="AG24" s="41" t="n"/>
+      <c r="AH24" s="41" t="n"/>
+      <c r="AI24" s="41" t="n"/>
     </row>
     <row r="25" ht="29.25" customHeight="1">
       <c r="A25" s="21" t="n"/>
@@ -8610,4 +8573,153 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>※ 新設様式（保証人が記入・署名）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>身　元　保　証　書</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="95" t="inlineStr">
+        <is>
+          <t>令和　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="96" t="inlineStr">
+        <is>
+          <t>株式会社ウェルピア羽島／大日産業株式会社　　代表取締役　林　幹根　殿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　下記の被用者の身元を保証します。被用者が故意又は重大な過失により貴社に損害を与えた場合は、本書に定める極度額を限度として、被用者と連帯して賠償の責任を負います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="98" t="inlineStr">
+        <is>
+          <t>被用者 氏名</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>被用者 所属</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="100" t="inlineStr">
+        <is>
+          <t>保証期間</t>
+        </is>
+      </c>
+      <c r="C13" s="101" t="inlineStr">
+        <is>
+          <t>本書締結日から　5年間　（身元保証法に基づく上限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="100" t="inlineStr">
+        <is>
+          <t>極度額</t>
+        </is>
+      </c>
+      <c r="C14" s="101" t="inlineStr">
+        <is>
+          <t>金　　　　　　　　円</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="C15" s="87" t="inlineStr">
+        <is>
+          <t>（目安：幹部＝月総支給×24ヶ月／役職×12ヶ月／一般社員×6ヶ月。具体的な金額を記入＝民法465条の2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="98" t="inlineStr">
+        <is>
+          <t>保証人 住所</t>
+        </is>
+      </c>
+      <c r="C17" s="99" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="98" t="inlineStr">
+        <is>
+          <t>保証人 氏名</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　　　　　　　　　　　　　　㊞</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="98" t="inlineStr">
+        <is>
+          <t>保証人 生年月日</t>
+        </is>
+      </c>
+      <c r="C19" s="99" t="inlineStr">
+        <is>
+          <t>令和・昭和・平成　　　年　　　月　　　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="98" t="inlineStr">
+        <is>
+          <t>被用者との関係</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>